--- a/GII.xlsx
+++ b/GII.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,23 +544,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ventilator Market Size, Share, and Growth Analysis, By Product Type (Intensive Care Ventilators, Portable Ventilators), By Modality (Non-Invasive Ventilation, Invasive Ventilation), By Ventilator Type, By Mode, By End User, By Region - Industry Forecast 2025-2032</t>
+          <t>Go Kart Market Size, Share, and Growth Analysis, By Propulsion(Electric, Gasoline, Others), By Application(Rental (Electric, Gasoline, Others), Racing (Electric), By Seating Capacity(Single, Double), By Track(Indoor, Outdoor), By Region  - Industry Forecast 2025-2032</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SQMIG35A2176</t>
+          <t>SQMIG25J2070</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.skyquestt.com/report/ventilator-market</t>
+          <t>https://www.skyquestt.com/report/go-kart-market</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>223</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -581,17 +581,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Ventilator Market size was valued at USD 3.9 billion in 2023 and is poised to grow from USD 4.15 billion in 2024 to USD 6.76 billion by 2032, growing at a CAGR of 6.3% during the forecast period (2025-2032).
-The ventilator market is poised for significant growth driven by technological advancements, such as sophisticated portable ventilators and enhanced sensor technologies. Contributing factors include rising rates of preterm births, an aging population, a surge in respiratory diseases, and an increase in ICU bed availability. The shift toward home healthcare presents new opportunities, offering cost-effective and comfortable solutions for patients. Advances in microprocessor-controlled ventilation and innovative ventilator modes have revolutionized the treatment of severe respiratory conditions. Upgraded ventilators now feature extensive safeguards, ensuring readiness for emergencies with integrated sensors and monitors tracking crucial parameters like air pressure, volume, flow rate, and mechanical integrity, including battery backups and oxygen levels, thus ensuring comprehensive patient safety and care.
-Top-down and bottom-up approaches were used to estimate and validate the size of the Ventilator market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
-Ventilator Market Segments Analysis
-Global Ventilator Market is segmented by Product Type, Modality, Ventilator Type, Mode, End User and region. Based on Product Type, the market is segmented into Intensive Care Ventilators, Portable Ventilators and Neonatal Ventilators. Based on Modality, the market is segmented into Non-Invasive Ventilation and Invasive Ventilation. Based on Ventilator Type, the market is segmented into Adult Ventilators, Neonatal Ventilators and Pediatric Ventilators. Based on Mode, the market is segmented into Combined-Mode Ventilation, Volume-Mode Ventilation, Pressure-Mode Ventilator and Other. Based on End User, the market is segmented into Hospitals, Specialty Clinics, Long Term Care Centers, Rehabilitation Centers, Homecare Settings and Others. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
-Driver of the Ventilator Market
-The global ventilator market is primarily driven by the rising incidence of respiratory conditions, including chronic obstructive pulmonary disease, sleep apnea, acute lung injury, and hypoxemia. Additionally, the growing elderly population and the increase in preterm births are significant factors contributing to market expansion. Furthermore, the widespread prevalence of tobacco use, which is a leading cause of respiratory illnesses, further stimulates the demand for ventilators. As these health challenges escalate, the need for effective respiratory support devices becomes increasingly critical, thereby enhancing market growth and creating opportunities for innovation and development within the ventilator sector.
-Restraints in the Ventilator Market
-The ventilator market faces significant restraints due to the rising number of undiagnosed and undertreated patients, which can be attributed to a lack of awareness about respiratory diseases among the general population. As more individuals remain unaware of their respiratory conditions and thus go untreated, the demand for ventilators may not grow as expected, ultimately impeding market expansion. This issue highlights the need for increased education and awareness campaigns to inform patients about respiratory health, as addressing the gap in diagnosis and treatment could improve market dynamics and encourage better utilization of ventilatory support systems.
-Market Trends of the Ventilator Market
-The ventilator market is witnessing significant growth driven by technological advancements, including the rise of portable ventilators and those equipped with advanced sensors for real-time monitoring and data transfer, enhancing clinical decision-making. This trend is further fueled by the increasing incidence of respiratory diseases globally, particularly in emerging economies like India, China, and Japan, where healthcare infrastructure is rapidly evolving. The demand for innovative solutions that improve patient outcomes and the efficiency of care delivery is propelling market expansion. As healthcare systems adapt to meet rising patient needs, the ventilator market is positioned for sustained growth, highlighting the importance of innovation in medical technology.</t>
+          <t>Global Go Kart Market size was valued at USD 153.4 billion in 2023 and is poised to grow from USD 160.46 billion in 2024 to USD 229.94 billion by 2032, growing at a CAGR of 4.6% during the forecast period (2025-2032).
+The global go-kart market is thriving within the leisure and motorsport sectors, appealing to a diverse audience from children to adults. As an entry-level motorsport, go-karting offers an affordable and safe way for enthusiasts to experience racing, fueling the growth of tracks and rental facilities worldwide. This activity serves not only as a competitive sport but also as a family-friendly entertainment option, commonly featured in amusement parks and recreation centers. Furthermore, many professional drivers, including Formula 1 champions, began their journeys in go-karting, underscoring its role in nurturing future racing talent. The market is also evolving with advancements in technology, particularly the rise of electric go-karts, which are increasingly popular for their eco-friendliness and suitability for indoor tracks, further broadening the participant base.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Go Kart market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Go Kart Market Segments Analysis
+Global Go Kart Market is segmented by Propulsion Type, Seating Capacity, Track, Application and region. Based on Propulsion Type, the market is segmented into Gasoline, Electric and Others. Based on Seating Capacity, the market is segmented into Single Seater and Double Seater. Based on Track, the market is segmented into Indoor and Outdoor. Based on Application, the market is segmented into Rental and Racing. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Go Kart Market
+The global go-kart market is being significantly propelled by the increasing popularity of go-karting as a recreational activity, providing enjoyment for individuals and families alike. This thrilling motorsport attracts participants of various ages and skill levels, making it accessible to a wide audience. The rising demand for leisure go-karting experiences, encompassing both indoor and outdoor tracks, has further fueled market growth. As more people seek out fun and engaging entertainment options, the go-kart industry capitalizes on this trend, resulting in a vibrant and expanding market that caters to a diverse range of enthusiasts looking for excitement and enjoyment.
+Restraints in the Global Go Kart Market
+Safety issues have emerged as a notable constraint within the global go-kart market. The potential for accidents and injuries during go-karting can be heightened when safety standards and protocols are not adhered to diligently. This concern has prompted heightened scrutiny and an urgent demand for enhanced safety measures and regulations within the industry. Consequently, businesses in the go-kart sector may face elevated operational costs as they strive to implement necessary safety improvements. These financial implications can deter investment and growth in the market, ultimately impacting its overall expansion and attractiveness to potential stakeholders.
+Market Trends of the Global Go Kart Market
+The Global Go-Kart market is witnessing a significant shift towards electric go-karts, driven by their myriad advantages over traditional gasoline-powered models. As consumers become more environmentally conscious and seek quieter, less maintenance-intensive options, go-kart rental facilities and racing tracks are increasingly adopting electric models to meet this demand. This trend aligns with the wider movement towards sustainable electric mobility within the automotive sector. Electric go-karts not only enhance the user experience with their clean and efficient operation but also appeal to a broader audience, further boosting market growth and innovation in go-kart design and technology.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -631,57 +631,46 @@
 o Macro-Economic Indicators
 o Value Chain Analysis
 o Pricing Analysis
-o Regulatory Analysis
-o Technology Analysis
-• Global Ventilator Market Size by Product Type &amp; CAGR (2025-2032)
-o Market Overview
-o Intensive Care Ventilators
-o Portable Ventilators
-o Neonatal Ventilators
-• Global Ventilator Market Size by Modality &amp; CAGR (2025-2032)
-o Market Overview
-o Non-Invasive Ventilation
-o Invasive Ventilation
-• Global Ventilator Market Size by Ventilator Type &amp; CAGR (2025-2032)
-o Market Overview
-o Adult Ventilators
-o Neonatal Ventilators
-o Pediatric Ventilators
-• Global Ventilator Market Size by Mode &amp; CAGR (2025-2032)
-o Market Overview
-o Combined-Mode Ventilation
-o Volume-Mode Ventilation
-o Pressure-Mode Ventilator
-o Other
-• Global Ventilator Market Size by End User &amp; CAGR (2025-2032)
-o Market Overview
-o Hospitals
-o Specialty Clinics
-o Long Term Care Centers
-o Rehabilitation Centers
-o Homecare Settings
+o Regulatory Landscape
+o Case Studies
+• Global Go Kart Market Size by Propulsion Type &amp; CAGR (2025-2032)
+o Market Overview
+o Gasoline
+o Electric
 o Others
-• Global Ventilator Market Size &amp; CAGR (2025-2032)
-o North America (Product Type, Modality, Ventilator Type, Mode, End User)
+• Global Go Kart Market Size by Seating Capacity &amp; CAGR (2025-2032)
+o Market Overview
+o Single Seater
+o Double Seater
+• Global Go Kart Market Size by Track &amp; CAGR (2025-2032)
+o Market Overview
+o Indoor
+o Outdoor
+• Global Go Kart Market Size by Application &amp; CAGR (2025-2032)
+o Market Overview
+o Rental
+o Racing
+• Global Go Kart Market Size &amp; CAGR (2025-2032)
+o North America (Propulsion Type, Seating Capacity, Track, Application)
  US
  Canada
-o Europe (Product Type, Modality, Ventilator Type, Mode, End User)
+o Europe (Propulsion Type, Seating Capacity, Track, Application)
  Germany
  Spain
  France
  UK
  Italy
  Rest of Europe
-o Asia Pacific (Product Type, Modality, Ventilator Type, Mode, End User)
+o Asia Pacific (Propulsion Type, Seating Capacity, Track, Application)
  China
  India
  Japan
  South Korea
  Rest of Asia-Pacific
-o Latin America (Product Type, Modality, Ventilator Type, Mode, End User)
+o Latin America (Propulsion Type, Seating Capacity, Track, Application)
  Brazil
  Rest of Latin America
-o Middle East &amp; Africa (Product Type, Modality, Ventilator Type, Mode, End User)
+o Middle East &amp; Africa (Propulsion Type, Seating Capacity, Track, Application)
  GCC Countries
  South Africa
  Rest of Middle East &amp; Africa
@@ -697,102 +686,82 @@
  Company's Segmental Share Analysis
  Revenue Y-O-Y Comparison (2022-2024)
 • Key Company Profiles
-o Medtronic (Ireland)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o ResMed (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Philips (Netherlands)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Getinge (Sweden)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Hamilton Medical (Switzerland)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Drägerwerk AG &amp; Co. KGaA (Germany)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Vyaire Medical (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Fisher &amp; Paykel Healthcare (New Zealand)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Maquet (Germany)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o GE Healthcare (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Allied Healthcare Products, Inc. (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Teleflex Incorporated (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Becton, Dickinson and Company (BD) (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Nihon Kohden Corporation (Japan)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Fukuda Denshi Co., Ltd. (Japan)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Siare Engineering International Group S.r.l. (Italy)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Airon Corporation (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Breas Medical AB (Sweden)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Loewenstein Medical GmbH + Co. KG (Germany)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Beijing Aeonmed Co., Ltd. (China)
+o Sodi Kart (France)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Kart Republic (Italy)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Praga Karts (Czech Republic)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o RS Kart (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Arrow Karts (Australia)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Alfano (Italy)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Righetti Ridolfi (Italy)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Rotax (Austria)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o OTK Kart Group (Italy)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o RMS Karts (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Aqua Kart (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o PDB Karts (Australia)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o SH Karting (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o KZ Karts (France)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o FA Kart (Italy)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Birel ART Racing (Italy)
  Company Overview
  Business Segment Overview
  Financial Updates
@@ -804,7 +773,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -827,51 +796,47 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>◦ Medtronic (Ireland)
-◦ ResMed (US)
-◦ Philips (Netherlands)
-◦ Getinge (Sweden)
-◦ Hamilton Medical (Switzerland)
-◦ Drägerwerk AG &amp; Co. KGaA (Germany)
-◦ Vyaire Medical (US)
-◦ Fisher &amp; Paykel Healthcare (New Zealand)
-◦ Maquet (Germany)
-◦ GE Healthcare (US)
-◦ Allied Healthcare Products, Inc. (US)
-◦ Teleflex Incorporated (US)
-◦ Becton, Dickinson and Company (BD) (US)
-◦ Nihon Kohden Corporation (Japan)
-◦ Fukuda Denshi Co., Ltd. (Japan)
-◦ Siare Engineering International Group S.r.l. (Italy)
-◦ Airon Corporation (US)
-◦ Breas Medical AB (Sweden)
-◦ Loewenstein Medical GmbH + Co. KG (Germany)
-◦ Beijing Aeonmed Co., Ltd. (China)</t>
+          <t>◦ Sodi Kart (France)
+◦ Kart Republic (Italy)
+◦ Praga Karts (Czech Republic)
+◦ RS Kart (USA)
+◦ Arrow Karts (Australia)
+◦ Alfano (Italy)
+◦ Righetti Ridolfi (Italy)
+◦ Rotax (Austria)
+◦ OTK Kart Group (Italy)
+◦ RMS Karts (USA)
+◦ Aqua Kart (Germany)
+◦ PDB Karts (Australia)
+◦ SH Karting (USA)
+◦ KZ Karts (France)
+◦ FA Kart (Italy)
+◦ Birel ART Racing (Italy)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>By Product Type (Intensive Care Ventilators, Portable Ventilators, Neonatal Ventilators), By Modality (Non-Invasive Ventilation, Invasive Ventilation), By Ventilator Type (Adult Ventilators, Neonatal Ventilators, Pediatric Ventilators), By Mode (Combined-Mode Ventilation, Volume-Mode Ventilation, Pressure-Mode Ventilator, Other), By End User (Hospitals, Specialty Clinics, Long Term Care Centers, Rehabilitation Centers, Homecare Settings, Others)</t>
+          <t>By Propulsion Type (Gasoline, Electric, Others), By Seating Capacity (Single Seater, Double Seater), By Track (Indoor, Outdoor), By Application (Rental, Racing)</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>153.4</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>160.46</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>229.94</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -883,54 +848,54 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Europe Electric Scooter Market Size, Share, and Growth Analysis, By Vehicle Type (E-Kick Scooters &amp; Bikes, Electric Mopeds), By Power (Less than 3.6 Kw, 3.6 Kw to 7.2 Kw), By Technology, By Motor, By Charging, By Country- Industry Forecast 2025-2032</t>
+          <t>Bluetooth Speaker Market Size, Share, and Growth Analysis, By Type (Smart Bluetooth Speakers, Conventional Bluetooth Speakers), By Portability (Portable, Fixed), By Price, By Distribution Channel, By Region - Industry Forecast 2025-2032</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SQMIR25C2121</t>
+          <t>SQMIG25E2105</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.skyquestt.com/report/europe-electric-scooter-market</t>
+          <t>https://www.skyquestt.com/report/bluetooth-speaker-market</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>223</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Europe Electric Scooter Market size was valued at USD 18.2 billion in 2023 and is poised to grow from USD 22.75 billion in 2024 to USD 135.6 billion by 2032, growing at a CAGR of 25.0% during the forecast period (2025-2032).
-The electric scooter market, encompassing various models like kick scooters, electric motorbikes, and mopeds, is witnessing robust growth driven by an increased demand for sustainable transportation solutions. These scooters, characterized by their ease of use, are popular for both private and public transit, shared mobility, and industrial applications. Factors such as rising use in ride-sharing services across Europe, stringent pollution regulations, and the push towards electric mobility in response to environmental concerns further bolster market acceptance. Additionally, the proliferation of service providers and smartphone apps facilitating vehicle reservations and parking solutions enhances user convenience. Technological advancements continue to foster innovative solutions, significantly supporting the expansion of the electric scooter market within Europe.
-Top-down and bottom-up approaches were used to estimate and validate the size of the Europe Electric Scooter market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
-Europe Electric Scooter Market Segments Analysis
-Europe Electric Scooter Market is segmented by Vehicle Type, Power, Technology, Motor, Charging, End User and region. Based on Vehicle Type, the market is segmented into E-Kick Scooters &amp; Bikes, Electric Mopeds and Electric Motorcycles. Based on Power, the market is segmented into Less than 3 Kw, 4 Kw to 20 Kw and 21 Kw to 100 Kw. Based on Technology, the market is segmented into Sealed Lead Acid Battery, Lithium-ion Battery and Lithium-ion Polymer Battery. Based on Motor, the market is segmented into Hub Motors and Mid-drive Motors. Based on Charging, the market is segmented into Connector Charging and Wireless Charging. Based on End User, the market is segmented into Government Institutions, Academic Institutes/Universities, Business Organizations, Micromobility Service Providers, Individuals and Other End Users. Based on Country, the market is segmented into Germany, Spain, France, UK, Italy, Rest of Europe.
-Driver of the Europe Electric Scooter Market
-The European electric scooter market is experiencing significant growth, largely due to the rise of e-commerce platforms. This shift towards online shopping has made it more convenient for consumers to purchase electric bikes and scooters, while also providing sellers with the opportunity to reach a broader audience. Online marketplaces offer an extensive range of brands, allowing consumers to explore various options that best meet their needs. As both consumers and businesses capitalize on the efficiency and accessibility of these digital portals, this trend is driving further expansion and innovation within the electric scooter market in Europe.
-Restraints in the Europe Electric Scooter Market
-The Europe Electric Scooter market is currently facing significant challenges due to financial constraints affecting consumers. Many individuals are experiencing job losses and reduced incomes, leading them to cut back on discretionary spending, including non-essential items like electric scooters. The impact of the COVID-19 pandemic has severely disrupted various economic sectors, particularly urban transportation and the automotive industry. As a result of government restrictions, major manufacturers were compelled to halt operations or function at limited capacity, further exacerbating the situation. This financial strain on consumers ultimately hinders the growth potential of the electric scooter market in Europe.
-Market Trends of the Europe Electric Scooter Market
-The European electric scooter market is experiencing a significant upward trend driven by the rising adoption of electric motorcycles and e-bikes for short-distance travel. The proliferation of electric scooters in ride-sharing services is enhancing urban mobility solutions, while stringent emission regulations are further incentivizing consumers to switch to eco-friendly alternatives. Additionally, increasing health consciousness among millennials is propelling demand for sustainable transport options, emphasizing active lifestyles. Combined with supportive government policies promoting green initiatives and infrastructure development, these factors are collectively creating a robust market environment poised for substantial growth in the coming years.</t>
+          <t>Global Bluetooth Speaker Market size was valued at USD 16.7 billion in 2023 and is poised to grow from USD 19.32 billion in 2024 to USD 62.05 billion by 2032, growing at a CAGR of 15.7% during the forecast period (2025-2032).
+The Bluetooth speaker market is experiencing robust growth, fueled by the global shift towards wireless technology, which enhances convenience by eliminating cords. Increasing online streaming, the integration of voice assistants within smart homes, and the widespread adoption of technology are driving demand for these devices. Upcoming launches of innovative speakers featuring advanced Bluetooth capabilities will further bolster market expansion. Moreover, the growing trend of outdoor activities necessitating portable music solutions presents new opportunities for vendors in this space. The rising preference for smart speakers in residential and commercial settings, alongside consumer demand for extended battery life, rapid charging, smart connectivity, and superior audio quality, indicates a promising outlook for Bluetooth speaker sales in the future.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Bluetooth Speaker market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Bluetooth Speaker Market Segments Analysis
+Global Bluetooth Speaker Market is segmented by Type, Portability, Price, Distribution Channel and region. Based on Type, the market is segmented into Smart Bluetooth Speakers and Conventional Bluetooth Speakers. Based on Portability, the market is segmented into Portable and Fixed. Based on Price, the market is segmented into Low, Medium and High. Based on Distribution Channel, the market is segmented into Specialty Stores, Supermarkets and Hypermarkets, Departmental Stores, Online and Others. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Bluetooth Speaker Market
+The widespread adoption of smartphones and internet connectivity globally has significantly contributed to the rising trend of online music streaming. This surge in digital music consumption is expected to drive an increase in Bluetooth speaker sales in the upcoming years. As consumers seek portability and improved audio experiences, the demand for Bluetooth speakers will likely rise, enabling users to enjoy high-quality music anytime and anywhere. Consequently, the combination of enhanced mobile technology and the convenience of streaming services will continue to fuel the growth of the Bluetooth speaker market, making it a prominent sector in the audio equipment industry.
+Restraints in the Global Bluetooth Speaker Market
+The global Bluetooth speaker market is facing significant challenges due to the widespread availability of various inexpensive wired speakers. These low-cost alternatives are considerably hindering the sales of Bluetooth speakers, as consumers often opt for more affordable options that fulfill their audio needs. The competitive pricing of these wired speakers has a notable impact on purchasing decisions, effectively undermining the appeal of Bluetooth technology. Consequently, this market restraint poses a barrier to growth for Bluetooth speaker manufacturers, as they must contend with the allure of budget-friendly substitutes that dominate the sound industry globally.
+Market Trends of the Global Bluetooth Speaker Market
+The Global Bluetooth Speaker market is witnessing a significant trend driven by the integration of smart assistants like Alexa, Google Assistant, and Siri. As consumers increasingly embrace smart home technologies, there is a mounting demand for Bluetooth speakers that offer seamless connectivity and compatibility with a wide range of devices. This trend not only enhances user convenience but also expands the functional capabilities of speakers, allowing users to control their smart homes effortlessly. Manufacturers are responding by innovating and differentiating their products with enhanced smart features, ultimately broadening the appeal of Bluetooth speakers across diverse consumer segments.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -945,7 +910,7 @@
 o Market Size Estimation
 o Market Assumptions &amp; Limitations
 • Executive Summary
-o Market Outlook
+o Global Market Outlook
 o Supply &amp; Demand Trend Analysis
 o Segmental Opportunity Analysis
 • Market Dynamics &amp; Outlook
@@ -970,45 +935,53 @@
 o Macro-Economic Indicators
 o Value Chain Analysis
 o Pricing Analysis
-• Europe Electric Scooter Market Size by Vehicle Type &amp; CAGR (2025-2032)
-o Market Overview
-o E-Kick Scooters &amp; Bikes
-o Electric Mopeds
-o Electric Motorcycles
-• Europe Electric Scooter Market Size by Power &amp; CAGR (2025-2032)
-o Market Overview
-o Less than 3 Kw
-o 4 Kw to 20 Kw
-o 21 Kw to 100 Kw
-• Europe Electric Scooter Market Size by Technology &amp; CAGR (2025-2032)
-o Market Overview
-o Sealed Lead Acid Battery
-o Lithium-ion Battery
-o Lithium-ion Polymer Battery
-• Europe Electric Scooter Market Size by Motor &amp; CAGR (2025-2032)
-o Market Overview
-o Hub Motors
-o Mid-drive Motors
-• Europe Electric Scooter Market Size by Charging &amp; CAGR (2025-2032)
-o Market Overview
-o Connector Charging
-o Wireless Charging
-• Europe Electric Scooter Market Size by End User &amp; CAGR (2025-2032)
-o Market Overview
-o Government Institutions
-o Academic Institutes/Universities
-o Business Organizations
-o Micromobility Service Providers
-o Individuals
-o Other End Users
-• Europe Electric Scooter Market Size &amp; CAGR (2025-2032)
-o Europe (Vehicle Type, Power, Technology, Motor, Charging, End User)
+o Regulatory Landscape
+o Case Studies
+o Technology Analysis
+• Global Bluetooth Speaker Market Size by Type &amp; CAGR (2025-2032)
+o Market Overview
+o Smart Bluetooth Speakers
+o Conventional Bluetooth Speakers
+• Global Bluetooth Speaker Market Size by Portability &amp; CAGR (2025-2032)
+o Market Overview
+o Portable
+o Fixed
+• Global Bluetooth Speaker Market Size by Price &amp; CAGR (2025-2032)
+o Market Overview
+o Low
+o Medium
+o High
+• Global Bluetooth Speaker Market Size by Distribution Channel &amp; CAGR (2025-2032)
+o Market Overview
+o Specialty Stores
+o Supermarkets and Hypermarkets
+o Departmental Stores
+o Online
+o Others
+• Global Bluetooth Speaker Market Size &amp; CAGR (2025-2032)
+o North America (Type, Portability, Price, Distribution Channel)
+ US
+ Canada
+o Europe (Type, Portability, Price, Distribution Channel)
  Germany
  Spain
  France
  UK
  Italy
  Rest of Europe
+o Asia Pacific (Type, Portability, Price, Distribution Channel)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Type, Portability, Price, Distribution Channel)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Type, Portability, Price, Distribution Channel)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
 • Competitive Intelligence
 o Top 5 Player Comparison
 o Market Positioning of Key Players, 2024
@@ -1021,97 +994,102 @@
  Company's Segmental Share Analysis
  Revenue Y-O-Y Comparison (2022-2024)
 • Key Company Profiles
-o Voi Technology (Sweden)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Tier Mobility (Germany)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Lime (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Dott (Netherlands)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Bird (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Wind Mobility (Germany)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Bolt Technology OÜ (Estonia)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Cooltra (Spain)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Yego Urban Mobility (Spain)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Circ (Germany)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Emmy Sharing (Germany)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o COUP (Germany)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o unu (Germany)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o NIU Technologies (China)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Segway-Ninebot (China)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Felyx (Netherlands)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Cityscoot (France)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Hive (Spain)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Taxify (Estonia)
+o Bose Corporation (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Sony Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o JBL (Harman International) (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Ultimate Ears (Logitech) (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Bang &amp; Olufsen (Denmark)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Sennheiser Electronics (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Anker Innovations (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Marshall Amplification (UK)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Samsung Electronics (South Korea)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Sonos Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Xiaomi Corporation (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Apple Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o LG Electronics (South Korea)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Creative Technology Ltd. (Singapore)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Harman Kardon (Harman International) (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Edifier International Limited (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Pioneer Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Beats by Dre (Apple) (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o UE (Ultimate Ears) (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Klipsch Audio Technologies (USA)
  Company Overview
  Business Segment Overview
  Financial Updates
@@ -1146,50 +1124,51 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>◦ Voi Technology (Sweden)
-◦ Tier Mobility (Germany)
-◦ Lime (US)
-◦ Dott (Netherlands)
-◦ Bird (US)
-◦ Wind Mobility (Germany)
-◦ Bolt Technology OÜ (Estonia)
-◦ Cooltra (Spain)
-◦ Yego Urban Mobility (Spain)
-◦ Circ (Germany)
-◦ Emmy Sharing (Germany)
-◦ COUP (Germany)
-◦ Unu (Germany)
-◦ NIU Technologies (China)
-◦ Segway-Ninebot (China)
-◦ Felyx (Netherlands)
-◦ Cityscoot (France)
-◦ Hive (Spain)
-◦ Taxify (Estonia)</t>
+          <t>◦ Bose Corporation (USA)
+◦ Sony Corporation (Japan)
+◦ JBL (Harman International) (USA)
+◦ Ultimate Ears (Logitech) (USA)
+◦ Bang &amp; Olufsen (Denmark)
+◦ Sennheiser Electronics (Germany)
+◦ Anker Innovations (China)
+◦ Marshall Amplification (UK)
+◦ Samsung Electronics (South Korea)
+◦ Sonos Inc. (USA)
+◦ Xiaomi Corporation (China)
+◦ Apple Inc. (USA)
+◦ LG Electronics (South Korea)
+◦ Creative Technology Ltd. (Singapore)
+◦ Harman Kardon (Harman International) (USA)
+◦ Edifier International Limited (China)
+◦ Pioneer Corporation (Japan)
+◦ Beats by Dre (Apple) (USA)
+◦ UE (Ultimate Ears) (USA)
+◦ Klipsch Audio Technologies (USA)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>By Vehicle Type (E-Kick Scooters &amp; Bikes, Electric Mopeds), By Power (Less than 3 Kw, 4 Kw to 20 Kw, 21 Kw to 100 Kw), By Technology (Sealed Lead Acid Battery, Lithium-ion Battery, Lithium-ion Polymer Battery), By Motor (Hub Motors, Mid-drive Motors), By Charging (Connector Charging, Wireless Charging), By End User (Government Institutions, Academic Institutes/Universities, Business Organizations, Micromobility Service Providers, Individuals, Other End Users)</t>
+          <t>By Type (Smart Bluetooth Speakers, Conventional Bluetooth Speakers), By Portability (Portable, Fixed), By Price (Low, Medium, High), By Distribution Channel (Specialty Stores, Supermarkets and Hypermarkets, Departmental Stores, Online, Others)</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>19.32</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>135.6</t>
+          <t>62.05</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1201,54 +1180,54 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>North America Electric Scooter Market Size, Share, and Growth Analysis, By Vehicle Type (E-Kick Scooters &amp; Bikes, Electric Mopeds), By Power (Less than 3 Kw, 4 Kw to 20 Kw), By Technology, By Motor, By Country- Industry Forecast 2025-2032</t>
+          <t>Patient Infotainment Terminal Market Size, Share, and Growth Analysis, By Size (Small Size, Medium Size), By Application (Medical Treatment, Home Care Service), By End Users, By Region - Industry Forecast 2025-2032</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SQMIR25C2131</t>
+          <t>SQMIG35G2266</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.skyquestt.com/report/north-america-electric-scooter-market</t>
+          <t>https://www.skyquestt.com/report/patient-infotainment-terminal-market</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>219</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>North America Electric Scooter Market size was valued at USD 800 million in 2023 and is poised to grow from USD 950 million in 2024 to USD 3890 million by 2032, growing at a CAGR of 19.2% during the forecast period (2025-2032).
-The market for electric scooters and motorbikes is witnessing significant growth, driven by their suitability for short-distance commuting and logistics applications such as courier and e-commerce deliveries. With ranges under 100 kilometers per charge and lighter, more efficient designs, these vehicles offer enhanced maneuverability in urban settings. The rise of electric scooter-sharing programs, coupled with increasing concerns about greenhouse gas emissions, is boosting demand for micro-mobility solutions. Additionally, the burgeoning availability of smart charging stations further supports market expansion. While the North American transportation sector is the second-largest contributor to carbon emissions, lingering effects of the COVID-19 pandemic and rising unemployment may temper consumer spending on larger purchases, presenting both challenges and opportunities in this evolving landscape.
-Top-down and bottom-up approaches were used to estimate and validate the size of the North America Electric Scooter market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
-North America Electric Scooter Market Segments Analysis
-North America Electric Scooter Market is segmented by Vehicle Type, Power, Technology, Motor, Charging, End User and region. Based on Vehicle Type, the market is segmented into E-Kick Scooters &amp; Bikes, Electric Mopeds and Electric Motorcycles. Based on Power, the market is segmented into Less than 3 Kw, 4 Kw to 20 Kw and 21 Kw to 100 Kw. Based on Technology, the market is segmented into Sealed Lead Acid Battery, Lithium-ion Battery and Lithium-ion Polymer Battery. Based on Motor, the market is segmented into Hub Motors and Mid-drive Motors. Based on Charging, the market is segmented into Connector Charging and Wireless Charging. Based on End User, the market is segmented into Government Institutions, Academic Institutes/Universities, Business Organizations, Micromobility Service Providers, Individuals and Other End Users. Based on Country, the market is segmented into US, and Canada.
-Driver of the North America Electric Scooter Market
-The North America Electric Scooter market is poised for significant growth as awareness of vehicle emissions and fluctuating gasoline prices rise. An increasing number of young adults are shifting their preferences towards eco-friendly transportation alternatives, driving up the demand for electric scooters across the United States and Canada. This trend reflects a broader societal move towards sustainable mobility solutions, creating a lucrative opportunity for manufacturers and service providers in the electric scooter sector. As consumers prioritize low-emission options, the market is likely to benefit from this change in attitudes and preferences, leading to greater adoption and expansion in the region.
-Restraints in the North America Electric Scooter Market
-The ongoing COVID-19 pandemic has adversely affected the electric scooter market in North America. The outbreak led to a complete halt in the production of electric two-wheelers, resulting in significant disruptions in the supply chain. This interruption in manufacturing processes has further contributed to a decline in sales, highlighting how the pandemic's repercussions have hindered the growth of the electric scooter segment. The challenges faced by manufacturers and retailers alike during this period have created substantial obstacles, impacting the overall market dynamics and restricting the progress anticipated in the electric scooter industry.
-Market Trends of the North America Electric Scooter Market
-The North America electric scooter market is witnessing a robust upward trend, bolstered by a post-COVID-19 surge in e-scooter usage. Average journey distances have soared by 26%, with cities like Detroit reporting remarkable increases of up to 60% in rides. This growth is indicative of a shifting urban mobility landscape, where consumers increasingly favor sustainable and convenient transportation options. The rising emphasis on eco-friendly alternatives, coupled with supportive regulations and urban infrastructure development, is further propelling the e-scooter market. As cities embrace micro-mobility solutions, the North American electric scooter market is poised for continued expansion and innovation in the coming years.</t>
+          <t>Global Patient Infotainment Terminal Market size was valued at USD 677.5 million in 2023 and is poised to grow from USD 709.34 million in 2024 to USD 1024.31 million by 2032, growing at a CAGR of 4.7% during the forecast period (2025-2032).
+The global patient infotainment terminal market is witnessing significant growth as healthcare facilities prioritize patient experience and outcomes. These interactive bedside systems offer patients entertainment, communication tools, health information, and education, enhancing engagement and reducing anxiety during their healthcare journey. A key market driver is the increasing emphasis on patient-centered care, with healthcare providers investing in technologies that boost comfort and satisfaction. Furthermore, the COVID-19 pandemic has accelerated the adoption of these terminals, facilitating remote monitoring and telehealth, thereby minimizing physical contact. Additionally, the rising aging population and prevalence of chronic diseases have amplified demand in long-term care facilities, where infotainment terminals improve residents' quality of life and streamline staff operations.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Patient Infotainment Terminal market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Patient Infotainment Terminal Market Segments Analysis
+Global Patient Infotainment Terminal Market is segmented by Size, Application, End Users and region. Based on Size, the market is segmented into Small Size, Medium Size and Large Size. Based on Application, the market is segmented into Medical Treatment, Home Care Service, Community Health and Others. Based on End Users, the market is segmented into Hospitals and Clinics, Ambulatory Surgical Centers, Home Care Settings and Others. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Patient Infotainment Terminal Market
+The Global Patient Infotainment Terminal market is significantly driven by the growing emphasis among healthcare providers on patient-centered care, which aims to elevate the overall experience of patients during their hospital stays. By incorporating infotainment terminals, healthcare facilities can offer a variety of services that encompass entertainment, communication, and educational resources for patients. These capabilities not only enhance patient satisfaction but also promote improved health outcomes, thereby encouraging the widespread adoption of such terminals within medical settings. As a result, the demand for patient infotainment terminals in the healthcare sector continues to rise, reflecting their vital role in modern patient care.
+Restraints in the Global Patient Infotainment Terminal Market
+One of the primary challenges facing the Global Patient Infotainment Terminal market is the substantial initial investment required for implementation in healthcare settings. This encompasses various expenses such as purchasing hardware, software development, installation, and the costs associated with ongoing maintenance and support. For smaller healthcare organizations, particularly those operating under tighter budgets, these financial burdens can be difficult to rationalize and may deter them from adopting this technology. As a result, the significant costs associated with patient infotainment terminals can serve as a considerable barrier to widespread implementation and usage in the healthcare sector.
+Market Trends of the Global Patient Infotainment Terminal Market
+The Global Patient Infotainment Terminal market is poised for significant growth, driven by the rising demand for patient-centric healthcare solutions. As the industry emphasizes enhancing patient experiences, infotainment terminals are becoming essential tools in hospitals and healthcare facilities. These terminals not only provide entertainment options but also serve as platforms for education and communication, empowering patients with internet access, on-demand video content, and vital health information. This shift towards prioritizing patient engagement and satisfaction is expected to propel the adoption of advanced, user-friendly infotainment systems, aligning with the broader healthcare trend of personalized care and improved patient outcomes.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1263,7 +1242,7 @@
 o Market Size Estimation
 o Market Assumptions &amp; Limitations
 • Executive Summary
-o Market Outlook
+o Global Market Outlook
 o Supply &amp; Demand Trend Analysis
 o Segmental Opportunity Analysis
 • Market Dynamics &amp; Outlook
@@ -1288,42 +1267,50 @@
 o Macro-Economic Indicators
 o Value Chain Analysis
 o Pricing Analysis
-• North America Electric Scooter Market Size by Vehicle Type &amp; CAGR (2025-2032)
-o Market Overview
-o E-Kick Scooters &amp; Bikes
-o Electric Mopeds
-• North America Electric Scooter Market Size by Power &amp; CAGR (2025-2032)
-o Market Overview
-o Less than 3 Kw
-o 4 Kw to 20 Kw
-o 21 Kw to 100 Kw
-• North America Electric Scooter Market Size by Technology &amp; CAGR (2025-2032)
-o Market Overview
-o Sealed Lead Acid Battery
-o Lithium-ion Battery
-o Lithium-ion Polymer Battery
-• North America Electric Scooter Market Size by Motor &amp; CAGR (2025-2032)
-o Market Overview
-o Hub Motors
- Gearless Hub Motors
- Geared Hub Motors
-o Mid-drive Motors
-• North America Electric Scooter Market Size by Charging &amp; CAGR (2025-2032)
-o Market Overview
-o Connector Charging
-o Wireless Charging
-• North America Electric Scooter Market Size by End User &amp; CAGR (2025-2032)
-o Market Overview
-o Government Institutions
-o Academic Institutes/Universities
-o Business Organizations
-o Micromobility Service Providers
-o Individuals
-o Other End Users
-• North America Electric Scooter Market Size &amp; CAGR (2025-2032)
-o North America (Vehicle Type, Power, Technology, Motor, Charging, End User)
+o Regulatory Landscape
+o Case Studies
+o Technology Analysis
+• Global Patient Infotainment Terminal Market Size by Size &amp; CAGR (2025-2032)
+o Market Overview
+o Small Size
+o Medium Size
+o Large Size
+• Global Patient Infotainment Terminal Market Size by Application &amp; CAGR (2025-2032)
+o Market Overview
+o Medical Treatment
+o Home Care Service
+o Community Health
+o Others
+• Global Patient Infotainment Terminal Market Size by End Users &amp; CAGR (2025-2032)
+o Market Overview
+o Hospitals and Clinics
+o Ambulatory Surgical Centers
+o Home Care Settings
+o Others
+• Global Patient Infotainment Terminal Market Size &amp; CAGR (2025-2032)
+o North America (Size, Application, End Users)
  US
  Canada
+o Europe (Size, Application, End Users)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Size, Application, End Users)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Size, Application, End Users)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Size, Application, End Users)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
 • Competitive Intelligence
 o Top 5 Player Comparison
 o Market Positioning of Key Players, 2024
@@ -1336,97 +1323,102 @@
  Company's Segmental Share Analysis
  Revenue Y-O-Y Comparison (2022-2024)
 • Key Company Profiles
-o Bird (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Lime (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Spin (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Razor USA (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Gotrax (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Unagi Scooters (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Apollo Scooters (Canada)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Fluidfreeride (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Voro Motors (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Glion Scooters (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Hiboy (China)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Xiaomi (China)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Superpedestrian (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Okai (China)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o INOKIM (Israel)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Dualtron (South Korea)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o EMOVE (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Electric Rider (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o TurboAnt (US)
+o Telemedicine Technologies, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Zynex, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Atheer, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Cerner Corporation (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Getinge Group (Sweden)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Roche Diagnostics (Switzerland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Philips Healthcare (Netherlands)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Siemens Healthineers (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o GE Healthcare (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o HITACHI Medical Systems (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Advantech Co., Ltd. (Taiwan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Sharp Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Vega Technologies (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Intuiface (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o NEC Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Barco NV (Belgium)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Samsung Electronics (South Korea)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Toshiba Medical Systems Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o LG Electronics (South Korea)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Medtronic PLC (Ireland)
  Company Overview
  Business Segment Overview
  Financial Updates
@@ -1438,7 +1430,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1461,55 +1453,7071 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>◦ Bird (US)
-◦ Lime (US)
-◦ Spin (US)
-◦ Razor USA (US)
-◦ Gotrax (US)
-◦ Unagi Scooters (US)
-◦ Apollo Scooters (Canada)
-◦ Fluidfreeride (US)
-◦ Voro Motors (US)
-◦ Glion Scooters (US)
-◦ Hiboy (China)
-◦ Xiaomi (China)
-◦ Superpedestrian (US)
-◦ Okai (China)
-◦ INOKIM (Israel)
-◦ Dualtron (South Korea)
-◦ EMOVE (US)
-◦ Electric Rider (US)
-◦ TurboAnt (US)</t>
+          <t>◦ Telemedicine Technologies, Inc. (USA)
+◦ Zynex, Inc. (USA)
+◦ Atheer, Inc. (USA)
+◦ Cerner Corporation (USA)
+◦ Getinge Group (Sweden)
+◦ Roche Diagnostics (Switzerland)
+◦ Philips Healthcare (Netherlands)
+◦ Siemens Healthineers (Germany)
+◦ GE Healthcare (USA)
+◦ HITACHI Medical Systems (Japan)
+◦ Advantech Co., Ltd. (Taiwan)
+◦ Sharp Corporation (Japan)
+◦ Vega Technologies (USA)
+◦ Intuiface (USA)
+◦ NEC Corporation (Japan)
+◦ Barco NV (Belgium)
+◦ Samsung Electronics (South Korea)
+◦ Toshiba Medical Systems Corporation (Japan)
+◦ LG Electronics (South Korea)
+◦ Medtronic PLC (Ireland)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>By Vehicle Type (E-Kick Scooters &amp; Bikes, Electric Mopeds), By Power (Less than 3 Kw, 4 Kw to 20 Kw, 21 Kw to 100 Kw), By Technology (Sealed Lead Acid Battery, Lithium-ion Battery, Lithium-ion Polymer Battery), By Motor (Hub Motors (Gearless Hub Motors, Geared Hub Motors), Mid-drive Motors), By Charging (Connector Charging, Wireless Charging), By End User (Government Institutions, Academic Institutes/Universities, Business Organizations, Micromobility Service Providers, Individuals, Other End Users)</t>
+          <t>By Size (Small Size, Medium Size, Large Size), By Application (Medical Treatment, Home Care Service, Community Health, Others), By End Users (Hospitals and Clinics, Ambulatory Surgical Centers, Home Care Settings, Others)</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>677.5</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>709.34</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>1024.31</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>USD Million</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Electric Hair Brush Market Size, Share, and Growth Analysis, By Product Type (Flat, Round), By Gender (Female, Male), By Distribution Channel, By End Users, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SQMIG30L2241</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/electric-hair-brush-market</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Global Electric Hair Brush Market size was valued at USD 301.2 million in 2023 and is poised to grow from USD 315.96 million in 2024 to USD 463.27 million by 2032, growing at a CAGR of 4.9% during the forecast period (2025-2032).
+The international electric hairbrush market is experiencing significant growth, fueled by increasing consumer demand for convenient and efficient hair-styling solutions. Technological advancements in hair care appliances have driven this trend, as electric brushes provide quick and effortless styling, appealing particularly to those seeking time-saving grooming options. Features such as adjustable heat settings, ionization technology, and ergonomic designs enhance the attractiveness of these products. Looking ahead, the market is set to continue its upward trajectory, with a focus on innovation and product variety. Anticipated trends in materials, heating elements, and smart technologies promise to transform the market, offering consumers more versatile and personalized hair care solutions. Growing awareness of the benefits of electric brushes and the desire for salon-quality results at home will sustain demand in the coming years.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Electric Hair Brush market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Electric Hair Brush Market Segments Analysis
+Global Electric Hair Brush Market is segmented by Product Type, Gender, Distribution Channel, End Users and region. Based on Product Type, the market is segmented into Flat and Round. Based on Gender, the market is segmented into Female and Male. Based on Distribution Channel, the market is segmented into Supermarkets and Hypermarkets, Beauty Stores, Online Stores and Others. Based on End Users, the market is segmented into Household and Commercial. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Electric Hair Brush Market
+The Global Electric Hair Brush market is significantly propelled by advancements in technology that enhance both design and functionality. Innovations such as smart sensors, temperature regulation, and cutting-edge materials enhance the overall user experience, aligning with the changing preferences of consumers. These improvements not only make the products more appealing but also contribute to the growing adoption of electric hair brushes, effectively driving market expansion. As consumers increasingly seek out tools that offer convenience and efficiency, the incorporation of such advanced features plays a crucial role in satisfying their needs and fostering growth within the industry.
+Restraints in the Global Electric Hair Brush Market
+The global electric hair brush market faces significant challenges due to high competition and price sensitivity among consumers. With a multitude of manufacturers and a wide array of products in the marketplace, aggressive pricing strategies and price wars can adversely affect profit margins for businesses. Additionally, consumers tend to be very price-conscious, creating pressure on manufacturers to offer competitive rates and making it difficult to maintain premium pricing for higher-end products. As a result, navigating these market restraints becomes crucial for companies aiming to succeed and sustain profitability in this dynamic industry.
+Market Trends of the Global Electric Hair Brush Market
+The Global Electric Hair Brush market is witnessing a significant shift towards sustainability as consumers increasingly prioritize eco-friendly options. This trend is characterized by the rising demand for electric hair brushes incorporating energy-efficient technologies and sustainable materials, which not only enhance functionality but also minimize environmental impact. As part of the broader sustainability movement, this consumer behavior is reshaping the market landscape, driving innovation towards eco-conscious designs that align with the values of environmentally aware users. Consequently, manufacturers are compelled to adapt their offerings, fostering a competitive environment focused on delivering effective yet responsible grooming solutions.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Regulatory Landscape
+o Case Studies
+o Technology Analysis
+• Global Electric Hair Brush Market Size by Product Type &amp; CAGR (2025-2032)
+o Market Overview
+o Flat
+o Round
+• Global Electric Hair Brush Market Size by Gender &amp; CAGR (2025-2032)
+o Market Overview
+o Female
+o Male
+• Global Electric Hair Brush Market Size by Distribution Channel &amp; CAGR (2025-2032)
+o Market Overview
+o Supermarkets and Hypermarkets
+o Beauty Stores
+o Online Stores
+o Others
+• Global Electric Hair Brush Market Size by End Users &amp; CAGR (2025-2032)
+o Market Overview
+o Household
+o Commercial
+• Global Electric Hair Brush Market Size &amp; CAGR (2025-2032)
+o North America (Product Type, Gender, Distribution Channel, End Users)
+ US
+ Canada
+o Europe (Product Type, Gender, Distribution Channel, End Users)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Product Type, Gender, Distribution Channel, End Users)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Product Type, Gender, Distribution Channel, End Users)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Product Type, Gender, Distribution Channel, End Users)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Conair Corporation (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Revlon (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Philips (Netherlands)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Braun (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Remington (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Hot Tools Professional (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o BaBylissPRO (France)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Panasonic (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o T3 Micro (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Sundee (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Vega (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o GHD (UK)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Paul Mitchell (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Kiss Products (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Mermade Hair (Australia)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Mizutani Scissors (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o INFINITIPRO by Conair (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o SleekCurl (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Tescom (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Hiar Brush Pro (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>◦ Conair Corporation (USA)
+◦ Revlon (USA)
+◦ Philips (Netherlands)
+◦ Braun (Germany)
+◦ Remington (USA)
+◦ Hot Tools Professional (USA)
+◦ BaBylissPRO (France)
+◦ Panasonic (Japan)
+◦ T3 Micro (USA)
+◦ Sundee (China)
+◦ Vega (India)
+◦ GHD (UK)
+◦ Paul Mitchell (USA)
+◦ Kiss Products (USA)
+◦ Mermade Hair (Australia)
+◦ Mizutani Scissors (Japan)
+◦ INFINITIPRO by Conair (USA)
+◦ SleekCurl (China)
+◦ Tescom (Japan)
+◦ Hiar Brush Pro (USA)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>By Product Type (Flat, Round), By Gender (Female, Male), By Distribution Channel (Supermarkets and Hypermarkets, Beauty Stores, Online Stores, Others), By End Users (Household, Commercial)</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>301.2</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>315.96</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>463.27</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>4.9%</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>USD Million</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bio-Polyamide Market Size, Share, and Growth Analysis, By Product Type (Polyamide 6, Polyamide 66), By Material (Fiber, Engineering plastics), By Applications, By End Users, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SQMIG15E2459</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/bio-polyamide-market</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Global Bio-Polyamide Market size was valued at USD 210.2 million in 2023 and is poised to grow from USD 225.54 million in 2024 to USD 396.31 million by 2032, growing at a CAGR of 7.3% during the forecast period (2025-2032).
+The Global Bio-Polyamide Market is rapidly evolving within the polymers and materials industry, driven by the growing demand for sustainable solutions. Bio-polyamides, made from renewable resources like castor oil, are attracting attention due to their eco-friendliness and versatility across various sectors. Increasing environmental concerns about climate change and plastic pollution are propelling the shift towards greener alternatives to traditional petroleum-based plastics, making bio-polyamides a compelling choice. The automotive industry significantly contributes to market growth, utilizing bio-polyamides for lightweight applications that enhance fuel efficiency. Beyond automotive uses, these materials find applications in textiles, consumer goods, and industrial components, broadening their market reach. Moreover, advancements in production technologies have improved the attributes and processing of bio-polyamides, further boosting their adoption across diverse products.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Bio-Polyamide market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Bio-Polyamide Market Segments Analysis
+Global Bio-Polyamide Market is segmented by Product Type, Material, Applications, End Users and region. Based on Product Type, the market is segmented into Polyamide 6, Polyamide 66, Polyamide 10, Polyamide 11 and Polyamide 12. Based on Material, the market is segmented into Fiber and Engineering plastics. Based on Applications, the market is segmented into Textile, Industrial, Carpet and Staple. Based on End Users, the market is segmented into Automotive, Film &amp; coating, Industrial/Machinery, Electrical &amp; electronics, Consumer goods appliances, Wires &amp; cables and Others. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Bio-Polyamide Market
+The Global Bio-Polyamide market is primarily propelled by increasing environmental awareness and concerns regarding the ecological impact of conventional plastics. As consumers and industries alike seek sustainable alternatives, the demand for bio-based and biodegradable materials like bio-polyamides is rising. Sourced from renewable resources such as castor oil, these materials help in minimizing dependence on fossil fuels while significantly reducing carbon emissions. Furthermore, bio-polyamides possess biodegradable properties, making them a more eco-friendly option for a wide range of applications. This shift towards sustainability signals a transformative change in material usage, enhancing the market potential for bio-polyamides.
+Restraints in the Global Bio-Polyamide Market
+A significant challenge facing the global bio-polyamide market is the high cost of production. The manufacturing processes for bio-based polymers are often more intricate and expensive than those used for traditional petrochemical-based polymers. This disparity in pricing can hinder the competitiveness of bio-polyamides, particularly in markets that are sensitive to cost fluctuations. As a result, manufacturers may struggle to position bio-polyamides as viable alternatives, limiting their adoption in price-conscious sectors and potentially slowing down the overall growth of the market. Addressing these economic barriers will be crucial for enhancing the appeal of bio-polyamides across diverse applications.
+Market Trends of the Global Bio-Polyamide Market
+The global bio-polyamide market is witnessing a significant trend driven by the escalating demand for sustainable materials, as industries increasingly prioritize eco-friendly alternatives. Bio-polyamides, sourced from renewable materials such as castor oil and biowaste, present a viable substitute to traditional petroleum-based polyamides, aligning with global initiatives to combat climate change. Sectors such as automotive, textiles, and consumer goods are actively seeking to integrate these biopolymer solutions to minimize their environmental impact and enhance their sustainability profiles. As regulatory frameworks tighten and consumer awareness rises, the bio-polyamide market is positioned for robust growth, reflecting a broader shift towards environmentally responsible manufacturing practices.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Regulatory Landscape
+o Case Studies
+o Technology Analysis
+• Global Bio-Polyamide Market Size by Product Type &amp; CAGR (2025-2032)
+o Market Overview
+o Polyamide 6
+o Polyamide 66
+o Polyamide 10
+o Polyamide 11
+o Polyamide 12
+• Global Bio-Polyamide Market Size by Material &amp; CAGR (2025-2032)
+o Market Overview
+o Fiber
+o Engineering plastics
+• Global Bio-Polyamide Market Size by Applications &amp; CAGR (2025-2032)
+o Market Overview
+o Textile
+o Industrial
+o Carpet
+o Staple
+• Global Bio-Polyamide Market Size by End Users &amp; CAGR (2025-2032)
+o Market Overview
+o Automotive
+o Film &amp; coating
+o Industrial/Machinery
+o Electrical &amp; electronics
+o Consumer goods appliances
+o Wires &amp; cables
+o Others
+• Global Bio-Polyamide Market Size &amp; CAGR (2025-2032)
+o North America (Product Type, Material, Applications, End Users)
+ US
+ Canada
+o Europe (Product Type, Material, Applications, End Users)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Product Type, Material, Applications, End Users)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Product Type, Material, Applications, End Users)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Product Type, Material, Applications, End Users)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Arkema S.A. (France)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o DSM Engineering Materials (Netherlands)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o BASF SE (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Evonik Industries AG (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Solvay S.A. (Belgium)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Radici Group (Italy)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Rhodia (France)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Toray Industries Inc. (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o SABIC (Saudi Arabia)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o LANXESS AG (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o EMS-CHEMIE HOLDING AG (Switzerland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o INVISTA (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o DuPont de Nemours, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Asahi Kasei Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Domo Chemicals (Belgium)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o UBE Industries Ltd. (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Zhejiang Huajin Yike New Material Co., Ltd. (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Royal DSM (Netherlands)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Mitsui Chemicals, Inc. (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Radici Partecipazioni SpA (Italy)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>◦ Arkema S.A. (France)
+◦ DSM Engineering Materials (Netherlands)
+◦ BASF SE (Germany)
+◦ Evonik Industries AG (Germany)
+◦ Solvay S.A. (Belgium)
+◦ Radici Group (Italy)
+◦ Rhodia (France)
+◦ Toray Industries Inc. (Japan)
+◦ SABIC (Saudi Arabia)
+◦ LANXESS AG (Germany)
+◦ EMS-CHEMIE HOLDING AG (Switzerland)
+◦ INVISTA (USA)
+◦ DuPont de Nemours, Inc. (USA)
+◦ Asahi Kasei Corporation (Japan)
+◦ Domo Chemicals (Belgium)
+◦ UBE Industries Ltd. (Japan)
+◦ Zhejiang Huajin Yike New Material Co., Ltd. (China)
+◦ Royal DSM (Netherlands)
+◦ Mitsui Chemicals, Inc. (Japan)
+◦ Radici Partecipazioni SpA (Italy)</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>By Product Type (Polyamide 6, Polyamide 66, Polyamide 10, Polyamide 11, Polyamide 12), By Material (Fiber, Engineering plastics), By Applications (Textile, Industrial, Carpet, Staple), By End Users (Automotive, Film &amp; coating, Industrial/Machinery, Electrical &amp; electronics, Consumer goods appliances, Wires &amp; cables, Others)</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>210.2</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>225.54</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>396.31</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>7.3%</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>USD Million</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Heated Jacket Market Size, Share, and Growth Analysis, By Power Type (Below 5 Volt, 5 – 7 Volt), By Size (Small, Medium), By Applications, By End Users, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SQMIG25M2053</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/heated-jacket-market</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Global Heated Jacket Market size was valued at USD 201.1 million in 2023 and is poised to grow from USD 216.18 million in 2024 to USD 385.56 million by 2032, growing at a CAGR of 7.5% during the forecast period (2025-2032).
+The global heated jacket market has seen significant growth recently, fueled by technological advancements, shifting climate trends, and rising consumer demand for comfortable outdoor apparel. Featuring integrated heating elements, these jackets provide warmth in cold conditions, catering to outdoor enthusiasts, cold-environment workers, and winter sports participants. The growing awareness of the benefits of heated clothing has driven consumers towards jackets that offer adjustable temperatures, efficient battery power, and lightweight designs, expanding their usage beyond traditional winterwear to activities like skiing, hiking, hunting, and motorcycling. Improved battery technology has enhanced longevity and efficiency, while advanced heating systems ensure safety and reliability. Moreover, the increase in extreme weather events and interest in outdoor recreation further bolsters the heated jacket market as a practical solution for warmth.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Heated Jacket market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Heated Jacket Market Segments Analysis
+Global Heated Jacket Market is segmented by Power Type, Size, Applications, End Users and region. Based on Power Type, the market is segmented into Below 5 Volt, 5 – 7 Volt and 7 – 20 Volt. Based on Size, the market is segmented into Small, Medium, Large, XL(Excel) and 2XL (Double Excel). Based on Applications, the market is segmented into Leisure, Industrial/Construction, DIY and Others. Based on End Users, the market is segmented into Men, Women and Kids. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Heated Jacket Market
+The main catalyst propelling the heated jacket market is the growing demand for warmth and comfort during chilly weather. These jackets have gained popularity among various groups, including outdoor adventurers, individuals working in frigid conditions, and residents of areas characterized by severe winters. Additionally, as climate change leads to increasingly unpredictable and extreme weather patterns, the requirement for heated clothing, particularly jackets, is anticipated to rise. This trend signifies a shift towards seeking innovative solutions to combat cold temperatures, further boosting the market's growth trajectory as consumers prioritize both functionality and comfort.
+Restraints in the Global Heated Jacket Market
+The Global Heated Jacket market faces a notable restraint due to the higher cost associated with these garments compared to traditional jackets. This price disparity arises from the incorporation of heating elements, batteries, and advanced technologies, which significantly increases production expenses. Consequently, the elevated price point can serve as a considerable barrier for consumers who may hesitate to invest in heated jackets, despite the potential long-term advantages of enhanced warmth in cold environments. As a result, this initial financial commitment can dissuade potential buyers, ultimately hindering the overall growth and expansion of the market.
+Market Trends of the Global Heated Jacket Market
+The Global Heated Jacket market is experiencing a notable upward trend fueled by the increasing enthusiasm for outdoor and winter activities. As more individuals engage in pursuits such as winter sports, hiking, and camping, the demand for heated apparel that provides both warmth and comfort during cold weather is skyrocketing. This trend is particularly pronounced in regions characterized by harsh winters, including North America and Europe, where consumers are actively seeking innovative clothing solutions to enhance their outdoor experiences. Consequently, manufacturers are responding with advanced thermal technologies and stylish designs, positioning heated jackets as essential gear for outdoor enthusiasts.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Regulatory Landscape
+o Case Studies
+o Technology Analysis
+• Global Heated Jacket Market Size by Power Type &amp; CAGR (2025-2032)
+o Market Overview
+o Below 5 Volt
+o 5 – 7 Volt
+o 7 – 20 Volt
+• Global Heated Jacket Market Size by Size &amp; CAGR (2025-2032)
+o Market Overview
+o Small
+o Medium
+o Large
+o XL(Excel)
+o 2XL (Double Excel)
+• Global Heated Jacket Market Size by Applications &amp; CAGR (2025-2032)
+o Market Overview
+o Leisure
+o Industrial/Construction
+o DIY
+o Others
+• Global Heated Jacket Market Size by End Users &amp; CAGR (2025-2032)
+o Market Overview
+o Men
+o Women
+o Kids
+• Global Heated Jacket Market Size &amp; CAGR (2025-2032)
+o North America (Power Type, Size, Applications, End Users)
+ US
+ Canada
+o Europe (Power Type, Size, Applications, End Users)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Power Type, Size, Applications, End Users)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Power Type, Size, Applications, End Users)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Power Type, Size, Applications, End Users)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Milwaukee Tool (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Columbia Sportswear (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o The North Face (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o ORORO Heated Apparel (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o DEWALT (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Bosch (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Makita Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Ravean (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Gerbing (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Volt Resistance (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o ActionHeat (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o PROsmart (Canada)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o TIDEWE (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Conqueco (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Outcool (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Chaval Outdoor (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Regatta (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Hestra (Sweden)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o 8K Flexwarm (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Mobile Warming (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>◦ Milwaukee Tool (United States)
+◦ Columbia Sportswear (United States)
+◦ The North Face (United States)
+◦ ORORO Heated Apparel (United States)
+◦ DEWALT (United States)
+◦ Bosch (Germany)
+◦ Makita Corporation (Japan)
+◦ Ravean (United States)
+◦ Gerbing (United States)
+◦ Volt Resistance (United States)
+◦ ActionHeat (United States)
+◦ PROsmart (Canada)
+◦ TIDEWE (United States)
+◦ Conqueco (China)
+◦ Outcool (China)
+◦ Chaval Outdoor (United States)
+◦ Regatta (United Kingdom)
+◦ Hestra (Sweden)
+◦ 8K Flexwarm (United Kingdom)
+◦ Mobile Warming (United States)</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>By Power Type (Below 5 Volt, 5 – 7 Volt, 7 – 20 Volt), By Size (Small, Medium, Large, XL(Excel), 2XL (Double Excel)), By Applications (Leisure, Industrial/Construction, DIY, Others), By End Users (Men, Women, Kids)</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>201.1</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>216.18</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>385.56</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>USD Million</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Peripheral Nerve Injuries Market Size, Share, and Growth Analysis, By Product Type (Nerve Conduit, Nerve Protector), By Surgery (Direct nerve repair, Nerve Grafting), By Applications, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SQMIG35I2312</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/peripheral-nerve-injuries-market</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Global Peripheral Nerve Injuries Market size was valued at USD 1.55 billion in 2023 and is poised to grow from USD 1.66 billion in 2024 to USD 2.92 billion by 2032, growing at a CAGR of 7.3% during the forecast period (2025-2032).
+The peripheral nerve injuries market is evolving rapidly, fueled by the rising prevalence of trauma-related injuries, technological advances in nerve repair and regeneration, and an aging population. Recent innovations in surgical methodologies and biomaterials have markedly enhanced patient outcomes, contributing to market expansion. Additionally, the emergence of neurostimulation and neuromodulation therapies is broadening treatment alternatives. Collaborative efforts among academic institutions, medical device companies, and research organizations are driving the development of cutting-edge solutions. However, challenges persist, including the high costs associated with advanced treatments and limited reimbursement frameworks. As market players address these hurdles, they also seek to leverage growing demand for effective solutions in peripheral nerve injury management, positioning themselves within this dynamic segment of the healthcare landscape.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Peripheral Nerve Injuries market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Peripheral Nerve Injuries Market Segments Analysis
+Global Peripheral Nerve Injuries Market is segmented by Product Type, Surgery, Applications and region. Based on Product Type, the market is segmented into Nerve Conduit, Nerve Protector, Nerve Connector and Nerve Wraps. Based on Surgery, the market is segmented into Direct nerve repair, Nerve Grafting and Stem Cell Therapy. Based on Applications, the market is segmented into Upper Extremities and Lower Extremities. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Peripheral Nerve Injuries Market
+The global peripheral nerve injuries market is significantly driven by the escalating occurrence of these injuries, which can result from trauma, accidents, sports-related incidents, and chronic ailments like diabetes. As the rates of peripheral nerve injuries continue to rise, there is an increasing need for effective treatment options and therapeutic solutions. This growing demand not only highlights the urgency for advanced medical interventions but also presents opportunities for healthcare providers and companies to innovate and enhance their offerings. As a result, addressing this prevalent issue is crucial for both patient outcomes and market expansion in the field of peripheral nerve injury management.
+Restraints in the Global Peripheral Nerve Injuries Market
+One of the significant constraints in the Global Peripheral Nerve Injuries market is the elevated cost associated with treatment. The expenses incurred for managing peripheral nerve injuries can be considerable, especially when surgeries, rehabilitation, and ongoing care are required. These high treatment costs can create barriers to accessing necessary medical services for certain patients, thereby hindering overall market growth. As many individuals may find it difficult to afford comprehensive treatment options, this financial burden poses a challenge to the expansion and accessibility of care within the market, limiting opportunities for both patients and healthcare providers.
+Market Trends of the Global Peripheral Nerve Injuries Market
+The Global Peripheral Nerve Injuries market is experiencing a notable trend driven by rapid technological advancements in nerve repair and regeneration techniques. Researchers and medical device firms are increasingly focused on developing innovative solutions, such as advanced nerve conduits, neurostimulation devices, and bioengineered materials, which significantly enhance treatment outcomes for nerve injuries. These cutting-edge technologies not only aim to improve nerve regeneration and expedite recovery times but also seek to reduce associated complications, thus fostering a growing demand for more effective and efficient treatment options in clinical practice. The integration of these advancements is set to shape the future landscape of the market positively.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Regulatory Landscape
+o Case Studies
+• Global Peripheral Nerve Injuries Market Size by Product Type &amp; CAGR (2025-2032)
+o Market Overview
+o Nerve Conduit
+o Nerve Protector
+o Nerve Connector
+o Nerve Wraps
+• Global Peripheral Nerve Injuries Market Size by Surgery &amp; CAGR (2025-2032)
+o Market Overview
+o Direct nerve repair
+o Nerve Grafting
+o Stem Cell Therapy
+• Global Peripheral Nerve Injuries Market Size by Applications &amp; CAGR (2025-2032)
+o Market Overview
+o Upper Extremities
+o Lower Extremities
+• Global Peripheral Nerve Injuries Market Size &amp; CAGR (2025-2032)
+o North America (Product Type, Surgery, Applications)
+ US
+ Canada
+o Europe (Product Type, Surgery, Applications)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Product Type, Surgery, Applications)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Product Type, Surgery, Applications)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Product Type, Surgery, Applications)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Axogen Corporation (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Integra LifeSciences Holdings Corporation (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Medtronic plc (Ireland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Stryker Corporation (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Baxter International Inc. (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Polyganics BV (Netherlands)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Smith &amp; Nephew plc (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Boston Scientific Corporation (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Abbott Laboratories (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o NeuroPace, Inc. (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Nuvectra Corporation (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o OrthoPediatrics Corp. (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Zimmer Biomet Holdings, Inc. (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o NeuroMetrix, Inc. (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o MicroPort Scientific Corporation (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Nihon Kohden Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Natus Medical Incorporated (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o LivaNova plc (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Bioventus LLC (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Renerva, LLC (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>◦ Axogen Corporation (United States)
+◦ Integra LifeSciences Holdings Corporation (United States)
+◦ Medtronic plc (Ireland)
+◦ Stryker Corporation (United States)
+◦ Baxter International Inc. (United States)
+◦ Polyganics BV (Netherlands)
+◦ Smith &amp; Nephew plc (United Kingdom)
+◦ Boston Scientific Corporation (United States)
+◦ Abbott Laboratories (United States)
+◦ NeuroPace, Inc. (United States)
+◦ Nuvectra Corporation (United States)
+◦ OrthoPediatrics Corp. (United States)
+◦ Zimmer Biomet Holdings, Inc. (United States)
+◦ NeuroMetrix, Inc. (United States)
+◦ MicroPort Scientific Corporation (China)
+◦ Nihon Kohden Corporation (Japan)
+◦ Natus Medical Incorporated (United States)
+◦ LivaNova plc (United Kingdom)
+◦ Bioventus LLC (United States)
+◦ Renerva, LLC (United States)</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>By Product Type (Nerve Conduit, Nerve Protector, Nerve Connector, Nerve Wraps), By Surgery (Direct nerve repair, Nerve Grafting, Stem Cell Therapy), By Applications (Upper Extremities, Lower Extremities)</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>7.3%</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>USD Billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Wall Bed Market Size, Share, and Growth Analysis, By Product Type (Single Wall Beds, Double Wall Beds), By Operation (Manual, Automatic), By Material, By Size, By Distribution Channel, By End Users, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SQMIG30L2242</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/wall-bed-market</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Global Wall Bed Market size was valued at USD 3.9 billion in 2023 and is poised to grow from USD 4.2 billion in 2024 to USD 7.67 billion by 2032, growing at a CAGR of 7.8% during the forecast period (2025-2032).
+The global Wall Bed market is thriving, driven by urbanization and limited living spaces that elevate the demand for innovative, space-saving furniture solutions. The trend towards multifunctional furnishings in both residential and commercial settings further fuels this market expansion. Manufacturers are focusing on design enhancements, incorporating features such as storage options and user-friendly mechanisms to cater to diverse consumer needs. Sustainability trends also play a significant role, with a rising demand for eco-friendly materials and efficient designs. As the real estate landscape shifts and consumers seek practical solutions for optimizing space, the Wall Bed market is poised for continued growth, reflecting evolving lifestyle preferences and a commitment to functionality.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Wall Bed market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Wall Bed Market Segments Analysis
+Global Wall Bed Market is segmented by Product Type, Operation, Material, Size, Distribution Channel, End Users and region. Based on Product Type, the market is segmented into Single Wall Beds, Double Wall Beds and Others. Based on Operation, the market is segmented into Manual, Automatic and Hybrid. Based on Material, the market is segmented into Metal and Wooden. Based on Size, the market is segmented into King, Queen and Others. Based on Distribution Channel, the market is segmented into Hypermarkets and Supermarkets, Specialty Stores, Online Retail and Others. Based on End Users, the market is segmented into Residential and Commercial. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Wall Bed Market
+The Global Wall Bed market is driven by the growing urbanization and the trend towards compact living spaces, leading to an increased demand for space-saving furniture solutions, with wall beds emerging as a practical and popular option. The rise of remote work and the shift in home office culture further amplify the need for multifunctional furniture, thereby accelerating the acceptance of wall beds. Furthermore, advancements in design that incorporate features like built-in storage and customizable configurations significantly enhance the appeal of wall beds. This convergence of factors is propelling the market forward as consumers seek efficient and versatile living solutions.
+Restraints in the Global Wall Bed Market
+A key constraint facing the global wall bed market is the initial cost associated with these products, particularly models boasting advanced features, which can be prohibitively high for budget-conscious consumers. Furthermore, the perception that wall beds are intricate or difficult to install can deter potential buyers. The variety of alternative options available to consumers, coupled with a limited awareness of the advantages that wall beds offer in specific settings, further hampers market growth and slows down overall penetration rates in this sector. Addressing these issues is crucial for enhancing market accessibility and increasing consumer adoption.
+Market Trends of the Global Wall Bed Market
+The Global Wall Bed market is witnessing significant growth driven by rising consumer awareness and an increasing preference for smart, modular designs that enhance functionality. Innovations such as integrated lighting, USB ports, and automated mechanisms are becoming standard features, attracting tech-savvy consumers seeking convenience. Additionally, sustainability trends are gaining traction, with customers prioritizing eco-friendly materials and responsible production methods in their furniture choices. This dual trend of functionality and sustainability is reshaping the market landscape, leading manufacturers to adopt greener practices while catering to the evolving demands for space-saving, versatile living solutions in urban environments.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Regulatory Landscape
+o Case Studies
+• Global Wall Bed Market Size by Product Type &amp; CAGR (2025-2032)
+o Market Overview
+o Single Wall Beds
+o Double Wall Beds
+o Others
+• Global Wall Bed Market Size by Operation &amp; CAGR (2025-2032)
+o Market Overview
+o Manual
+o Automatic
+o Hybrid
+• Global Wall Bed Market Size by Material &amp; CAGR (2025-2032)
+o Market Overview
+o Metal
+o Wooden
+• Global Wall Bed Market Size by Size &amp; CAGR (2025-2032)
+o Market Overview
+o King
+o Queen
+o Others
+• Global Wall Bed Market Size by Distribution Channel &amp; CAGR (2025-2032)
+o Market Overview
+o Hypermarkets and Supermarkets
+o Specialty Stores
+o Online Retail
+o Others
+• Global Wall Bed Market Size by End Users &amp; CAGR (2025-2032)
+o Market Overview
+o Residential
+o Commercial
+• Global Wall Bed Market Size &amp; CAGR (2025-2032)
+o North America (Product Type, Operation, Material, Size, Distribution Channel, End Users)
+ US
+ Canada
+o Europe (Product Type, Operation, Material, Size, Distribution Channel, End Users)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Product Type, Operation, Material, Size, Distribution Channel, End Users)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Product Type, Operation, Material, Size, Distribution Channel, End Users)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Product Type, Operation, Material, Size, Distribution Channel, End Users)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Flybed (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Wall Bed King (United States and Canada)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Foshan Youpai Home Technology Co., Ltd. (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Malrox Beds (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Murphy Wall-Beds Hardware, Inc. (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Wall Bed Factory (Australia)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Clei (Italy)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Resource Furniture (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Wall Beds Manufacturing (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Murphy Bed USA (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o The Bedder Way Co. (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Expand Furniture (Canada)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Wall Bed Express (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Futon Creations (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Space Saving Furniture (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Wall Bed Systems (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o The Wall Bed Company (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Smart Furniture (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Innovative Wall Beds (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o SpaceSaver Beds (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>◦ Flybed (India)
+◦ Wall Bed King (United States and Canada)
+◦ Foshan Youpai Home Technology Co., Ltd. (China)
+◦ Malrox Beds (India)
+◦ Murphy Wall-Beds Hardware, Inc. (United States)
+◦ Wall Bed Factory (Australia)
+◦ Clei (Italy)
+◦ Resource Furniture (United States)
+◦ Wall Beds Manufacturing (United States)
+◦ Murphy Bed USA (United States)
+◦ The Bedder Way Co. (United States)
+◦ Expand Furniture (Canada)
+◦ Wall Bed Express (United States)
+◦ Futon Creations (United States)
+◦ Space Saving Furniture (United Kingdom)
+◦ Wall Bed Systems (United States)
+◦ The Wall Bed Company (United States)
+◦ Smart Furniture (United States)
+◦ Innovative Wall Beds (United States)
+◦ SpaceSaver Beds (United States)</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>By Product Type (Single Wall Beds, Double Wall Beds, Others), By Operation (Manual, Automatic, Hybrid), By Material (Metal, Wooden), By Size (King, Queen, Others), By Distribution Channel (Hypermarkets and Supermarkets, Specialty Stores, Online Retail, Others), By End Users (Residential, Commercial)</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>7.67</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>7.8%</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>USD Billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Endoscopic Retrograde Cholangiopancreatography Market Size, Share, and Growth Analysis, By Product Type (Endoscopes, Endotherapy Devices), By Procedure (Biliary Sphincterotomy, Biliary Stenting), By End Users, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SQMIG35A2748</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/endoscopic-retrograde-cholangiopancreatography-market</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Global Endoscopic Retrograde Cholangiopancreatography Market size was valued at USD 1.5 billion in 2023 and is poised to grow from USD 1.65 billion in 2024 to USD 3.48 billion by 2032, growing at a CAGR of 9.8% during the forecast period (2025-2032).
+The rising popularity of minimally invasive surgical techniques has led to a significant uptick in the demand for endoscopic retrograde cholangiopancreatography (ERCP) procedures, positioning this sector for robust growth in the coming years. The preference for ERCP is driven by its benefits, such as shorter recovery periods and decreased complication rates compared to traditional surgery. Recent data from the American Cancer Society highlights the urgency for such advancements, as the U.S. anticipates approximately 41,210 new liver cancer cases in 2023. This statistic underlines the increasing necessity for sophisticated diagnostic and therapeutic options, reinforcing the importance of ongoing investments and innovations within the ERCP market.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Endoscopic Retrograde Cholangiopancreatography market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Endoscopic Retrograde Cholangiopancreatography Market Segments Analysis
+Global Endoscopic Retrograde Cholangiopancreatography Market is segmented by Product Type, Procedure, End Users and region. Based on Product Type, the market is segmented into Endoscopes, Endotherapy Devices, Visualization Systems, Energy Devices and Others. Based on Procedure, the market is segmented into Biliary Sphincterotomy, Biliary Stenting, Biliary Dialtation, Pancreatic Sphincterotomy, Pancreatic Duct Stenting and Pancreatic Duct Dilatation. Based on End Users, the market is segmented into Hospitals, Ambulatory Surgery Centers &amp; Clinics and Others. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Endoscopic Retrograde Cholangiopancreatography Market
+The global endoscopic retrograde cholangiopancreatography (ERCP) market is propelled by the increasing demand for advanced diagnostic and therapeutic solutions targeting the pancreas, liver, gallbladder, and bile ducts. ERCP is a sophisticated procedure that combines luminal endoscopy and fluoroscopic imaging, allowing for effective identification and treatment of pancreatobiliary disorders. This technique involves the use of a flexible, illuminated endoscope, which navigates through the digestive tract for direct visualization of critical organs, while simultaneously capturing X-ray images. The ability to provide comprehensive assessments and interventions drives the growth of the ERCP market, catering to the rising needs of healthcare providers worldwide.
+Restraints in the Global Endoscopic Retrograde Cholangiopancreatography Market
+The growth of the Global Endoscopic Retrograde Cholangiopancreatography market is being restrained by stringent regulatory guidelines enforced by governing bodies in various countries, which create obstacles for the introduction of new technologies. Adhering to these regulations necessitates extensive testing and compliance with safety and efficacy standards, resulting in a complicated and time-consuming approval process for novel medical innovations. Despite these regulatory challenges, there are positive developments within the market. Notably, the increase in disposable income, particularly in developing nations, has emerged as a significant driver of market expansion, indicating potential for future growth despite existing constraints.
+Market Trends of the Global Endoscopic Retrograde Cholangiopancreatography Market
+The Global Endoscopic Retrograde Cholangiopancreatography (ERCP) market is set to flourish, driven by innovative strategic initiatives from leading industry players. Notable activities, such as product launches, mergers, and acquisitions, are transforming the landscape. For instance, the April 2022 partnership between Olympus and EndoClot Plus, which introduced the EndoClot PHS, exemplifies the market's focus on enhancing therapeutic endoscopic solutions. This collaboration emphasizes the shift towards nonthermal, nontraumatic techniques for efficient hemostasis in gastrointestinal procedures. As healthcare providers increasingly prioritize advanced and effective treatments, the ERCP market is poised for substantial growth, reflecting a commitment to improving patient outcomes and enhancing procedural safety.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Regulatory Landscape
+o Case Studies
+• Global Endoscopic Retrograde Cholangiopancreatography Market Size by Product Type &amp; CAGR (2025-2032)
+o Market Overview
+o Endoscopes
+o Endotherapy Devices
+ Sphincterotomes
+ Lithotripter
+ Stents
+ Cannulas
+ Forceps
+ Snares
+ Catheters
+ Guiding Wires
+ Balloons
+ Baskets
+o Visualization Systems
+o Energy Devices
+o Others
+• Global Endoscopic Retrograde Cholangiopancreatography Market Size by Procedure &amp; CAGR (2025-2032)
+o Market Overview
+o Biliary Sphincterotomy
+o Biliary Stenting
+o Biliary Dialtation
+o Pancreatic Sphincterotomy
+o Pancreatic Duct Stenting
+o Pancreatic Duct Dilatation
+• Global Endoscopic Retrograde Cholangiopancreatography Market Size by End Users &amp; CAGR (2025-2032)
+o Market Overview
+o Hospitals
+o Ambulatory Surgery Centers &amp; Clinics
+o Others
+• Global Endoscopic Retrograde Cholangiopancreatography Market Size &amp; CAGR (2025-2032)
+o North America (Product Type, Procedure, End Users)
+ US
+ Canada
+o Europe (Product Type, Procedure, End Users)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Product Type, Procedure, End Users)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Product Type, Procedure, End Users)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Product Type, Procedure, End Users)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Olympus Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o CONMED Corporation (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Fujifilm Holdings Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o HOYA Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Boston Scientific Corporation (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Johnson &amp; Johnson (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Medtronic PLC (Ireland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Cook Medical (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o STERRIS PLC (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o TeleMed Systems Inc. (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o DCC Healthcare (Medi-Globe GmbH) (Ireland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Huger Medical Instrument Co. Ltd (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o SonoScape Medical Corporation (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o KARL STORZ SE &amp; Co. KG (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Ambu A/S (Denmark)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o B. Braun Melsungen AG (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o PENTAX Medical (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Hitachi Ltd. (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Canon Medical Systems Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Sony Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>◦ Olympus Corporation (Japan)
+◦ CONMED Corporation (United States)
+◦ Fujifilm Holdings Corporation (Japan)
+◦ HOYA Corporation (Japan)
+◦ Boston Scientific Corporation (United States)
+◦ Johnson &amp; Johnson (United States)
+◦ Medtronic PLC (Ireland)
+◦ Cook Medical (United States)
+◦ STERRIS PLC (United States)
+◦ TeleMed Systems Inc. (United States)
+◦ DCC Healthcare (Medi-Globe GmbH) (Ireland)
+◦ Huger Medical Instrument Co. Ltd (China)
+◦ SonoScape Medical Corporation (China)
+◦ KARL STORZ SE &amp; Co. KG (Germany)
+◦ Ambu A/S (Denmark)
+◦ B. Braun Melsungen AG (Germany)
+◦ PENTAX Medical (Japan)
+◦ Hitachi Ltd. (Japan)
+◦ Canon Medical Systems Corporation (Japan)
+◦ Sony Corporation (Japan)</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>By Product Type (Endoscopes, Endotherapy Devices (Sphincterotomes, Lithotripter, Stents, Cannulas, Forceps, Snares, Catheters, Guiding Wires, Balloons, Baskets), Visualization Systems, Energy Devices, Others), By Procedure (Biliary Sphincterotomy, Biliary Stenting, Biliary Dialtation, Pancreatic Sphincterotomy, Pancreatic Duct Stenting, Pancreatic Duct Dilatation), By End Users (Hospitals, Ambulatory Surgery Centers &amp; Clinics, Others)</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>9.8%</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>USD Billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Catheter Securement Device Market Size, Share, and Growth Analysis, By Product Type (Arterial, Central Venous), By Application (Cardiovascular, Radiology), By End Users, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SQMIG35A2749</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/catheter-securement-device-market</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Global Catheter Securement Device Market size was valued at USD 1.2 billion in 2023 and is poised to grow from USD 1.28 billion in 2024 to USD 2.17 billion by 2032, growing at a CAGR of 6.8% during the forecast period (2025-2032).
+The global catheter securement device market is on an upward trajectory, fueled by several pivotal factors. The growing adoption of catheters in healthcare settings emphasizes their importance across various medical procedures. An influx of new manufacturers is driving competition and innovation within this market segment. Supportive government guidelines promoting the use of securement devices further bolster growth, as they align with initiatives aimed at enhancing patient safety and improving procedural outcomes. Additionally, the escalating incidence of catheter-associated infections highlights the urgent need for effective securement solutions, acting as a significant growth catalyst. As healthcare systems globally focus on optimizing patient safety and outcomes, the catheter securement device market is positioned for continued expansion in the coming years.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Catheter Securement Device market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Catheter Securement Device Market Segments Analysis
+Global Catheter Securement Device Market is segmented by Product Type, Application, End Users and region. Based on Product Type, the market is segmented into Arterial, Central Venous, Peripheral, Chest Drainage Tube, Abdominal Drainage Tubes, Epidural and All-Site Securement Devices. Based on Application, the market is segmented into Cardiovascular, Radiology, General Surgery, Urological, Respiratory and Gastric and Oropharyngeal. Based on End Users, the market is segmented into Hospitals &amp; Clinics, Home Healthcare and Diagnostic Centers. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Catheter Securement Device Market
+The rising number of dialysis patients opting for home treatment is significantly driving the demand for catheter securement devices, especially in relation to home hemodialysis. This shift towards home care has encouraged manufacturers of dialysis equipment to create advanced self-dialyzing systems and services tailored for effective catheter use in domestic settings. As more patients seek the convenience and flexibility of receiving treatment at home, the need for reliable catheter stabilization solutions has escalated, prompting innovations in design and functionality to enhance patient safety and comfort during at-home procedures.
+Restraints in the Global Catheter Securement Device Market
+The Global Catheter Securement Device market faces significant challenges due to the availability of dressing tapes, which offer a cost-effective alternative for retaining Vascular Access Devices (VADs). Traditionally, surgical sutures were the mainstay for securement; however, dressing tapes have emerged as a more economical option for healthcare facilities seeking to control expenses while maintaining effective catheter retention. While these tapes are budget-friendly, their usage is impacted by the changing practices in securement methods within the healthcare sector. As advancements and innovations continue to develop, this dynamic landscape could affect the market growth of catheter securement devices.
+Market Trends of the Global Catheter Securement Device Market
+The Global Catheter Securement Device market is experiencing significant growth, driven by the rising prevalence of chronic diseases such as cancer, stroke, diabetes, and cardiovascular conditions. With the World Health Organization reporting that chronic diseases account for 74% of global fatalities, the demand for effective catheterization in treatment protocols is surging. This trend is underscored by the necessity for securement devices to ensure patient safety and minimize complications associated with catheter use. The market is witnessing advancements in device innovations and an increased emphasis on quality care, positioning catheter securement devices as essential components in the evolving landscape of chronic disease management.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Regulatory Landscape
+o Case Studies
+o Technology Analysis
+• Global Catheter Securement Device Market Size by Product Type &amp; CAGR (2025-2032)
+o Market Overview
+o Arterial
+o Central Venous
+ Peripherally Inserted Central Catheter (PICC)
+ Subclavian
+ Midlines
+ Femoral
+ Portal
+ Jugular
+o Peripheral
+ Foley
+ Nasogastric Tube
+ Endotracheal Tube
+ Ventriculoperitoneal
+ Continuous Nerve Block
+o Chest Drainage Tube
+o Abdominal Drainage Tubes
+ Percutaneous Endoscopic Gastrostomy
+ Jejunal
+ Umbilical
+o Epidural
+o All-Site Securement Devices
+• Global Catheter Securement Device Market Size by Application &amp; CAGR (2025-2032)
+o Market Overview
+o Cardiovascular
+o Radiology
+o General Surgery
+o Urological
+o Respiratory
+o Gastric and Oropharyngeal
+• Global Catheter Securement Device Market Size by End Users &amp; CAGR (2025-2032)
+o Market Overview
+o Hospitals &amp; Clinics
+o Home Healthcare
+o Diagnostic Centers
+• Global Catheter Securement Device Market Size &amp; CAGR (2025-2032)
+o North America (Product Type, Application, End Users)
+ US
+ Canada
+o Europe (Product Type, Application, End Users)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Product Type, Application, End Users)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Product Type, Application, End Users)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Product Type, Application, End Users)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Convatec (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Terumo Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Alvimedica (Turkey)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o MicroPort (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Edwards Lifesciences (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o St. Jude Medical (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Becton, Dickinson and Company (BD) (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Smith &amp; Nephew (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Medtronic (Ireland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Boston Scientific (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Johnson &amp; Johnson (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Fresenius Medical Care (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Cook Medical (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Halyard Health (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Cardinal Health (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o 3M Health Care (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Conmed Corporation (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Terumo Penpol (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Alcon (Switzerland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Biotronik (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>◦ Convatec (United Kingdom)
+◦ Terumo Corporation (Japan)
+◦ Alvimedica (Turkey)
+◦ MicroPort (China)
+◦ Edwards Lifesciences (United States)
+◦ St. Jude Medical (United States)
+◦ Becton, Dickinson and Company (BD) (United States)
+◦ Smith &amp; Nephew (United Kingdom)
+◦ Medtronic (Ireland)
+◦ Boston Scientific (United States)
+◦ Johnson &amp; Johnson (United States)
+◦ Fresenius Medical Care (Germany)
+◦ Cook Medical (United States)
+◦ Halyard Health (United States)
+◦ Cardinal Health (United States)
+◦ 3M Health Care (United States)
+◦ Conmed Corporation (United States)
+◦ Terumo Penpol (India)
+◦ Alcon (Switzerland)
+◦ Biotronik (Germany)</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>By Product Type (Arterial, Central Venous (Peripherally Inserted Central Catheter (PICC), Subclavian, Midlines, Femoral, Portal, Jugular), Peripheral (Foley, Nasogastric Tube, Endotracheal Tube, Ventriculoperitoneal, Continuous Nerve Block), Chest Drainage Tube, Abdominal Drainage Tubes (Percutaneous Endoscopic Gastrostomy, Jejunal, Umbilical), Epidural, All-Site Securement Devices), By Application (Cardiovascular, Radiology, General Surgery, Urological, Respiratory, Gastric and Oropharyngeal), By End Users (Hospitals &amp; Clinics, Home Healthcare, Diagnostic Centers)</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>6.8%</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>USD Billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Pool Tables Market Size, Share, and Growth Analysis, By Type (American Pool Table, British Pool Table), By Size (7 ft, 8 ft), By Material, By Distribution Channel, By End Users, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SQMIG25J2071</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/pool-tables-market</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Global Pool Tables Market size was valued at USD 254.4 million in 2023 and is poised to grow from USD 271.44 million in 2024 to USD 456.03 million by 2032, growing at a CAGR of 6.7% during the forecast period (2025-2032).
+The pool tables market is experiencing significant growth driven by the rising popularity of cue games and enhanced entertainment options. This trend is bolstered by an increase in government academic institutions offering improved facilities for cue sports, which is further amplifying global demand. Various government agencies and private organizations are promoting pool through training programs, creating favorable conditions for market expansion. Additionally, leading industry players are responding to evolving customer preferences by designing customized pool tables, effectively catering to individual needs while broadening their customer base. This strategic approach not only boosts sales but also significantly contributes to the overall growth of the pool tables market, highlighting the intertwining of consumer preferences and market innovation.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Pool Tables market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Pool Tables Market Segments Analysis
+Global Pool Tables Market is segmented by Type, Size, Material, Distribution Channel, End Users and region. Based on Type, the market is segmented into American Pool Table, British Pool Table and Others. Based on Size, the market is segmented into 7 ft, 8 ft, 9 ft and Others. Based on Material, the market is segmented into Slate Pool Table, Wooden Pool Table, Metallic Pool Table and Others. Based on Distribution Channel, the market is segmented into Supermarkets and Hypermarkets, Specialty Stores, Online Stores and Others. Based on End Users, the market is segmented into Residential, Commercial and Professional. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Pool Tables Market
+The global demand for pool tables has significantly increased due to the heightened focus on home entertainment, a shift largely influenced by the COVID-19 pandemic. As individuals were compelled to spend more time at home, there was a notable rise in the search for enjoyable leisure activities. The restrictions on outdoor sports and social gatherings led consumers to seek alternatives that could provide entertainment within the confines of their homes. In this context, pool tables have become an appealing choice, providing a fun and engaging way to enjoy indoor recreation and enhance the overall home entertainment experience.
+Restraints in the Global Pool Tables Market
+The global pool tables market encounters several challenges, primarily related to shifting consumer preferences, particularly the increasing popularity of digital gaming over traditional cue sports. As the appeal of digital entertainment continues to rise, manufacturers must stay attuned to these evolving trends to remain relevant in the industry. Additionally, addressing maintenance issues is crucial; therefore, following manufacturer guidelines and collaborating with skilled HVAC professionals becomes essential. This approach ensures that valuable insights are gained, and proper maintenance practices are adhered to, ultimately enhancing the durability and optimal performance of pool tables in an increasingly competitive market landscape.
+Market Trends of the Global Pool Tables Market
+The global pool tables market is witnessing a significant trend towards sustainability and durability as manufacturers increasingly adopt composite and engineered wood materials for their products. This shift marks a departure from traditional solid wood construction, which has dominated the industry. These modern materials not only enhance the structural integrity and longevity of pool tables by minimizing issues like warping, but they also resonate with environmentally conscious consumers. As a result, the market is evolving towards offering products that appeal to eco-friendly values, thereby attracting a burgeoning segment of consumers who prioritize sustainability alongside quality and aesthetic appeal in their recreational purchases.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Regulatory Landscape
+o Case Studies
+• Global Pool Tables Market Size by Type &amp; CAGR (2025-2032)
+o Market Overview
+o American Pool Table
+o British Pool Table
+o Others
+• Global Pool Tables Market Size by Size &amp; CAGR (2025-2032)
+o Market Overview
+o 7 ft
+o 8 ft
+o 9 ft
+o Others
+• Global Pool Tables Market Size by Material &amp; CAGR (2025-2032)
+o Market Overview
+o Slate Pool Table
+o Wooden Pool Table
+o Metallic Pool Table
+o Others
+• Global Pool Tables Market Size by Distribution Channel &amp; CAGR (2025-2032)
+o Market Overview
+o Supermarkets and Hypermarkets
+o Specialty Stores
+o Online Stores
+o Others
+• Global Pool Tables Market Size by End Users &amp; CAGR (2025-2032)
+o Market Overview
+o Residential
+o Commercial
+o Professional
+• Global Pool Tables Market Size &amp; CAGR (2025-2032)
+o North America (Type, Size, Material, Distribution Channel, End Users)
+ US
+ Canada
+o Europe (Type, Size, Material, Distribution Channel, End Users)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Type, Size, Material, Distribution Channel, End Users)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Type, Size, Material, Distribution Channel, End Users)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Type, Size, Material, Distribution Channel, End Users)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Brunswick Billiards (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Olhausen Billiards (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Valley-Dynamo (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Garlando (Italy)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Alcocks (Australia)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Presidential Billiards (South Africa)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Rasson Billiards (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Imperial International (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Hathaway (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o American Heritage Billiards (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Plank &amp; Hide (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Liberty Games (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Hollis Billiards (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Champion Shuffleboard (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Sun-Glo (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Kettler (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Riley (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Peradon (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Hainsworth (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Garlando (Italy)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>◦ Brunswick Billiards (United States)
+◦ Olhausen Billiards (United States)
+◦ Valley-Dynamo (United States)
+◦ Garlando (Italy)
+◦ Alcocks (Australia)
+◦ Presidential Billiards (South Africa)
+◦ Rasson Billiards (China)
+◦ Imperial International (United States)
+◦ Hathaway (United States)
+◦ American Heritage Billiards (United States)
+◦ Plank &amp; Hide (United States)
+◦ Liberty Games (United Kingdom)
+◦ Hollis Billiards (United States)
+◦ Champion Shuffleboard (United States)
+◦ Sun-Glo (United States)
+◦ Kettler (Germany)
+◦ Riley (United Kingdom)
+◦ Peradon (United Kingdom)
+◦ Hainsworth (United Kingdom)
+◦ Garlando (Italy)</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>By Type (American Pool Table, British Pool Table, Others), By Size (7 ft, 8 ft, 9 ft, Others), By Material (Slate Pool Table, Wooden Pool Table, Metallic Pool Table, Others), By Distribution Channel (Supermarkets and Hypermarkets, Specialty Stores, Online Stores, Others), By End Users (Residential, Commercial, Professional)</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>254.4</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>271.44</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>456.03</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>USD Million</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tea Market Size, Share, and Growth Analysis, By Type (Black, Green), By Form (Loose Leaf, Tea Bags), By Category, By Distribution Channel, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SQMIG30I2372</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/tea-market</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Global Tea Market size was valued at USD 21.5 billion in 2023 and is poised to grow from USD 22.85 billion in 2024 to USD 37.26 billion by 2032, growing at a CAGR of 6.3% during the forecast period (2025-2032).
+The international tea market is thriving, characterized by continuous growth and innovation driven by increasing consumer awareness of health benefits and flavor diversity. There's a notable shift towards premium and specialty teas, reflecting consumer demand for unique experiences. While Asia, particularly China and India, remains central to production and consumption, emerging regions like Africa and South America are becoming significant contributors to the global market. The rising popularity of herbal and specialty teas aligns with health-conscious trends, with green tea gaining traction for its antioxidant properties, especially in Western markets. Moreover, the convenience factor is promoting ready-to-drink (RTD) tea products, catering to busy consumers. E-commerce has enhanced accessibility to varied tea offerings, fostering global trade and opening new market opportunities.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Tea market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Tea Market Segments Analysis
+Global Tea Market is segmented by Type, Form, Category, Distribution Channel and region. Based on Type, the market is segmented into Black, Green, Oolong, Herbal and Others. Based on Form, the market is segmented into Loose Leaf, Tea Bags and Others. Based on Category, the market is segmented into Organic and Conventional. Based on Distribution Channel, the market is segmented into Hypermarkets &amp; Supermarkets, Convenience Stores, Specialty Stores and Online. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Tea Market
+A significant factor propelling the global tea market is the growing awareness among consumers regarding the health benefits associated with tea consumption. Particularly, green and herbal teas are viewed as healthier alternatives to sugary beverages such as sodas. Tea is abundant in antioxidants and offers various health advantages, including enhanced cardiovascular health, support for weight management, and a lowered risk of chronic diseases. As more individuals focus on health and wellness, the demand for tea as a natural and nutritious beverage is expected to rise. This trend highlights the shift toward healthier lifestyle choices among consumers worldwide.
+Restraints in the Global Tea Market
+The global tea market faces significant constraints due to climate change, which poses a considerable threat to tea cultivation. This industry relies heavily on specific climatic conditions, meaning that changes in temperature and precipitation patterns directly impact both yields and quality. Issues such as prolonged droughts, unpredictable weather, and a rise in pests and diseases can severely hinder production capabilities. Additionally, sustainability concerns surrounding land usage, water consumption, and pesticide residues may negatively affect the industry's reputation and limit access to markets with stringent regulations. Consequently, the tea industry must confront these sustainability challenges to thrive in a changing environment.
+Market Trends of the Global Tea Market
+The global tea market is experiencing a significant trend toward the increasing demand for specialty teas, driven by a growing consumer preference for unique and premium varieties. As health-consciousness rises, consumers are gravitating towards herbal, organic, artisanal blends, and single-origin teas that promise distinctive flavors and health benefits. This shift reflects a broader trend within the market, where discerning customers are willing to explore diverse categories, elevating the experience of tea consumption to new heights. The surge in interest for specialty teas is reshaping marketing strategies and product offerings, offering substantial opportunities for brands to innovate and connect with a more sophisticated consumer base.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Regulatory Landscape
+o Case Studies
+• Global Tea Market Size by Type &amp; CAGR (2025-2032)
+o Market Overview
+o Black
+o Green
+o Oolong
+o Herbal
+o Others
+• Global Tea Market Size by Form &amp; CAGR (2025-2032)
+o Market Overview
+o Loose Leaf
+o Tea Bags
+o Others
+• Global Tea Market Size by Category &amp; CAGR (2025-2032)
+o Market Overview
+o Organic
+o Conventional
+• Global Tea Market Size by Distribution Channel &amp; CAGR (2025-2032)
+o Market Overview
+o Hypermarkets &amp; Supermarkets
+o Convenience Stores
+o Specialty Stores
+o Online
+• Global Tea Market Size &amp; CAGR (2025-2032)
+o North America (Type, Form, Category, Distribution Channel)
+ US
+ Canada
+o Europe (Type, Form, Category, Distribution Channel)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Type, Form, Category, Distribution Channel)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Type, Form, Category, Distribution Channel)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Type, Form, Category, Distribution Channel)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Unilever (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Tata Consumer Products (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Associated British Foods (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o The Republic of Tea (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Numi, Inc. (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Bigelow Tea Company (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Tetley (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Vahdam Teas (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Harney &amp; Sons (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Lipton (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Twinings (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Dilmah (Sri Lanka)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Celestial Seasonings (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o PG Tips (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Yorkshire Tea (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Teekanne (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Teavana (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Harrods Tea (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Tazo Tea (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Numi Organic Tea (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>◦ Unilever (United Kingdom)
+◦ Tata Consumer Products (India)
+◦ Associated British Foods (United Kingdom)
+◦ The Republic of Tea (United States)
+◦ Numi, Inc. (United States)
+◦ Bigelow Tea Company (United States)
+◦ Tetley (India)
+◦ Vahdam Teas (India)
+◦ Harney &amp; Sons (United States)
+◦ Lipton (United Kingdom)
+◦ Twinings (United Kingdom)
+◦ Dilmah (Sri Lanka)
+◦ Celestial Seasonings (United States)
+◦ PG Tips (United Kingdom)
+◦ Yorkshire Tea (United Kingdom)
+◦ Teekanne (Germany)
+◦ Teavana (United States)
+◦ Harrods Tea (United Kingdom)
+◦ Tazo Tea (United States)
+◦ Numi Organic Tea (United States)</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>By Type (Black, Green, Oolong, Herbal, Others), By Form (Plastic Containers, Loose Tea, Paperboards, Aluminum Tins, and Tea Bags), By Form (Loose Leaf, Tea Bags, Others), By Category (Organic, Conventional), By Distribution Channel (Hypermarkets &amp; Supermarkets, Convenience Stores, Specialty Stores, Online)</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>21.5</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>37.26</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>6.3%</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>USD Billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Portable Bluetooth Speakers Market Size, Share, and Growth Analysis, By Product Type (Mini, Pocket), By Connectivity (Bluetooth, Hybrid), By Category, By Distribution Channel, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SQMIG25E2116</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/portable-bluetooth-speakers-market</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Global Portable Bluetooth Speakers Market size was valued at USD 11.8 billion in 2023 and is poised to grow from USD 13.03 billion in 2024 to USD 28.75 billion by 2032, growing at a CAGR of 10.4% during the forecast period (2025-2032).
+The portable Bluetooth speakers market is thriving, fueled by shifting consumer preferences for wireless, on-the-go audio solutions. With increasingly mobile lifestyles, these speakers deliver unmatched convenience and flexibility. Technological advancements have led to enhanced sound quality and extended battery life, further driving demand. Additionally, manufacturers are innovating personal and durable designs to capture consumer interest. Growing awareness of wireless connectivity benefits and seamless device pairing options is propelling market expansion. Responding to diverse consumer needs, companies are consistently launching new models featuring upgraded functionalities. This dynamic and competitive landscape provides consumers with a wide array of choices, enabling them to select speakers that best suit their preferences, thereby promoting continued growth in the sector.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Portable Bluetooth Speakers market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Portable Bluetooth Speakers Market Segments Analysis
+Global Portable Bluetooth Speakers Market is segmented by Product Type, Connectivity, Category, Distribution Channel and region. Based on Product Type, the market is segmented into Mini, Pocket, Capsule and Others. Based on Connectivity, the market is segmented into Bluetooth, Hybrid and Others. Based on Category, the market is segmented into Mass market and premium. Based on Distribution Channel, the market is segmented into Offline and Online. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Portable Bluetooth Speakers Market
+A significant factor propelling the Global Portable Bluetooth Speakers Market is the ongoing technological innovation. Manufacturers are relentlessly striving to improve aspects such as sound quality, connectivity features, and battery longevity. The incorporation of advanced functionalities like smart features, voice assistant compatibility, and durable designs has played a crucial role in appealing to consumers who seek versatile and superior audio experiences. This constant evolution in technology not only enhances user satisfaction but also drives demand for portable Bluetooth speakers, solidifying their presence in the audio equipment market as people increasingly prioritize high-quality and adaptable sound solutions.
+Restraints in the Global Portable Bluetooth Speakers Market
+One of the major challenges facing the global portable Bluetooth speakers market is the intense competitive pricing pressure. With a multitude of companies competing for market share, price wars have become prevalent, which can result in diminished profit margins. This situation poses risks to potential investments in research and development, as manufacturers are compelled to prioritize affordability. Consequently, maintaining a delicate balance between offering competitive prices and ensuring product quality is essential for companies operating in this price-sensitive market to sustain their competitiveness while navigating these financial constraints effectively.
+Market Trends of the Global Portable Bluetooth Speakers Market
+The Global Portable Bluetooth Speakers market is witnessing a significant trend towards voice assistant integration, as manufacturers increasingly embed virtual assistants such as Amazon's Alexa and Google Assistant into their products. This shift caters to the rising consumer demand for smart and connected devices, allowing users to effortlessly control their speakers, retrieve information, and execute tasks with simple voice commands. Such integration not only enhances user convenience but also propels portable speakers into the heart of the smart home ecosystem, fostering a seamless interaction between devices. Consequently, this trend is driving robust market growth, reflecting a broader move towards increasingly intelligent audio solutions.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Regulatory Landscape
+o Case Studies
+o Technology Analysis
+• Global Portable Bluetooth Speakers Market Size by Product Type &amp; CAGR (2025-2032)
+o Market Overview
+o Mini
+o Pocket
+o Capsule
+o Others
+• Global Portable Bluetooth Speakers Market Size by Connectivity &amp; CAGR (2025-2032)
+o Market Overview
+o Bluetooth
+o Hybrid
+o Others
+• Global Portable Bluetooth Speakers Market Size by Category &amp; CAGR (2025-2032)
+o Market Overview
+o Mass market
+o Premium
+• Global Portable Bluetooth Speakers Market Size by Distribution Channel &amp; CAGR (2025-2032)
+o Market Overview
+o Offline
+o Online
+• Global Portable Bluetooth Speakers Market Size &amp; CAGR (2025-2032)
+o North America (Product Type, Connectivity, Category, Distribution Channel)
+ US
+ Canada
+o Europe (Product Type, Connectivity, Category, Distribution Channel)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Product Type, Connectivity, Category, Distribution Channel)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Product Type, Connectivity, Category, Distribution Channel)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Product Type, Connectivity, Category, Distribution Channel)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o JBL (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Sony (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Bose (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Ultimate Ears (UE) (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Anker Soundcore (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o B&amp;O (Bang &amp; Olufsen) (Denmark)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Marshall (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Samsung (South Korea)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o LG Electronics (South Korea)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Sonos (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Harman Kardon (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Audioengine (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Devialet (France)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Edifier (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Creative Technology (Singapore)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Vizio (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Denon (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Klipsch (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Sennheiser (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o AKG Acoustics (Austria)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>◦ JBL (United States)
+◦ Sony (Japan)
+◦ Bose (United States)
+◦ Ultimate Ears (UE) (United States)
+◦ Anker Soundcore (China)
+◦ B&amp;O (Bang &amp; Olufsen) (Denmark)
+◦ Marshall (United Kingdom)
+◦ Samsung (South Korea)
+◦ LG Electronics (South Korea)
+◦ Sonos (United States)
+◦ Harman Kardon (United States)
+◦ Audioengine (United States)
+◦ Devialet (France)
+◦ Edifier (China)
+◦ Creative Technology (Singapore)
+◦ Vizio (United States)
+◦ Denon (Japan)
+◦ Klipsch (United States)
+◦ Sennheiser (Germany)
+◦ AKG Acoustics (Austria)</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>By Product Type (Mini, Pocket, Capsule, Others), By Connectivity (Bluetooth, Hybrid, Others), By Category (Mass market, Premium), By Distribution Channel (Offline, Online)</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>13.03</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>28.75</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>10.4%</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>USD Billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Airport Passenger Screening Systems Market Size, Share, and Growth Analysis, By Systems Type (Fixed Systems, Portable Systems), By Technology (X-ray Screening, Computed Tomography), By Application, By End Users, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SQMIG45F2132</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/airport-passenger-screening-systems-market</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Global Airport Passenger Screening Systems Market size was valued at USD 2.4 billion in 2023 and is poised to grow from USD 2.59 billion in 2024 to USD 4.76 billion by 2032, growing at a CAGR of 7.9% during the forecast period (2025-2032).
+The Global Airport Passenger Screening Systems Market is driven by an ongoing demand for enhanced security solutions to ensure passenger safety amid persistent terrorism threats. As air travel continues to rise globally, airports are increasingly investing in cutting-edge screening technologies. However, challenges such as privacy concerns and the need for operational efficiency persist. The market features a variety of products, including metal detectors and full-body scanners, with North America leading due to strict safety regulations. Current trends highlight the integration of artificial intelligence for improved threat detection and the advancement of non-intrusive, more efficient screening methods, reflecting the industry's commitment to innovation and security.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Airport Passenger Screening Systems market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Airport Passenger Screening Systems Market Segments Analysis
+Global Airport Passenger Screening Systems Market is segmented by Systems Type, Technology, Application, End Users and region. Based on Systems Type, the market is segmented into Fixed Systems, Portable Systems and Mobile Systems. Based on Technology, the market is segmented into X-ray Screening, Computed Tomography, Millimeter Wave Scanner, Explosive Trace Detection and Biometric Screening. Based on Application, the market is segmented into Baggage Screening, Passenger Screening, Cargo Screening and Airport Security Checkpoints. Based on End Users, the market is segmented into Commercial Airports, Private Airports, Cargo Airports and Military Airports. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Airport Passenger Screening Systems Market
+The persistent threat of terrorism is a significant catalyst for the Global Airport Passenger Screening Systems market, underscoring the need for advanced screening technologies to safeguard both passengers and aviation infrastructure. Additionally, the ongoing growth in global air travel, spurred by rising urbanization and economic development, further amplifies the demand for effective and technologically advanced screening solutions. As the aviation industry continues to expand, the integration of cutting-edge screening systems becomes essential to enhance security measures and ensure a safe travel experience for all. This combination of factors highlights the critical importance of investing in superior screening technologies.
+Restraints in the Global Airport Passenger Screening Systems Market
+The Global Airport Passenger Screening Systems market faces significant constraints, primarily due to privacy concerns associated with advanced screening technologies that often require capturing unique images of passengers. This raises alarming worries about personal privacy among travelers. Furthermore, operational efficiency is another critical challenge, particularly during peak travel periods, as rigorous screening protocols can result in delays and increased congestion at security checkpoints. These factors collectively hinder the smooth implementation and acceptance of advanced screening solutions, making it difficult to balance security needs with passenger convenience and privacy rights.
+Market Trends of the Global Airport Passenger Screening Systems Market
+The Global Airport Passenger Screening Systems market is experiencing a significant trend towards the integration of artificial intelligence (AI), which enhances the efficiency and accuracy of threat detection while significantly reducing false positives. As airports prioritize passenger experience and privacy concerns, the shift towards non-intrusive and contactless screening technologies is becoming increasingly prevalent. This trend not only improves operational effectiveness and security measures but also caters to the evolving expectations of travelers for a seamless journey. Consequently, the adoption of AI-driven solutions is expected to shape the evolution of airport screening systems, positioning the industry for robust growth in the coming years.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Regulatory Landscape
+o Case Studies
+o Technology Analysis
+• Global Airport Passenger Screening Systems Market Size by Systems Type &amp; CAGR (2025-2032)
+o Market Overview
+o Fixed Systems
+o Portable Systems
+o Mobile Systems
+• Global Airport Passenger Screening Systems Market Size by Technology &amp; CAGR (2025-2032)
+o Market Overview
+o X-ray Screening
+o Computed Tomography
+o Millimeter Wave Scanner
+o Explosive Trace Detection
+o Biometric Screening
+• Global Airport Passenger Screening Systems Market Size by Application &amp; CAGR (2025-2032)
+o Market Overview
+o Baggage Screening
+o Passenger Screening
+o Cargo Screening
+o Airport Security Checkpoints
+• Global Airport Passenger Screening Systems Market Size by End Users &amp; CAGR (2025-2032)
+o Market Overview
+o Commercial Airports
+o Private Airports
+o Cargo Airports
+o Military Airports
+• Global Airport Passenger Screening Systems Market Size &amp; CAGR (2025-2032)
+o North America (Systems Type, Technology, Application, End Users)
+ US
+ Canada
+o Europe (Systems Type, Technology, Application, End Users)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Systems Type, Technology, Application, End Users)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Systems Type, Technology, Application, End Users)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Systems Type, Technology, Application, End Users)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Analogic Corporation (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o OSI Systems Inc. (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Garrett Electronics Inc. (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Smiths Group plc (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Leidos, Inc. (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Nuctech Company Limited (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Kromek Group plc (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Optosecurity Inc. (Canada)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Thales Group (France)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o NEC Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Teledyne Technologies Incorporated (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Bruker (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o American Science and Engineering, Inc. (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Smiths Detection Group Ltd. (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Nuctech Company Limited (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>◦ Analogic Corporation (United States)
+◦ OSI Systems Inc. (United States)
+◦ Garrett Electronics Inc. (United States)
+◦ Smiths Group plc (United Kingdom)
+◦ Leidos, Inc. (United States)
+◦ Nuctech Company Limited (China)
+◦ Kromek Group plc (United Kingdom)
+◦ Optosecurity Inc. (Canada)
+◦ Thales Group (France)
+◦ NEC Corporation (Japan)
+◦ Teledyne Technologies Incorporated (United States)
+◦ Bruker (United States)
+◦ American Science and Engineering, Inc. (United States)
+◦ Smiths Detection Group Ltd. (United Kingdom)
+◦ Nuctech Company Limited (China)</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>By Systems Type (Fixed Systems, Portable Systems, Mobile Systems), By Technology (X-ray Screening, Computed Tomography, Millimeter Wave Scanner, Explosive Trace Detection, Biometric Screening), By Application (Baggage Screening, Passenger Screening, Cargo Screening, Airport Security Checkpoints), By End Users (Commercial Airports, Private Airports, Cargo Airports, Military Airports)</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>7.9%</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>USD Billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Vacuum Waste Systems Market Size, Share, and Growth Analysis, By Type (Stationary, Mobile), By Surface Position (Underground, Overground), By End Users, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SQMIG20L2043</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/vacuum-waste-systems-market</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Vacuum Waste Systems Market size was valued at USD 1.65 Billion in 2023 and is poised to grow from USD 1.8 Billion in 2024 to USD 3.64 Billion by 2032, growing at a CAGR of 9.2% during the forecast period (2025-2032).
+The global go-kart market is experiencing robust growth, driven by its appeal as an accessible and exhilarating entry point into motorsports for enthusiasts of all ages. As a cost-effective and relatively safe activity, go-karting has proliferated internationally, evident in the rise of tracks and rental facilities. Beyond competitive racing, which serves as a crucial training ground for future motorsport champions, go-karting is widely enjoyed as a family-friendly entertainment option in amusement parks and recreational venues. Additionally, the market is benefitting from advancements in technology, particularly with the increasing popularity of electric go-karts that attract a diverse audience due to their environmental benefits and practicality for indoor use. Overall, the vibrant go-kart segment continues to evolve, promising exciting opportunities.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Vacuum Waste Systems market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Vacuum Waste Systems Market Segments Analysis
+Global Vacuum Waste Systems Market is segmented by Type, Surface Position, End Users and region. Based on Type, the market is segmented into Stationary and Mobile. Based on Surface Position, the market is segmented into Underground and Overground. Based on End Users, the market is segmented into Transportation, Airports, Industrial and Others. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Vacuum Waste Systems Market
+The Vacuum Waste Systems market is propelled by the growing demand for efficient waste management solutions across various sectors. As municipalities and businesses strive for sustainable practices, the need for advanced vacuum waste systems has surged. These systems offer a streamlined approach to waste collection, reducing labor costs and increasing safety. Additionally, the rise in urbanization and population density necessitates innovative waste disposal methods that can accommodate increasing demands without compromising cleanliness. Furthermore, heightened environmental awareness is motivating industries to adopt eco-friendly technologies, further fueling the growth of the vacuum waste systems market. This trend is expected to intensify in the coming years.
+Restraints in the Vacuum Waste Systems Market
+Safety issues pose a considerable challenge to the Vacuum Waste Systems market. Incidents and potential hazards are a concern, particularly when safety standards and guidelines are not rigorously adhered to. This heightened focus on safety has resulted in greater industry scrutiny and necessitated the implementation of enhanced safety features and regulations. Consequently, organizations within the market face increased operational costs as they strive to comply with these safety measures. As businesses work to mitigate risks and maintain safe environments, the financial burden associated with these improvements can deter investment and slow market growth, impacting overall industry dynamics.
+Market Trends of the Vacuum Waste Systems Market
+The Vacuum Waste Systems market is experiencing a significant upward trend, driven by increasing urbanization and stringent environmental regulations. As cities expand, the need for efficient waste management solutions has become paramount, promoting the adoption of vacuum waste systems that offer streamlined collection and minimized environmental impact. These systems not only enhance sanitation by reducing odors and pest infestations but also lower labor and operational costs for municipalities. Furthermore, technological advancements and rising awareness of sustainable practices are propelling market growth, making vacuum waste systems a preferred choice for smart city initiatives and innovative waste management strategies in various sectors.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Regulatory Landscape
+o Case Studies
+• Global Vacuum Waste Systems Market Size by Type &amp; CAGR (2025-2032)
+o Market Overview
+o Stationary
+o Mobile
+• Global Vacuum Waste Systems Market Size by Surface Position &amp; CAGR (2025-2032)
+o Market Overview
+o Underground
+o Overground
+• Global Vacuum Waste Systems Market Size by End Users &amp; CAGR (2025-2032)
+o Market Overview
+o Transportation
+o Airports
+o Industrial
+o Others
+• Global Vacuum Waste Systems Market Size &amp; CAGR (2025-2032)
+o North America (Type, Surface Position, End Users)
+ US
+ Canada
+o Europe (Type, Surface Position, End Users)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Type, Surface Position, End Users)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Type, Surface Position, End Users)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Type, Surface Position, End Users)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Evac (Finland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Envac (Sweden)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Collins Aerospace (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Mundo-Tech, Inc. (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o AcornVac (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Bortek Industries, Inc. (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o MariMatic (Finland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Pneumatech (Belgium)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Pneumatic Waste Systems (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o SULO (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Vacuum Waste Solutions (Australia)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Aerospace Vacuum Services (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Pneumatic Conveying Services (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Schwäbische Hüttenwerke (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Vacuumschmelze GmbH (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Aviagen (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o VacuTech (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o VEGA (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Pneumatec (Belgium)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Rosenberg Ventilatoren GmbH (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>◦ Evac (Finland)
+◦ Envac (Sweden)
+◦ Collins Aerospace (United States)
+◦ Mundo-Tech, Inc. (United States)
+◦ AcornVac (United States)
+◦ Bortek Industries, Inc. (United States)
+◦ MariMatic (Finland)
+◦ Pneumatech (Belgium)
+◦ Pneumatic Waste Systems (United States)
+◦ SULO (Germany)
+◦ Vacuum Waste Solutions (Australia)
+◦ Aerospace Vacuum Services (United States)
+◦ Pneumatic Conveying Services (United States)
+◦ Schwäbische Hüttenwerke (Germany)
+◦ Vacuumschmelze GmbH (Germany)
+◦ Aviagen (United States)
+◦ VacuTech (United States)
+◦ VEGA (Germany)
+◦ Pneumatec (Belgium)
+◦ Rosenberg Ventilatoren GmbH (Germany)</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>By Type (Stationary, Mobile), By Surface Position (Underground, Overground), By End Users (Transportation, Airports, Industrial, Others)</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>USD Billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Floating Power Plant Market Size, Share, and Growth Analysis, By Power Source (Non-renewable, Renewable), By Capacity (1 MW–5 MW, 5.1 MW–20 MW), By Power Rating, By Type, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SQMIG55A2017</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/floating-power-plant-market</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Global Floating Power Plant Market size was valued at USD 5.2 billion in 2023 and is poised to grow from USD 5.79 billion in 2024 to USD 13.63 billion by 2032, growing at a CAGR of 11.3% during the forecast period (2025-2032).
+The floating power plant market is rapidly evolving, driven by the increasing demand for reliable renewable energy sources, especially in remote and off-grid areas. These innovative systems harness solar, wind, and hydro energy from bodies of water, offering a versatile solution for electricity generation where traditional infrastructure is lacking. This sector's growth is propelled by the global need for sustainable power in combating climate change. However, challenges such as high capital costs, regulatory uncertainties, and environmental concerns hinder market expansion. Yet, opportunities for innovation—such as improved designs and energy storage integration—emerge amidst these obstacles. Collaborations between governments, private entities, and academia can foster advancements, positioning the floating power plant market as a key player in global electrification efforts.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Floating Power Plant market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Floating Power Plant Market Segments Analysis
+Global Floating Power Plant Market is segmented by Power Source, Capacity, Power Rating, Type and region. Based on Power Source, the market is segmented into Non-renewable and Renewable. Based on Capacity, the market is segmented into 1 MW–5 MW, 5.1 MW–20 MW, 20.1 MW–100 MW, 100.1 MW–250 MW and Above 250 MW. Based on Power Rating, the market is segmented into Low-power FPP, Medium-power FPP and High-power FPP. Based on Type, the market is segmented into Ships, Barges and Others (Platforms. Etc.). Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Floating Power Plant Market
+A significant driving force behind the global floating power plant market is the growing demand for sustainable electricity solutions. As numerous sectors emphasize the importance of clean and renewable energy, floating power plants emerge as efficient and stable distributed energy sources. Their design allows for quick responsiveness to sudden load changes and rapid startup, which makes them ideal for enhancing grid stability in renewable energy contexts. Additionally, the increasing recognition of the benefits of floating power plants, including their capacity to deliver power to areas with inadequate infrastructure, further propels the growth of the floating power plant market.
+Restraints in the Global Floating Power Plant Market
+One of the significant challenges facing the global floating power plant market is the substantial upfront investment needed for project initiation. The establishment and operation of floating power plants incur considerable expenses related to engineering, construction, and installation. Additionally, the intricate nature of these projects, especially in offshore locations, contributes to the overall financial burden. This high level of investment may discourage potential investors, which can restrict the broader acceptance and implementation of floating power plants, ultimately affecting the growth trajectory of the Floating Power Plant Market.
+Market Trends of the Global Floating Power Plant Market
+A notable trend in the global floating power plant market is the increasing adoption of energy storage systems, particularly advanced battery technologies. This integration enhances the operational flexibility of floating power plants by allowing efficient storage and dispatch of electricity generated from intermittent renewable sources like wind and solar. By mitigating issues related to grid fluctuations, energy storage systems improve overall reliability and stability in power supply. As the demand for sustainable, resilient energy solutions grows, this synergy between floating power plants and energy storage emerges as a pivotal development, driving both innovation and investment opportunities in the renewable energy sector.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+• Global Floating Power Plant Market Size by Power Source &amp; CAGR (2025-2032)
+o Market Overview
+o Non-renewable
+ IC Engines
+ Gas Turbines
+o Renewable
+ Wind
+ Solar
+• Global Floating Power Plant Market Size by Capacity &amp; CAGR (2025-2032)
+o Market Overview
+o 1 MW–5 MW
+o 5.1 MW–20 MW
+o 20.1 MW–100 MW
+o 100.1 MW–250 MW
+o Above 250 MW
+• Global Floating Power Plant Market Size by Power Rating &amp; CAGR (2025-2032)
+o Market Overview
+o Low-power FPP
+o Medium-power FPP
+o High-power FPP
+• Global Floating Power Plant Market Size by Type &amp; CAGR (2025-2032)
+o Market Overview
+o Ships
+o Barges
+o Others (Platforms. Etc.)
+• Global Floating Power Plant Market Size &amp; CAGR (2025-2032)
+o North America (Power Source, Capacity, Power Rating, Type)
+ US
+ Canada
+o Europe (Power Source, Capacity, Power Rating, Type)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Power Source, Capacity, Power Rating, Type)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Power Source, Capacity, Power Rating, Type)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Power Source, Capacity, Power Rating, Type)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o MAN Energy Solutions SE (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Mitsubishi Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o General Electric Company (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Siemens AG (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Caterpillar Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Ciel et Terre International SAS (France)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Floating Power Plant A/S (Denmark)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Principle Power Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Wärtsilä (Finland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Equinor ASA (Norway)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Kawasaki Heavy Industries Ltd. (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Karadeniz Holding AS (Turkey)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Kyocera Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o BW Ideol (France)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Ocean Sun AS (Norway)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Yingli Green Energy Holding Company Limited (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Vikram Solar Limited (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o SUNGROW (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o SolarisFloat, LLC (Portugal)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Ocean Power Technologies Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>◦ MAN Energy Solutions SE (Germany)
+◦ Mitsubishi Corporation (Japan)
+◦ General Electric Company (USA)
+◦ Siemens AG (Germany)
+◦ Caterpillar Inc. (USA)
+◦ Ciel et Terre International SAS (France)
+◦ Floating Power Plant A/S (Denmark)
+◦ Principle Power Inc. (USA)
+◦ Wärtsilä (Finland)
+◦ Equinor ASA (Norway)
+◦ Kawasaki Heavy Industries Ltd. (Japan)
+◦ Karadeniz Holding AS (Turkey)
+◦ Kyocera Corporation (Japan)
+◦ BW Ideol (France)
+◦ Ocean Sun AS (Norway)
+◦ Yingli Green Energy Holding Company Limited (China)
+◦ Vikram Solar Limited (India)
+◦ SUNGROW (China)
+◦ SolarisFloat, LLC (Portugal)
+◦ Ocean Power Technologies Inc. (USA)</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>By Power Source (Non-renewable (IC Engines, Gas Turbines), Renewable (Wind, Solar)), By Capacity (1 MW–5 MW, 5.1 MW–20 MW, 20.1 MW–100 MW, 100.1 MW–250 MW, Above 250 MW), By Power Rating (Low-power FPP, Medium-power FPP, High-power FPP), By Type (Ships, Barges, Others (Platforms. Etc.))</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>5.79</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>13.63</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>11.3%</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>USD Billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Vehicle Electrification Market Size, Share, and Growth Analysis, By Voltage (14 V, 12 V), By Product (Electric Power Steering (EPS), Integrated Starter Generator (ISG)), By Hybridization, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SQMIG45J2173</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/vehicle-electrification-market</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Global Vehicle Electrification Market size was valued at USD 99.6 billion in 2023 and is poised to grow from USD 110.06 billion in 2024 to USD 244.64 billion by 2032, growing at a CAGR of 10.5% during the forecast period (2025-2032).
+The vehicle electrification market is gaining traction due to heightened global awareness of environmental pollution and carbon emissions linked to traditional vehicles. This growth is propelled by stringent government regulations aimed at reducing greenhouse gas emissions, including incentives for electric vehicle (EV) purchases, tighter emission standards, and expanded charging infrastructure. However, challenges persist, particularly the high upfront costs of EVs, driven largely by expensive battery components, which can limit accessibility for consumers. Despite these hurdles, the market brims with opportunities, especially as demand for EVs stimulates technological advancements in battery technology, charging solutions, and power management systems. Investments in charging infrastructure and renewable energy integration will further catalyze the evolution of a sustainable mobility landscape, shaping the future of vehicle electrification.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Vehicle Electrification market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Vehicle Electrification Market Segments Analysis
+Global Vehicle Electrification Market is segmented by Voltage, Product, Hybridization and region. Based on Voltage, the market is segmented into 14 V, 12 V, 48 V and 24 V. Based on Product, the market is segmented into Electric Power Steering (EPS), Integrated Starter Generator (ISG), Stop/Start System, Liquid Heater PTC, Electric Oil Pump, Electric Vacuum Pump and Starter Motor. Based on Hybridization, the market is segmented into Internal Combustion Engine (ICE) &amp; Micro-Hybrid Vehicle, Battery Electric Vehicle ((BEV), Plug-In Hybrid Electric Vehicle (PHEV) and 48 Mild-Hybrid. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Vehicle Electrification Market
+The global vehicle electrification market is being significantly propelled by supportive measures from governments around the world, which are putting in place a variety of policies, incentives, and regulations designed to foster the adoption of electric vehicles. Notably, in 2022, the United States introduced an expansion and extension of federal tax credits specifically for electric vehicles, offering substantial financial incentives to consumers. This move is expected to enhance the attractiveness of electric vehicles, thereby accelerating their uptake and fostering a broader shift towards vehicle electrification in line with global sustainability goals.
+Restraints in the Global Vehicle Electrification Market
+The restricted access to charging infrastructure poses a critical obstacle to the broad acceptance of electric vehicles within the Global Vehicle Electrification market. In 2022, this limitation became evident as a potential hindrance to market expansion, especially in areas where charging networks are insufficient and the pace of infrastructure development lags. The lack of widespread charging stations not only affects consumer confidence but also slows down the transition to electric mobility. As long as these infrastructure gaps exist, they will continue to present significant challenges to the growth and adoption of electric vehicles globally.
+Market Trends of the Global Vehicle Electrification Market
+The Global Vehicle Electrification market is witnessing a remarkable trend driven by significant advancements in battery technology and increased vehicle range. Automakers are prioritizing enhancements in battery energy density, enabling electric vehicles (EVs) to achieve longer driving ranges, effectively alleviating range anxiety among consumers. Notable examples, such as Tesla's Model S Plaid, boasting an impressive range of over 520 miles, and Hyundai's Ioniq 5, capable of 300 miles, exemplify these innovations. As these advancements bolster consumer confidence, they play a pivotal role in the mainstream adoption of EVs, propelling the electrification market forward and reshaping the automotive landscape.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+• Global Vehicle Electrification Market Size by Voltage &amp; CAGR (2025-2032)
+o Market Overview
+o 14 V
+o 12 V
+o 48 V
+o 24 V
+• Global Vehicle Electrification Market Size by Product &amp; CAGR (2025-2032)
+o Market Overview
+o Electric Power Steering (EPS)
+o Integrated Starter Generator (ISG)
+o Stop/Start System
+o Liquid Heater PTC
+o Electric Oil Pump
+o Electric Vacuum Pump
+o Starter Motor
+• Global Vehicle Electrification Market Size by Hybridization &amp; CAGR (2025-2032)
+o Market Overview
+o Internal Combustion Engine (ICE) &amp; Micro-Hybrid Vehicle
+o Battery Electric Vehicle ((BEV)
+o Plug-In Hybrid Electric Vehicle (PHEV)
+o 48 Mild-Hybrid
+• Global Vehicle Electrification Market Size &amp; CAGR (2025-2032)
+o North America (Voltage, Product, Hybridization)
+ US
+ Canada
+o Europe (Voltage, Product, Hybridization)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Voltage, Product, Hybridization)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Voltage, Product, Hybridization)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Voltage, Product, Hybridization)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Tesla, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o BYD Company Ltd. (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Volkswagen AG (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Toyota Motor Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o General Motors Company (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Ford Motor Company (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Nissan Motor Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Hyundai Motor Company (South Korea)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Renault S.A. (France)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Stellantis N.V. (Netherlands)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o BMW AG (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Daimler AG (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o LG Chem Ltd. (South Korea)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o CATL (Contemporary Amperex Technology Co. Limited) (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Panasonic Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Robert Bosch GmbH (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Continental AG (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Magna International Inc. (Canada)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Aptiv PLC (Ireland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o NXP Semiconductors N.V. (Netherlands)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>◦ Tesla, Inc. (USA)
+◦ BYD Company Ltd. (China)
+◦ Volkswagen AG (Germany)
+◦ Toyota Motor Corporation (Japan)
+◦ General Motors Company (USA)
+◦ Ford Motor Company (USA)
+◦ Nissan Motor Corporation (Japan)
+◦ Hyundai Motor Company (South Korea)
+◦ Renault S.A. (France)
+◦ Stellantis N.V. (Netherlands)
+◦ BMW AG (Germany)
+◦ Daimler AG (Germany)
+◦ LG Chem Ltd. (South Korea)
+◦ CATL (Contemporary Amperex Technology Co. Limited) (China)
+◦ Panasonic Corporation (Japan)
+◦ Robert Bosch GmbH (Germany)
+◦ Continental AG (Germany)
+◦ Magna International Inc. (Canada)
+◦ Aptiv PLC (Ireland)
+◦ NXP Semiconductors N.V. (Netherlands)</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>By Voltage (14 V, 12 V, 48 V, 24 V), By Product (Electric Power Steering (EPS), Integrated Starter Generator (ISG), Stop/Start System, Liquid Heater PTC, Electric Oil Pump, Electric Vacuum Pump, Starter Motor), By Hybridization (Internal Combustion Engine (ICE) &amp; Micro-Hybrid Vehicle, Battery Electric Vehicle ((BEV), Plug-In Hybrid Electric Vehicle (PHEV), 48 Mild-Hybrid))</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>110.06</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>244.64</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>10.5%</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>USD Billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Unified Communication as a Service Market Size, Share, and Growth Analysis, By Component (Telephony, Unified Messaging), By Communication Type (Voice, Video), By Delivery Model, By Deployment, By Organization size, By End-Use, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SQMIG45D2084</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/unified-communication-as-a-service-market</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Global Unified Communication as a Service Market size was valued at USD 71.1 billion in 2023 and is poised to grow from USD 86.32 billion in 2024 to USD 407.23 billion by 2032, growing at a CAGR of 21.4% during the forecast period (2025-2032).
+The unified communication as a service (UCaaS) market is experiencing significant growth, driven by the rising need for effective and integrated communication solutions. As organizations embrace remote and hybrid work, seamless communication becomes essential for boosting productivity and streamlining processes. The urgency for enhanced employee collaboration and customer engagement is compelling companies to upgrade their communication infrastructures to remain competitive. Moreover, government initiatives promoting digital transformation and improved telecom infrastructure are accelerating UCaaS adoption. Investments in broadband access, coupled with tax breaks and financing schemes, encourage businesses to transition to cloud-based solutions. This digital revolution across sectors creates numerous development opportunities within the UCaaS industry as firms increasingly seek customizable and scalable solutions to enhance customer relationships and operational efficiency.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Unified Communication As A Service market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Unified Communication As A Service Market Segments Analysis
+Global Unified Communication as a Service Market is segmented by Component, Communication Type, Delivery Model, Deployment, Organization size, End-Use and region. Based on Component, the market is segmented into Telephony, Unified Messaging, Conferencing and Collaboration Platforms and Applications. Based on Communication Type, the market is segmented into Voice, Video, Messaging and Collaboration. Based on Delivery Model, the market is segmented into Managed Services, and Hosted/Cloud Services. Based on Deployment, the market is segmented into Private cloud services and Public cloud services. Based on Organization size, the market is segmented into Small and medium sized enterprises and Large Enterprises. Based on End-Use, the market is segmented into Banking Financial Services and Insurance (BFSI), Healthcare, IT Enabled Services and Telecommunication, Retail and Consumer Goods, Transportation and Logistics, Travel and Hospitality, Automotive, Public Sector and Others. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Unified Communication As A Service Market
+The global Unified Communication as a Service (UCaaS) market is significantly driven by the increasing demand for cloud-based solutions. As businesses increasingly shift their operations to the cloud, UCaaS has emerged as a favorable option due to its scalability, cost-effectiveness, and flexibility. Organizations are drawn to these cloud-based platforms, which allow for efficient communication across diverse devices and locations, ultimately making UCaaS solutions accessible and economical in terms of infrastructure requirements. This trend highlights the growing preference for unified communication tools that enhance collaboration and connectivity in an ever-evolving digital landscape.
+Restraints in the Global Unified Communication As A Service Market
+The Global Unified Communication as a Service (UCaaS) market faces notable challenges primarily concerning data security and privacy. Since UCaaS relies on the transmission of sensitive information over the Internet, companies are understandably apprehensive about the risk of cyberattacks and hacking incidents. This fear creates a reluctance among certain organizations, particularly within heavily regulated industries such as healthcare and finance, to adopt UCaaS solutions fully. These sectors are bound by strict regulatory frameworks that make them cautious about transitioning to UCaaS, leading to significant constraints on market growth despite its potential advantages.
+Market Trends of the Global Unified Communication As A Service Market
+As of October 2023, the global Unified Communication as a Service (UCaaS) market is witnessing a significant trend towards the integration of automation and artificial intelligence (AI). This convergence is revolutionizing communication systems, with AI-driven solutions such as chatbots, speech recognition, automated scheduling, and sentiment analysis enhancing user experiences and delivering real-time responses. By minimizing human intervention, these advanced technologies not only provide organizations with actionable data insights but also optimize operational efficiency across customer service channels. Consequently, businesses are adopting smarter and more flexible UCaaS solutions to meet evolving communication needs, driving the market's robust growth.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Technology Analysis
+• Global Unified Communication as a Service Market Size by Component &amp; CAGR (2025-2032)
+o Market Overview
+o Telephony
+o Unified Messaging
+o Conferencing
+o Collaboration Platforms and Applications
+• Global Unified Communication as a Service Market Size by Communication Type &amp; CAGR (2025-2032)
+o Market Overview
+o Voice
+o Video
+o Messaging
+o Collaboration
+• Global Unified Communication as a Service Market Size by Delivery Model &amp; CAGR (2025-2032)
+o Market Overview
+o Managed Services
+o Hosted/Cloud Services
+• Global Unified Communication as a Service Market Size by Deployment &amp; CAGR (2025-2032)
+o Market Overview
+o Private cloud services
+o Public cloud services
+• Global Unified Communication as a Service Market Size by Organization size &amp; CAGR (2025-2032)
+o Market Overview
+o Small and medium sized enterprises
+o Large Enterprises
+• Global Unified Communication as a Service Market Size by End-Use &amp; CAGR (2025-2032)
+o Market Overview
+o Banking Financial Services and Insurance (BFSI)
+o Healthcare
+o IT Enabled Services and Telecommunication
+o Retail and Consumer Goods
+o Transportation and Logistics
+o Travel and Hospitality
+o Automotive
+o Public Sector
+o Others
+• Global Unified Communication as a Service Market Size &amp; CAGR (2025-2032)
+o North America (Component, Communication Type, Delivery Model, Deployment, Organization size, End-Use)
+ US
+ Canada
+o Europe (Component, Communication Type, Delivery Model, Deployment, Organization size, End-Use)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Component, Communication Type, Delivery Model, Deployment, Organization size, End-Use)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Component, Communication Type, Delivery Model, Deployment, Organization size, End-Use)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Component, Communication Type, Delivery Model, Deployment, Organization size, End-Use)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o RingCentral, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o 8x8, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Zoom Video Communications, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Microsoft Corporation (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Cisco Systems, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Verizon Communications Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o AT&amp;T Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Mitel Networks Corporation (Canada)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Avaya Holdings Corp. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Vonage Holdings Corp. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Dialpad, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Fuze, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o BT Group plc (UK)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Orange S.A. (France)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Alcatel-Lucent Enterprise (France)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o LogMeIn, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Google LLC (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o NEC Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Windstream Holdings, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Telstra Corporation Limited (Australia)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>◦ RingCentral, Inc. (USA)
+◦ 8x8, Inc. (USA)
+◦ Zoom Video Communications, Inc. (USA)
+◦ Microsoft Corporation (USA)
+◦ Cisco Systems, Inc. (USA)
+◦ Verizon Communications Inc. (USA)
+◦ AT&amp;T Inc. (USA)
+◦ Mitel Networks Corporation (Canada)
+◦ Avaya Holdings Corp. (USA)
+◦ Vonage Holdings Corp. (USA)
+◦ Dialpad, Inc. (USA)
+◦ Fuze, Inc. (USA)
+◦ BT Group plc (UK)
+◦ Orange S.A. (France)
+◦ Alcatel-Lucent Enterprise (France)
+◦ LogMeIn, Inc. (USA)
+◦ Google LLC (USA)
+◦ NEC Corporation (Japan)
+◦ Windstream Holdings, Inc. (USA)
+◦ Telstra Corporation Limited (Australia)</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>By Component (Telephony, Unified Messaging, Conferencing, Collaboration Platforms and Applications), By Communication Type (Voice, Video, Messaging, Collaboration), By Delivery Model (Managed Services, Hosted/Cloud Services), By Deployment (Private cloud services, Public cloud services), By Organization size (Small and medium sized enterprises, Large Enterprises), By End-Use (Banking Financial Services and Insurance (BFSI), Healthcare, IT Enabled Services and Telecommunication, Retail and Consumer Goods, Transportation and Logistics, Travel and Hospitality, Automotive, Public Sector, Others)</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>71.1</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>86.32</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>407.23</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>USD Billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Automotive Cyber Security Market Size, Share, and Growth Analysis, By Component (Software, Hardware), By Application (ADAS &amp; safety, Body control &amp; comfort), By Form Type, By Security Type, By Approach, By Vehicle Type, By Propulsion Type, By Vehicle Autonomy, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SQMIG45K2099</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/automotive-cyber-security-market</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Global Automotive Cyber Security Market size was valued at USD 4.3 billion in 2023 and is poised to grow from USD 5.25 billion in 2024 to USD 25.75 billion by 2032, growing at a CAGR of 22.0% during the forecast period (2025-2032).
+The global automotive cybersecurity landscape is witnessing transformative trends driven by the increasing complexity of connected vehicles and a heightened awareness of the need for robust protection against cyber threats. Manufacturers are embedding cybersecurity measures from the design phase of vehicles, recognizing its critical role in the lifecycle of automotive technology that now includes advanced features like infotainment systems, Advanced Driver-Assistance Systems (ADAS), and autonomous driving. Additionally, the rising adoption of over-the-air (OTA) updates signals a proactive shift, allowing automakers to deploy software fixes, enhancements, and security updates remotely. This agile approach enables swift responses to emerging vulnerabilities, highlighting the industry's commitment to maintaining the cybersecurity integrity of vehicles throughout their operational lifespan, thus solidifying demand for reliable OTA update systems.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Automotive Cyber Security market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Automotive Cyber Security Market Segments Analysis
+Global Automotive Cyber Security Market is segmented by Component, Application, Form Type, Security Type, Approach, Vehicle Type, Propulsion Type, Vehicle Autonomy, and region. Based on Component, the market is segmented into Software and Hardware. Based on Application, the market is segmented into ADAS &amp; safety, Body control &amp; comfort, Infotainment, Telematics, Powertrain systems and Communication systems. Based on Form Type, the market is segmented into In-vehicle and External cloud services. Based on Security Type, the market is segmented into Application, Wireless and Endpoint. Based on Approach, the market is segmented into Intrusion Detection System and Security Operations Centre. Based on Vehicle Type, the market is segmented into Passenger Vehicles, Light Commercial Vehicles and Heavy Commercial Vehicles. Based on Propulsion Type, the market is segmented into ICE Vehicles and Electric Vehicles. Based on Vehicle Autonomy, the market is segmented into Non-autonomous Vehicles, Semi-autonomous Vehicles and Autonomous Vehicles. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Automotive Cyber Security Market
+The global automotive cybersecurity market is being propelled by the rising prevalence of connected and autonomous vehicles. These vehicles are equipped with intricate networks and communication systems that are essential for their operation, making them vulnerable to various cyber threats. As the complexity of these systems grows, the necessity for robust cybersecurity measures to protect critical vehicle functions and ensure user safety becomes paramount. This escalating awareness of potential risks associated with cyberattacks is driving a heightened demand for advanced cybersecurity solutions within the automotive industry, as manufacturers and consumers alike seek to safeguard their technology and data.
+Restraints in the Global Automotive Cyber Security Market
+The Global Automotive Cyber Security market faces significant restraints due to the complexities associated with integrating advanced cybersecurity solutions into modern vehicles. The interconnected nature of vehicle systems and the diversity of communication protocols present substantial challenges that necessitate advanced technology and specialized expertise. Achieving a balance between robust cybersecurity measures and maintaining the vehicle's performance becomes a formidable task. These intricacies can contribute to delays in the adoption of cybersecurity measures, ultimately prolonging the timeline for deployment within the automotive industry. As a result, the slow pace of integration hampers the overall progress of enhancing vehicle cybersecurity.
+Market Trends of the Global Automotive Cyber Security Market
+The Global Automotive Cyber Security market is witnessing a transformative trend driven by the surging integration of advanced AI and machine learning technologies. These innovations enhance the vehicle's ability to detect threats in real-time, identify anomalies, and conduct predictive analysis, thus significantly elevating security measures. As the automotive industry shifts towards connected and autonomous vehicles, the demand for AI-driven cybersecurity solutions grows in response to increasingly complex challenges. This evolution not only reinforces vehicle safety but also propels market growth, reflecting a promising future for automotive cybersecurity as manufacturers prioritize robust protective measures in their designs.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Technology Analysis
+• Global Automotive Cyber Security Market Size by Component &amp; CAGR (2025-2032)
+o Market Overview
+o Software
+o Hardware
+• Global Automotive Cyber Security Market Size by Application &amp; CAGR (2025-2032)
+o Market Overview
+o ADAS &amp; safety
+o Body control &amp; comfort
+o Infotainment
+o Telematics
+o Powertrain systems
+o Communication systems
+o Others
+• Global Automotive Cyber Security Market Size by Form Type &amp; CAGR (2025-2032)
+o Market Overview
+o In-vehicle
+o External cloud services
+• Global Automotive Cyber Security Market Size by Security Type &amp; CAGR (2025-2032)
+o Market Overview
+o Application
+o Wireless
+o Endpoint
+• Global Automotive Cyber Security Market Size by Approach &amp; CAGR (2025-2032)
+o Market Overview
+o Intrusion Detection System
+o Security Operations Centre
+• Global Automotive Cyber Security Market Size by Vehicle Type &amp; CAGR (2025-2032)
+o Market Overview
+o Passenger Vehicles
+o Light Commercial Vehicles
+o Heavy Commercial Vehicles
+• Global Automotive Cyber Security Market Size by Propulsion Type &amp; CAGR (2025-2032)
+o Market Overview
+o ICE Vehicles
+o Electric Vehicles
+• Global Automotive Cyber Security Market Size by Vehicle Autonomy &amp; CAGR (2025-2032)
+o Market Overview
+o Non-autonomous Vehicles
+o Semi-autonomous Vehicles
+o Autonomous Vehicles
+• Global Automotive Cyber Security Market Size &amp; CAGR (2025-2032)
+o North America (Component, Application, Form Type, Security Type, Approach, Vehicle Type, Propulsion Type, Vehicle Autonomy)
+ US
+ Canada
+o Europe (Component, Application, Form Type, Security Type, Approach, Vehicle Type, Propulsion Type, Vehicle Autonomy)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Component, Application, Form Type, Security Type, Approach, Vehicle Type, Propulsion Type, Vehicle Autonomy)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Component, Application, Form Type, Security Type, Approach, Vehicle Type, Propulsion Type, Vehicle Autonomy)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Component, Application, Form Type, Security Type, Approach, Vehicle Type, Propulsion Type, Vehicle Autonomy)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Continental AG (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Robert Bosch GmbH (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Harman International (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Denso Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Aptiv PLC (Ireland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o NXP Semiconductors (Netherlands)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Infineon Technologies AG (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Upstream Security Ltd. (Israel)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Karamba Security (Israel)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Argus Cyber Security Ltd. (Israel)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o SafeRide Technologies (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Vector Informatik GmbH (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Green Hills Software (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Intel Corporation (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Lear Corporation (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Garrett Motion Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o BlackBerry Limited (Canada)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Capgemini S.E. (France)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Trend Micro Incorporated (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o ETAS GmbH (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>◦ Continental AG (Germany)
+◦ Robert Bosch GmbH (Germany)
+◦ Harman International (USA)
+◦ Denso Corporation (Japan)
+◦ Aptiv PLC (Ireland)
+◦ NXP Semiconductors (Netherlands)
+◦ Infineon Technologies AG (Germany)
+◦ Upstream Security Ltd. (Israel)
+◦ Karamba Security (Israel)
+◦ Argus Cyber Security Ltd. (Israel)
+◦ SafeRide Technologies (USA)
+◦ Vector Informatik GmbH (Germany)
+◦ Green Hills Software (USA)
+◦ Intel Corporation (USA)
+◦ Lear Corporation (USA)
+◦ Garrett Motion Inc. (USA)
+◦ BlackBerry Limited (Canada)
+◦ Capgemini S.E. (France)
+◦ Trend Micro Incorporated (Japan)
+◦ ETAS GmbH (Germany)</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>By Component (Software, Hardware), By Application (ADAS &amp; safety, Body control &amp; comfort, Infotainment, Telematics, Powertrain systems, Communication systems), By Form Type (In-vehicle, External cloud services), By Security Type (Application, Wireless, Endpoint), By Approach (Intrusion Detection System, Security Operations Centre), By Vehicle Type (Passenger Vehicles, Light Commercial Vehicles, Heavy Commercial Vehicles), By Propulsion Type (ICE Vehicles, Electric Vehicles), By Vehicle Autonomy (Non-autonomous Vehicles, Semi-autonomous Vehicles, Autonomous Vehicles)</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>25.75</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>22.0%</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>USD Billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Bone Growth Stimulators Market Size, Share, and Growth Analysis, By Material Type (Bone Growth Stimulation Devices, Bone Morphogenetic Proteins), By Application (Spinal Fusion Surgeries, Delayed Union &amp; Nonunion Bone Fractures), By End User, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SQMIG35A2314</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/bone-growth-stimulators-market</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Global Bone Growth Stimulators Market size was valued at USD 2.8 billion in 2023 and is poised to grow from USD 2.96 billion in 2024 to USD 4.57 billion by 2032, growing at a CAGR of 5.6% during the forecast period (2025-2032).
+The bone growth stimulation market is witnessing significant growth, driven by an increasing incidence of bone fractures and sports injuries globally. With around 54 cases of spinal cord injury annually per million people in the U.S., and an estimated 250,000 to 500,000 spinal cord injuries worldwide, demand for bone stimulators is rising. These devices are crucial in cases where fractures do not heal adequately. The technology has advanced Orthopaedic surgeries and has high application in spinal fusion, dentistry, and fracture repair. Furthermore, the ongoing clinical research into bone morphogenetic proteins highlights strong market potential. Coupled with the rising prevalence of osteoarthritis and degenerative bone diseases, the market is also expected to benefit from the growing popularity of platelet-rich plasma and improved healing outcomes.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Bone Growth Stimulators market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Bone Growth Stimulators Market Segments Analysis
+Global Bone Growth Stimulators Market is segmented by Material Type, Application, End User and region. Based on Material Type, the market is segmented into Bone Growth Stimulation Devices, Bone Morphogenetic Proteins and Platelet-Rich Plasma. Based on Application, the market is segmented into Spinal Fusion Surgeries, Delayed Union &amp; Nonunion Bone Fractures, Oral &amp; Maxillofacial Surgeries and Other Applications. Based on End User, the market is segmented into Hospitals and Ambulatory Surgical Centers, Home Care Settings and Academic and Research Institutes. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Bone Growth Stimulators Market
+The Global Bone Growth Stimulators market is significantly driven by the increasing occurrence of orthopedic disorders, including fractures, delayed unions, non-unions, and fractures resulting from osteoporosis. As the population ages, the prevalence of these orthopedic issues is on the rise, leading to a heightened demand for effective treatment options such as bone growth stimulators. This trend reflects a broader understanding of the necessity for advanced therapeutic interventions that cater to the needs of individuals suffering from these conditions, thereby propelling market growth and innovation in the development of bone growth stimulation technologies.
+Restraints in the Global Bone Growth Stimulators Market
+The Global Bone Growth Stimulators market faces certain limitations primarily due to potential side effects and risks linked to their usage. Although these stimulators are largely deemed safe, issues such as skin irritation, allergic reactions, and discomfort during treatments can arise. These concerns may lead to hesitation among patients and healthcare professionals alike, potentially discouraging them from opting for bone growth stimulators. As a result, the perceived risk of adverse effects could hinder market growth and adoption rates, impacting the overall acceptance of these devices within the medical community and among patients seeking effective treatment options.
+Market Trends of the Global Bone Growth Stimulators Market
+The Global Bone Growth Stimulators market is witnessing a significant shift towards non-invasive treatment options, driven by an increasing demand for patient-friendly solutions. As healthcare providers and patients alike prioritize comfort and minimally invasive procedures, bone growth stimulators have gained traction as effective alternatives to traditional surgical interventions. This trend is particularly pronounced in orthopedic applications, such as spinal fusion and fracture repairs, where the emphasis on faster recovery and reduced complications aligns with the broader healthcare movement towards safer and more efficient therapeutic modalities. Such developments are expected to propel market growth and innovation in the coming years.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+• Global Bone Growth Stimulators Market Size by Material Type &amp; CAGR (2025-2032)
+o Market Overview
+o Bone Growth Stimulation Devices
+ External Bone Growth Stimulators
+ Ultrasonic Bone Growth Stimulators
+ Implanted Bone Growth Stimulators
+o Bone Morphogenetic Proteins
+o Platelet-Rich Plasma
+• Global Bone Growth Stimulators Market Size by Application &amp; CAGR (2025-2032)
+o Market Overview
+o Spinal Fusion Surgeries
+o Delayed Union &amp; Nonunion Bone Fractures
+o Oral &amp; Maxillofacial Surgeries
+o Other Applications
+• Global Bone Growth Stimulators Market Size by End User &amp; CAGR (2025-2032)
+o Market Overview
+o Hospitals and Ambulatory Surgical Centers
+o Home Care Settings
+o Academic and Research Institutes
+• Global Bone Growth Stimulators Market Size &amp; CAGR (2025-2032)
+o North America (Material Type, Application, End User)
+ US
+ Canada
+o Europe (Material Type, Application, End User)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Material Type, Application, End User)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Material Type, Application, End User)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Material Type, Application, End User)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Orthofix Holdings, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Medtronic plc (Ireland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Zimmer Biomet Holdings, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Stryker Corporation (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Terumo Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Bioventus LLC (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Igea S.p.A. (Italy)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Ossatec AS (Norway)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Biotronik SE &amp; Co. KG (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o DJO Global, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o EMS Physio Ltd. (UK)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Orthocell Ltd. (Australia)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Altis Biologics (South Africa)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o ISTO Biologics (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Regenlab SA (Switzerland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Exactech, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Collagen Matrix, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o ATEC, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>◦ Orthofix Holdings, Inc. (USA)
+◦ Medtronic plc (Ireland)
+◦ Zimmer Biomet Holdings, Inc. (USA)
+◦ Stryker Corporation (USA)
+◦ Terumo Corporation (Japan)
+◦ Bioventus LLC (USA)
+◦ Igea S.p.A. (Italy)
+◦ Ossatec AS (Norway)
+◦ Biotronik SE &amp; Co. KG (Germany)
+◦ DJO Global, Inc. (USA)
+◦ EMS Physio Ltd. (UK)
+◦ Orthocell Ltd. (Australia)
+◦ Altis Biologics (South Africa)
+◦ ISTO Biologics (USA)
+◦ Regenlab SA (Switzerland)
+◦ Exactech, Inc. (USA)
+◦ Collagen Matrix, Inc. (USA)
+◦ ATEC, Inc. (USA)</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>By Material Type (Bone Growth Stimulation Devices, Bone Morphogenetic Proteins, Platelet-Rich Plasma), By Application (Spinal Fusion Surgeries, Delayed Union &amp; Nonunion Bone Fractures, Oral &amp; Maxillofacial Surgeries, Other Applications), By End User (Hospitals and Ambulatory Surgical Centers, Home Care Settings, Academic and Research Institutes)</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>5.6%</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>USD Billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Automotive Infotainment Market Size, Share, and Growth Analysis, By Product (Audio unit, Display unit), By Installation Type (In-dash infotainment, Rear seat infotainment), By Vehicle, By Operating System, By Distribution Channel, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SQMIG25A2137</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/automotive-infotainment-market</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Global Automotive Infotainment Market size was valued at USD 8.8 billion in 2023 and is poised to grow from USD 9.72 billion in 2024 to USD 21.44 billion by 2032, growing at a CAGR of 10.4% during the forecast period (2025-2032).
+Demand for tech-savvy vehicles in developing nations is surging, fueled by rising disposable incomes and accessible financing options. Consumers are increasingly drawn to modern features, prompting automakers to enhance car technology beyond entertainment systems. Companies are integrating advanced safety features like driver assistance systems and augmented reality displays, benefiting from the growth of the Internet of Things (IoT). However, the COVID-19 pandemic disrupted supply chains, leading to vehicle shortages and a semiconductor crisis, forcing manufacturers like BMW to scale back features to maintain production. As safety technologies advance, including digital monitoring systems and real-time data analytics, the car infotainment market is poised for growth. This blend of innovation and data collection underscores a transformative shift in the automotive landscape.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Automotive Infotainment market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Automotive Infotainment Market Segments Analysis
+Global Automotive Infotainment Market is segmented by Product, Installation Type, Vehicle, Operating System, Distribution Channel and region. Based on Product, the market is segmented into Audio unit, Display unit, Heads-up display, Navigation unit and Communication unit. Based on Installation Type, the market is segmented into In-dash infotainment and Rear seat infotainment. Based on Vehicle, the market is segmented into Passenger cars, Light Commercial Vehicles (LCVs) and Heavy Commercial Vehicles (HCVs). Based on Operating System, the market is segmented into QNX, Linux, Microsoft and Others. Based on Distribution Channel, the market is segmented into OEM and Aftermarket. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Automotive Infotainment Market
+A key factor propelling the global automotive infotainment market is the surging demand for advanced in-car entertainment systems. Modern consumers are seeking solutions that provide superior audio and video quality, effortless connectivity, and intuitive user interfaces. As vehicle owners increasingly prioritize entertainment during travel, the need for sophisticated infotainment options continues to rise, driving manufacturers to innovate and enhance their offerings. This growing consumer preference for high-performance infotainment solutions is reshaping the automotive landscape and encouraging investment in technology that delivers enjoyable and engaging driving experiences. Consequently, this trend is significantly influencing the overall growth of the industry.
+Restraints in the Global Automotive Infotainment Market
+A significant challenge facing the global automotive infotainment market is the elevated cost associated with advanced infotainment systems. Developing and integrating cutting-edge technologies, such as artificial intelligence (AI) and augmented reality (AR), requires substantial investment, driving up the overall cost of these systems. This high pricing can limit accessibility for a considerable portion of consumers, ultimately hindering widespread adoption and growth in the market. As a result, manufacturers may struggle to find a balance between innovation and affordability, impacting their ability to capture a larger share of the market while keeping consumer interests in mind.
+Market Trends of the Global Automotive Infotainment Market
+The Global Automotive Infotainment market is witnessing a significant surge due to the escalating demand for connected cars. As consumers increasingly seek enhanced in-vehicle experiences, automotive manufacturers are prioritizing the integration of advanced infotainment systems that facilitate seamless connectivity with entertainment, navigation, and communication services. This trend is driven by the rise of smart technology and consumer expectations for personalization and convenience. Additionally, the shift towards electric vehicles and autonomous driving is further propelling the need for sophisticated infotainment solutions, positioning the automotive infotainment market for robust growth in the coming years as manufacturers innovate to meet evolving consumer needs.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Technology Analysis
+• Global Automotive Infotainment Market Size by Product &amp; CAGR (2025-2032)
+o Market Overview
+o Audio unit
+o Display unit
+o Heads-up display
+o Navigation unit
+o Communication unit
+• Global Automotive Infotainment Market Size by Installation Type &amp; CAGR (2025-2032)
+o Market Overview
+o In-dash infotainment
+o Rear seat infotainment
+• Global Automotive Infotainment Market Size by Vehicle &amp; CAGR (2025-2032)
+o Market Overview
+o Passenger cars
+o Light Commercial Vehicles (LCVs)
+o Heavy Commercial Vehicles (HCVs)
+• Global Automotive Infotainment Market Size by Operating System &amp; CAGR (2025-2032)
+o Market Overview
+o QNX
+o Linux
+o Microsoft
+o Others
+• Global Automotive Infotainment Market Size by Distribution Channel &amp; CAGR (2025-2032)
+o Market Overview
+o OEM
+o Aftermarket
+• Global Automotive Infotainment Market Size &amp; CAGR (2025-2032)
+o North America (Product, Installation Type, Vehicle, Operating System, Distribution Channel)
+ US
+ Canada
+o Europe (Product, Installation Type, Vehicle, Operating System, Distribution Channel)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Product, Installation Type, Vehicle, Operating System, Distribution Channel)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Product, Installation Type, Vehicle, Operating System, Distribution Channel)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Product, Installation Type, Vehicle, Operating System, Distribution Channel)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Harman International (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Continental AG (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Robert Bosch GmbH (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Alpine Electronics, Inc. (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Denso Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Visteon Corporation (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Panasonic Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Pioneer Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Clarion Co., Ltd. (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Hyundai Mobis (South Korea)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o LG Electronics (South Korea)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Desay SV Automotive (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Faurecia (France)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Aptiv PLC (Ireland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o TomTom NV (Netherlands)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o NVIDIA Corporation (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Qualcomm Incorporated (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Texas Instruments Incorporated (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Elektrobit (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Cerence Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>◦ Harman International (USA)
+◦ Continental AG (Germany)
+◦ Robert Bosch GmbH (Germany)
+◦ Alpine Electronics, Inc. (Japan)
+◦ Denso Corporation (Japan)
+◦ Visteon Corporation (USA)
+◦ Panasonic Corporation (Japan)
+◦ Pioneer Corporation (Japan)
+◦ Clarion Co., Ltd. (Japan)
+◦ Hyundai Mobis (South Korea)
+◦ LG Electronics (South Korea)
+◦ Desay SV Automotive (China)
+◦ Faurecia (France)
+◦ Aptiv PLC (Ireland)
+◦ TomTom NV (Netherlands)
+◦ NVIDIA Corporation (USA)
+◦ Qualcomm Incorporated (USA)
+◦ Texas Instruments Incorporated (USA)
+◦ Elektrobit (Germany)
+◦ Cerence Inc. (USA)</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>By Product (Audio unit, Display unit, Heads-up display, Navigation unit), By Installation Type (In-dash infotainment, Rear seat infotainment), By Vehicle (Passenger cars, Light Commercial Vehicles (LCVs), Heavy Commercial Vehicles (HCVs)), By Operating System (QNX, Linux, Microsoft, Others), By Distribution Channel (OEM, Aftermarket)</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>9.72</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>21.44</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>10.4%</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>USD Billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Corporate E-Learning Market Size, Share, and Growth Analysis, By Training Type (Custom e-Learning, Responsive e-Learning), By Courses (Self-Paced Courses, Instructor-Led Virtual Courses), By Technology, By Learning method, By End-user, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SQMIG45A2101</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/corporate-elearning-market</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Global Corporate E-Learning Market size was valued at USD 104.8 billion in 2023 and is poised to grow from USD 120.31 billion in 2024 to USD 362.94 billion by 2032, growing at a CAGR of 14.8% during the forecast period (2025-2032).
+The corporate e-learning landscape is witnessing a surge in the adoption of customized learning solutions, driven by the need to engage employees and enhance knowledge retention. Organizations are leveraging learning analytics and artificial intelligence to analyze performance data, enabling personalized content that addresses skill gaps. A notable shift towards mobile learning provides employees with flexible training options, crucial for remote work environments. The concept of lifelong learning is being reinforced through easy access to training materials, fostering on-demand learning capabilities. Microlearning strategies, which break down complex topics into concise segments, are gaining traction, particularly in mobile formats. Additionally, the integration of augmented and virtual reality technologies, along with the rise of social learning components, signifies a transformative evolution in corporate e-learning. The US Corporate eLearning Market is projected to sustain a healthy growth rate in the coming years.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Corporate E-Learning market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Corporate E-Learning Market Segments Analysis
+Global Corporate E-Learning Market is segmented by Training Type, Courses, Technology, Learning method, End-user and region. Based on Training Type, the market is segmented into Custom e-Learning, Responsive e-Learning, Micro e-Learning, Translation &amp; Localization, Game-Based Learning and Rapid e-Learning. Based on Courses, the market is segmented into Self-Paced Courses and Instructor-Led Virtual Courses. Based on Technology, the market is segmented into Artificial Intelligence, Augmented Reality and Virtual Reality, Big Data and Cloud Computing. Based on Learning method, the market is segmented into Blended Learning, Mobile Learning, Virtual Classrooms and Simulation. Based on End-user, the market is segmented into Academic, Corporate and Government. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Corporate E-Learning Market
+The Global Corporate E-Learning market is driven by the flexibility it offers employees in terms of time and location, making it an attractive online training solution for organizations with a worldwide presence. This adaptability accommodates a diverse array of learners, including those situated in different time zones or with varying schedules. As a result, corporate e-learning enhances both accessibility and engagement in training programs, leading to higher participation rates. The ability to learn anytime and anywhere not only caters to the unique needs of individuals but also fosters a more inclusive learning environment, ultimately benefiting organizations in their training initiatives.
+Restraints in the Global Corporate E-Learning Market
+The primary challenges hindering the growth of the global corporate e-learning market are the potential risks associated with data security and privacy. As sensitive employee information is shared and stored within these platforms, the threat of cybersecurity issues, including unauthorized access and data breaches, becomes a significant concern. Consequently, businesses must implement robust measures to safeguard user data and protect their intellectual property, creating additional responsibilities and costs for organizations involved in corporate e-learning. Addressing these security challenges is essential to instill trust in the system and ensure the continued growth of this burgeoning market.
+Market Trends of the Global Corporate E-Learning Market
+The global corporate e-learning market is increasingly trending towards the integration of artificial intelligence (AI) and machine learning technologies to create personalized learning experiences. Organizations are leveraging these advanced tools to analyze individual learner behaviors, preferences, and performance metrics, enabling the dynamic adjustment of training materials tailored to each employee's specific needs. This shift not only enhances engagement but also maximizes training effectiveness by ensuring that content resonates with learners on a personal level. As companies continue to prioritize personalized training solutions, the demand for AI-powered e-learning platforms is projected to grow significantly, reshaping the corporate training landscape.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Technology Analysis
+• Global Corporate E-Learning Market Size by Training Type &amp; CAGR (2025-2032)
+o Market Overview
+o Custom e-Learning
+o Responsive e-Learning
+o Micro e-Learning
+o Translation &amp; Localization
+o Game-Based Learning
+o Rapid e-Learning
+• Global Corporate E-Learning Market Size by Courses &amp; CAGR (2025-2032)
+o Market Overview
+o Self-Paced Courses
+o Instructor-Led Virtual Courses
+• Global Corporate E-Learning Market Size by Technology &amp; CAGR (2025-2032)
+o Market Overview
+o Artificial Intelligence
+o Augmented Reality and Virtual Reality
+o Big Data
+o Cloud Computing
+• Global Corporate E-Learning Market Size by Learning method &amp; CAGR (2025-2032)
+o Market Overview
+o Blended Learning
+o Mobile Learning
+o Virtual Classrooms
+o Simulation
+• Global Corporate E-Learning Market Size by End-user &amp; CAGR (2025-2032)
+o Market Overview
+o Academic
+o Corporate
+o Government
+• Global Corporate E-Learning Market Size &amp; CAGR (2025-2032)
+o North America (Training Type, Courses, Technology, Learning method, End-user)
+ US
+ Canada
+o Europe (Training Type, Courses, Technology, Learning method, End-user)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Training Type, Courses, Technology, Learning method, End-user)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Training Type, Courses, Technology, Learning method, End-user)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Training Type, Courses, Technology, Learning method, End-user)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Adobe Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o SAP SE (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Oracle Corporation (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Skillsoft Corp. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Cornerstone OnDemand, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Docebo Inc. (Canada)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Udemy, Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o LinkedIn Learning (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Articulate Global, LLC. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Tata Interactive Systems (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o GP Strategies Corporation (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o City &amp; Guilds Group (UK)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Allen Interactions Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o EI Design (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o SweetRush Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Saba Software (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Learning Technologies Group plc (UK)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Niit Limited (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Kaltura Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Desire2Learn (D2L) Corporation (Canada)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>◦ Adobe Inc. (USA)
+◦ SAP SE (Germany)
+◦ Oracle Corporation (USA)
+◦ Skillsoft Corp. (USA)
+◦ Cornerstone OnDemand, Inc. (USA)
+◦ Docebo Inc. (Canada)
+◦ Udemy, Inc. (USA)
+◦ LinkedIn Learning (USA)
+◦ Articulate Global, LLC. (USA)
+◦ Tata Interactive Systems (India)
+◦ GP Strategies Corporation (USA)
+◦ City &amp; Guilds Group (UK)
+◦ Allen Interactions Inc. (USA)
+◦ EI Design (India)
+◦ SweetRush Inc. (USA)
+◦ Saba Software (USA)
+◦ Learning Technologies Group plc (UK)
+◦ Niit Limited (India)
+◦ Kaltura Inc. (USA)
+◦ Desire2Learn (D2L) Corporation (Canada)</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>By Training Type (Custom e-Learning, Responsive e-Learning, Micro e-Learning, Translation &amp; Localization, Game-Based Learning, Rapid e-Learning), By Courses (Self-Paced Courses, Instructor-Led Virtual Courses), By Technology (Artificial Intelligence, Augmented Reality and Virtual Reality, Big Data, Cloud Computing), By Learning method (Blended Learning, Mobile Learning, Virtual Classrooms, Simulation), By End-user (Academic, Corporate, Government)</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>104.8</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>120.31</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>362.94</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>14.8%</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>USD Billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Analytics Outsourcing Market Size, Share, and Growth Analysis, By Service Type (Descriptive Analytics, Predictive Analytics), By Deployment Model (On-premises, Cloud-based), By Industry Vertical, By Data Source, By Organization Size, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SQMIG45B2062</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/data-analytics-outsourcing-market</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Global Data Analytics Outsourcing Market size was valued at USD 19.8 billion in 2023 and is poised to grow from USD 26.69 billion in 2024 to USD 290.99 billion by 2032, growing at a CAGR of 34.8% during the forecast period (2025-2032).
+The data analytics outsourcing market is experiencing rapid growth, driven by the increasing demand for faster data interpretation and the widespread adoption of cloud-based analytical tools. The shortage of skilled data analysts further fuels this trend, while advancements in AI and machine learning technologies enhance the ability to analyze complex datasets efficiently. Both small and large organizations can benefit from cost-effective, usage-based data analytics services. Key market drivers include the surge in businesses generating vast amounts of intricate data and the growing necessity for data-driven decision-making to improve efficiency and cut costs. Additionally, innovations in self-service analysis software and on-demand data analysis services present new opportunities for exploration. The US data analytics outsourcing market is expected to maintain a sustainable CAGR in the upcoming forecast year.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Data Analytics Outsourcing market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Data Analytics Outsourcing Market Segments Analysis
+Global Data Analytics Outsourcing Market is segmented by Service Type, Deployment Model, Industry Vertical, Data Source, Organization Size and region. Based on Service Type, the market is segmented into Descriptive Analytics, Predictive Analytics and Prescriptive Analytics. Based on Deployment Model, the market is segmented into On-premises, Cloud-based and Hybrid. Based on Industry Vertical, the market is segmented into Financial Services, Healthcare, Retail and Manufacturing. Based on Data Source, the market is segmented into Structured Data, Unstructured Data and Semi-structured Data. Based on Organization Size, the market is segmented into Small and Medium-sized Enterprises (SMEs) and Large Enterprises. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Data Analytics Outsourcing Market
+As organizations across various industries increasingly acknowledge the critical role of data in shaping their strategic initiatives, the demand for data analytics outsourcing is surging. Companies are eager to leverage advanced analytics to enhance their operational efficiency, improve service offerings, and sustain a competitive advantage in the marketplace. This rising inclination towards data-driven decision-making is driving the growth of the global data analytics outsourcing market. Consequently, businesses are seeking external expertise to harness the power of analytics, leading to a robust expansion of this sector as they strive for innovation and excellence in their operations.
+Restraints in the Global Data Analytics Outsourcing Market
+A significant challenge in the Global Data Analytics Outsourcing market is the high demand for advanced analytics and data science experts, which currently exceeds the supply of qualified professionals. The increasing requirement for skills in machine learning, artificial intelligence, and big data analytics creates a competitive landscape where companies struggle to find suitable talent. This shortage of skilled workers hampers the overall effectiveness and potential of outsourcing initiatives, as firms are unable to fully leverage the benefits of advanced data analytics. Consequently, this talent gap acts as a restraint on the growth and progress of the outsourcing market in this domain.
+Market Trends of the Global Data Analytics Outsourcing Market
+The Global Data Analytics Outsourcing market is experiencing a robust trend driven by the integration of artificial intelligence (AI) and machine learning technologies. As organizations increasingly seek to leverage data for strategic decision-making, the adoption of these advanced analytics capabilities enhances forecasting accuracy and streamlines complex processes. This shift not only improves data insights but also fosters a competitive advantage in various industries. Consequently, the demand for specialized outsourcing services that offer sophisticated analytic solutions is rising, indicating a pivotal transition towards more innovative and efficient data management practices in a landscape characterized by rapid technological advancements.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Technology Analysis
+• Global Data Analytics Outsourcing Market Size by Service Type &amp; CAGR (2025-2032)
+o Market Overview
+o Descriptive Analytics
+o Predictive Analytics
+o Prescriptive Analytics
+• Global Data Analytics Outsourcing Market Size by Deployment Model &amp; CAGR (2025-2032)
+o Market Overview
+o On-premises
+o Cloud-based
+o Hybrid
+• Global Data Analytics Outsourcing Market Size by Industry Vertical &amp; CAGR (2025-2032)
+o Market Overview
+o Financial Services
+o Healthcare
+o Retail
+o Manufacturing
+• Global Data Analytics Outsourcing Market Size by Data Source &amp; CAGR (2025-2032)
+o Market Overview
+o Structured Data
+o Unstructured Data
+o Semi-structured Data
+• Global Data Analytics Outsourcing Market Size by Organization Size &amp; CAGR (2025-2032)
+o Market Overview
+o Small and Medium-sized Enterprises (SMEs)
+o Large Enterprises
+• Global Data Analytics Outsourcing Market Size &amp; CAGR (2025-2032)
+o North America (Service Type, Deployment Model, Industry Vertical, Data Source, Organization Size)
+ US
+ Canada
+o Europe (Service Type, Deployment Model, Industry Vertical, Data Source, Organization Size)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Service Type, Deployment Model, Industry Vertical, Data Source, Organization Size)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Service Type, Deployment Model, Industry Vertical, Data Source, Organization Size)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Service Type, Deployment Model, Industry Vertical, Data Source, Organization Size)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Accenture (Ireland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o IBM (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Capgemini (France)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Wipro (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Tata Consultancy Services (TCS) (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Infosys (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Cognizant (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Genpact (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Deloitte (UK)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Ernst &amp; Young (EY) (UK)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o PricewaterhouseCoopers (PwC) (UK)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o KPMG (Netherlands)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Mu Sigma (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Fractal Analytics (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o EXL Service (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o WNS Global Services (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Quantiphi (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o LatentView Analytics (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Cartesian Consulting (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Absolutdata Analytics (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>◦ Accenture (Ireland)
+◦ IBM (USA)
+◦ Capgemini (France)
+◦ Wipro (India)
+◦ Tata Consultancy Services (TCS) (India)
+◦ Infosys (India)
+◦ Cognizant (USA)
+◦ Genpact (USA)
+◦ Deloitte (UK)
+◦ Ernst &amp; Young (EY) (UK)
+◦ PricewaterhouseCoopers (PwC) (UK)
+◦ KPMG (Netherlands)
+◦ Mu Sigma (USA)
+◦ Fractal Analytics (USA)
+◦ EXL Service (USA)
+◦ WNS Global Services (India)
+◦ Quantiphi (USA)
+◦ LatentView Analytics (India)
+◦ Cartesian Consulting (India)
+◦ Absolutdata Analytics (USA)</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>By Service Type (Descriptive Analytics, Predictive Analytics, Prescriptive Analytics), By Deployment Model (On-premises, Cloud-based, Hybrid), By Industry Vertical (Financial Services, Healthcare, Retail, Manufacturing), By Data Source (Structured Data, Unstructured Data, Semi-structured Data), By Organization Size (Small and Medium-sized Enterprises (SMEs), Large Enterprises)</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>26.69</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>290.99</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>USD Billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Armored Vehicles Market Size, Share, and Growth Analysis, By Platform (Combat Vehicles, Combat Support Vehicles), By Mobility (Wheeled, Tracked), By Type, By Mode Of Operation, By System, By Region - Industry Forecast 2025-2032</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SQMIG20A2235</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.skyquestt.com/report/armored-vehicles-market</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Global Armored Vehicles Market size was valued at USD 44.2 billion in 2023 and is poised to grow from USD 45.79 billion in 2024 to USD 60.77 billion by 2032, growing at a CAGR of 3.6% during the forecast period (2025-2032).
+The armored vehicle market is anticipated to grow, driven by an increased demand for bulletproof vehicles and the ongoing militarization of law enforcement. However, expansion is challenged in various countries due to reduced national defense budgets. Opportunities for growth exist through the development of modular armored vehicles and integration of unmanned combat systems. Armored vehicles, which provide critical protection against bullets and other projectiles, play vital roles in both military and civilian applications. Military capabilities are enhanced through versatile deployment options like wheeled or tracked variations, vital for logistical operations, combat, and reconnaissance. While main battle tanks deliver significant firepower, armored personnel carriers and infantry combat vehicles ensure troop safety and mobility, making them indispensable for ground forces.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Armored Vehicles market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Armored Vehicles Market Segments Analysis
+Global Armored Vehicles Market is segmented by Platform, Mobility, Type, Mode Of Operation, System and region. Based on Platform, the market is segmented into Combat Vehicles, Combat Support Vehicles and Unmanned Armored Ground Vehicles. Based on Mobility, the market is segmented into Wheeled and Tracked. Based on Type, the market is segmented into Electric Armored Vehicles and Conventional Armored Vehicles. Based on Mode Of Operation, the market is segmented into Manned Armored Vehicles and Unmanned Armored Vehicles. Based on System, the market is segmented into Drive Systems, Structures &amp; Mechanisms, Weapons &amp; Ammunition Control Systems, Countermeasure Systems, Command &amp; Control Systems, Navigation Systems, Observation &amp; Display Systems and Others. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Armored Vehicles Market
+The analysis of the global armored vehicles market reveals that rising geopolitical tensions and regional conflicts significantly drive market demand. Nations are investing heavily in advanced military technology to improve their troops' operational effectiveness and, most critically, to protect their forces while achieving mission objectives in hostile environments. This strategic focus has led to an increased emphasis on upgrading current armored vehicle fleets and expanding the number of active units. Consequently, the combined effects of these factors are compelling governments to allocate substantial resources toward enhancing their military capabilities in response to evolving security challenges.
+Restraints in the Global Armored Vehicles Market
+The global armored vehicles market faces significant constraints due to the uneven adoption of advanced technologies across different regions. While contemporary armored vehicles are equipped with numerous high-tech features, some areas struggle to implement these advancements due to a lack of required skills and infrastructural support. This technological gap hinders the progress and modernization of armored vehicle capabilities, particularly in developing economies where growth trends and adoption rates are on the rise. As a result, this disparity creates a barrier to fully realizing the potential of modern armored vehicles in emerging markets.
+Market Trends of the Global Armored Vehicles Market
+The global armored vehicles market is experiencing a robust trend toward hybrid and electric-powered vehicles, driven by increasing environmental consciousness and the need for operational efficiency. Manufacturers are prioritizing sustainable energy solutions in vehicle design, resulting in reduced fuel consumption and lower maintenance costs. This shift not only addresses ecological concerns but also enhances the longevity and cost-effectiveness of the vehicles. As defense budgets around the world adapt to green technologies, the demand for advanced, eco-friendly armored solutions is poised to redefine industry standards, ensuring that both military and civilian applications align with modern sustainability goals.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>• Introduction
+o Objectives of the Study
+o Scope of the Report
+o Definitions
+• Research Methodology
+o Information Procurement
+o Secondary &amp; Primary Data Methods
+o Market Size Estimation
+o Market Assumptions &amp; Limitations
+• Executive Summary
+o Global Market Outlook
+o Supply &amp; Demand Trend Analysis
+o Segmental Opportunity Analysis
+• Market Dynamics &amp; Outlook
+o Market Overview
+o Market Size
+o Market Dynamics
+ Drivers &amp; Opportunities
+ Restraints &amp; Challenges
+o Porters Analysis
+ Competitive rivalry
+ Threat of substitute
+ Bargaining power of buyers
+ Threat of new entrants
+ Bargaining power of suppliers
+• Key Market Insights
+o Key Success Factors
+o Degree of Competition
+o Top Investment Pockets
+o Market Ecosystem
+o Market Attractiveness Index, 2024
+o PESTEL Analysis
+o Macro-Economic Indicators
+o Value Chain Analysis
+o Pricing Analysis
+o Regulatory Landscape
+o Case Studies
+• Global Armored Vehicles Market Size by Platform &amp; CAGR (2025-2032)
+o Market Overview
+o Combat Vehicles
+o Combat Support Vehicles
+o Unmanned Armored Ground Vehicles
+• Global Armored Vehicles Market Size by Mobility &amp; CAGR (2025-2032)
+o Market Overview
+o Wheeled
+o Tracked
+• Global Armored Vehicles Market Size by Type &amp; CAGR (2025-2032)
+o Market Overview
+o Electric Armored Vehicles
+o Conventional Armored Vehicles
+• Global Armored Vehicles Market Size by Mode Of Operation &amp; CAGR (2025-2032)
+o Market Overview
+o Manned Armored Vehicles
+o Unmanned Armored Vehicles
+• Global Armored Vehicles Market Size by System &amp; CAGR (2025-2032)
+o Market Overview
+o Drive Systems
+o Structures &amp; Mechanisms
+o Weapons &amp; Ammunition Control Systems
+o Countermeasure Systems
+o Command &amp; Control Systems
+o Navigation Systems
+o Observation &amp; Display Systems
+o Others
+• Global Armored Vehicles Market Size &amp; CAGR (2025-2032)
+o North America (Platform, Mobility, Type, Mode Of Operation, System)
+ US
+ Canada
+o Europe (Platform, Mobility, Type, Mode Of Operation, System)
+ Germany
+ Spain
+ France
+ UK
+ Italy
+ Rest of Europe
+o Asia Pacific (Platform, Mobility, Type, Mode Of Operation, System)
+ China
+ India
+ Japan
+ South Korea
+ Rest of Asia-Pacific
+o Latin America (Platform, Mobility, Type, Mode Of Operation, System)
+ Brazil
+ Rest of Latin America
+o Middle East &amp; Africa (Platform, Mobility, Type, Mode Of Operation, System)
+ GCC Countries
+ South Africa
+ Rest of Middle East &amp; Africa
+• Competitive Intelligence
+o Top 5 Player Comparison
+o Market Positioning of Key Players, 2024
+o Strategies Adopted by Key Market Players
+o Recent Developments in the Market
+o Company Market Share Analysis, 2024
+o Company Profiles of All Key Players
+ Company Details
+ Product Portfolio Analysis
+ Company's Segmental Share Analysis
+ Revenue Y-O-Y Comparison (2022-2024)
+• Key Company Profiles
+o Oshkosh Defense (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o BAE Systems (United Kingdom)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o General Dynamics Land Systems (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Rheinmetall AG (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Krauss-Maffei Wegmann (KMW) (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Lockheed Martin (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Hanwha Defense (South Korea)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Nexter Systems (France)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o STREIT Group (United Arab Emirates)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o The Armored Group (TAG) (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Alpine Armoring (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o INKAS Armored Vehicle Manufacturing (Canada)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Plasan (Israel)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Kurganmashzavod (Russia)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Leonardo (Italy)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Elbit Systems (Israel)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o General Motors Defense (United States)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o BAE Systems Hägglunds (Sweden)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Patria (Finland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Thales Group (France)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+• Conclusion &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>◦ USA
+◦ Canada
+◦ Germany
+◦ Spain
+◦ Italy
+◦ France
+◦ UK
+◦ China
+◦ India
+◦ Japan
+◦ South Korea
+◦ Brazil
+◦ GCC Countries
+◦ South Africa</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>◦ Oshkosh Defense (United States)
+◦ BAE Systems (United Kingdom)
+◦ General Dynamics Land Systems (United States)
+◦ Rheinmetall AG (Germany)
+◦ Krauss-Maffei Wegmann (KMW) (Germany)
+◦ Lockheed Martin (United States)
+◦ Hanwha Defense (South Korea)
+◦ Nexter Systems (France)
+◦ STREIT Group (United Arab Emirates)
+◦ The Armored Group (TAG) (United States)
+◦ Alpine Armoring (United States)
+◦ INKAS Armored Vehicle Manufacturing (Canada)
+◦ Plasan (Israel)
+◦ Kurganmashzavod (Russia)
+◦ Leonardo (Italy)
+◦ Elbit Systems (Israel)
+◦ General Motors Defense (United States)
+◦ BAE Systems Hägglunds (Sweden)
+◦ Patria (Finland)
+◦ Thales Group (France)</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>By Platform (Combat Vehicles, Combat Support Vehicles, Unmanned Armored Ground Vehicles), By Mobility (Wheeled, Tracked), By Type (Electric Armored Vehicles, Conventional Armored Vehicles), By Mode Of Operation (Manned Armored Vehicles, Unmanned Armored Vehicles), By System (Drive Systems, Structures &amp; Mechanisms, Weapons &amp; Ammunition Control Systems, Countermeasure Systems, Command &amp; Control Systems, Navigation Systems, Observation &amp; Display Systems, Others)</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>44.2</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>45.79</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>60.77</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>USD Billion</t>
         </is>
       </c>
     </row>

--- a/GII.xlsx
+++ b/GII.xlsx
@@ -544,23 +544,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Airsoft Guns Market Size, Share, and Growth Analysis, By Product Type (Handguns, Rifles), By Mechanism (Spring powered, Electric powered), By Price Range, By Distribution Channel, By Region - Industry Forecast 2025-2032</t>
+          <t>Power Tools Market Size, Share, and Growth Analysis, By Tool Type (Drilling And Fastening Tools, Demolition Tools), By Mode Of Operation (Electric, Pneumatic), By Application, By Region - Industry Forecast 2025-2032</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SQMIG25E2160</t>
+          <t>SQMIG20D2077</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.skyquestt.com/report/airsoft-guns-market%C2%A0</t>
+          <t>https://www.skyquestt.com/report/power-tools-market</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>157</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -581,17 +581,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Airsoft Guns Market size was valued at USD 2.1 billion in 2023 and is poised to grow from USD 2.27 billion in 2024 to USD 4.27 billion by 2032, growing at a CAGR of 8.2% during the forecast period (2025-2032).
-The airsoft guns market is experiencing robust growth, propelled by the rising popularity of recreational shooting and tactical sports. As more consumers engage in airsoft gaming events and competitive leagues, demand for high-quality, realistic airsoft guns is escalating. The market, segmented into electric, gas, and spring-powered models, favors electric airsoft guns (AEGs) for their rapid-fire capability and versatility. Innovations like 3D printing and gas blowback systems are enhancing product realism and durability, attracting both enthusiasts and military training programs. Recent product launches, such as Tokyo Marui's M4A1R and KRYTAC's gas-powered KRISS Vector, exemplify this trend towards advanced, affordable offerings. Despite regulatory hurdles, the market is set for steady growth, driven by technological advancements and an expanding consumer base.
-Top-down and bottom-up approaches were used to estimate and validate the size of the airsoft guns market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
-airsoft guns Market Segments Analysis
-Global Airsoft Guns Market is segmented by Product Type, Mechanism, Price Range, Distribution Channel and region. Based on Product Type, the market is segmented into Handguns, Rifles, Shotgun and Muzzle loading. Based on Mechanism, the market is segmented into Spring powered, Electric powered and Gas powered. Based on Price Range, the market is segmented into Low (up to 100$), Mid (100$-200$) and High (above 300$). Based on Distribution Channel, the market is segmented into Online and Offline. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
-Driver of the airsoft guns Market
-A significant driver of growth in the global airsoft guns market is the rising interest in airsoft sports, competitive tournaments, and military simulation activities. The surge in participation in organized airsoft leagues, coupled with the appeal of adventure tourism and tactical gaming communities, has led to an increased demand for high-performance airsoft guns, as well as essential accessories and realistic training equipment globally. This growing enthusiasm for airsoft as both a recreational activity and a competitive sport is propelling market expansion and fostering innovation in product offerings to meet the needs of passionate players.
-Restraints in the airsoft guns Market
-The airsoft guns market faces several constraints that hinder its growth, primarily due to stringent government regulations and legal limitations imposed in numerous countries. Many areas necessitate licensing, impose import bans, and categorize airsoft guns alongside firearms, creating obstacles for potential buyers. Additionally, concerns regarding public safety, potential weapon misuse, and the realistic appearance of these guns further exacerbate the regulatory challenges. These factors not only discourage consumers from making purchases but also impede the overall expansion of the global airsoft market, creating a complex landscape for manufacturers and retailers alike.
-Market Trends of the airsoft guns Market
-The airsoft guns market is witnessing a notable upward trend fueled by the burgeoning popularity of competitive airsoft sports and MilSim events. This increase in organized tournaments is prompting enthusiasts globally to invest in high-performance, realistic airsoft guns, enhancing their tactical gameplay experience. Additionally, the impact of social media and the integration of e-sports elements into airsoft competitions are broadening the appeal, successfully engaging a younger demographic. As brands innovate and cater to evolving consumer preferences, the market is set to expand further, establishing airsoft not just as a hobby but as a vibrant community-driven sport.</t>
+          <t>Power Tools Market size was valued at USD 37.5 billion in 2023 and is poised to grow from USD 39.68 billion in 2024 to USD 62.29 billion by 2032, growing at a CAGR of 5.8% during the forecast period (2025-2032).
+The power tools market is currently experiencing significant double-digit growth fueled by various factors in both developed and emerging economies. Notably, the rise in public infrastructure projects in markets like Brazil, Russia, India, China, South Africa, and Gulf Cooperation Council (GCC) countries is a key driver. With rapid population growth, nations like China and India are investing heavily in construction, leading to an increased demand for power tools across building, manufacturing, and maintenance sectors. Additionally, pandemic-induced behavioral shifts have spurred consumer interest in DIY projects, boosting sales of tools for home renovations. Looking ahead, anticipated investments in electric vehicle (EV) infrastructure, including 200 new gigafactories by 2030, will significantly elevate the requirement for power tools in this sector.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Power Tools Market size was valued at USD 37.5 billion in 2023 and is poised to grow from USD 39.68 billion in 2024 to USD 62.29 billion by 2032, growing at a CAGR of 5.8% during the forecast period (2025-2032). market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Power Tools Market size was valued at USD 37.5 billion in 2023 and is poised to grow from USD 39.68 billion in 2024 to USD 62.29 billion by 2032, growing at a CAGR of 5.8% during the forecast period (2025-2032). Market Segments Analysis
+Global Power Tools Market is segmented by Tool Type, Mode Of Operation, Application and region. Based on Tool Type, the market is segmented into Drilling And Fastening Tools, Demolition Tools, Sawing And Cutting Tools, Material Removal Tools, Routing Tools and Other Tools. Based on Mode Of Operation, the market is segmented into Electric, Pneumatic and Hydraulic. Based on Application, the market is segmented into Industrial/Professional and Residential/DIY. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Power Tools Market size was valued at USD 37.5 billion in 2023 and is poised to grow from USD 39.68 billion in 2024 to USD 62.29 billion by 2032, growing at a CAGR of 5.8% during the forecast period (2025-2032). Market
+One of the key market drivers for the global power tools market is the increasing demand for efficient and time-saving construction and manufacturing solutions. As urbanization and infrastructure development accelerate worldwide, there is a growing need for advanced power tools that enhance productivity and precision. The rise of DIY culture, particularly among millennials and homeowners seeking to undertake renovations and home improvements, further fuels this demand. Additionally, technological advancements in battery-powered and cordless tools are driving innovation and attracting both professional and amateur users, thus contributing to the market's robust growth forecasted from 2024 to 2032.
+Restraints in the Power Tools Market size was valued at USD 37.5 billion in 2023 and is poised to grow from USD 39.68 billion in 2024 to USD 62.29 billion by 2032, growing at a CAGR of 5.8% during the forecast period (2025-2032). Market
+The Power Tools Market is currently navigating several restraints that could hinder its growth. One significant challenge is the volatility in raw material prices, largely affecting the production of power tools, including power generators. Developed nations such as the United States, the United Kingdom, Japan, China, and India are projected to drive demand; however, fluctuating costs and economic instability pose risks. Many power tools are manufactured using steel, metals, and aluminum, materials that are often not locally sourced, resulting in price variations impacted by exchange rate fluctuations. These rising raw material costs consequently limit the overall growth potential of the market.
+Market Trends of the Power Tools Market size was valued at USD 37.5 billion in 2023 and is poised to grow from USD 39.68 billion in 2024 to USD 62.29 billion by 2032, growing at a CAGR of 5.8% during the forecast period (2025-2032). Market
+The Power Tools Market is experiencing a significant shift as it evolves towards sustainable and versatile solutions, with a market size valued at USD 37.5 billion in 2023, projected to grow to USD 62.29 billion by 2032, reflecting a robust CAGR of 5.8% from 2025 onwards. Leading companies like Atlas Copco AB and Robert Bosch Tool Corporation are at the forefront, introducing green energy technologies and multi-use cordless tools that cater to consumer preferences for lightweight, portable, and highly accurate devices. This demand for high-quality, efficient products drives innovation, positioning disruptive players to capitalize on the evolving landscape of the power tools industry.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -631,53 +631,66 @@
 o Macro-Economic Indicators
 o Value Chain Analysis
 o Pricing Analysis
-o Customer &amp; Buying Criteria Analysis
-• Global Airsoft Guns Market Size by Product Type &amp; CAGR (2025-2032)
+o Regulatory Analysis
+o Technology Analysis
+• Global Power Tools Market Size by Tool Type &amp; CAGR (2025-2032)
 o Market Overview
-o Handguns
-o Rifles
-o Shotgun
-o Muzzle loading
-• Global Airsoft Guns Market Size by Mechanism &amp; CAGR (2025-2032)
+o Drilling And Fastening Tools
+ Drills
+ Impact Drivers
+ Impact Wrenches
+ Screwdrivers And Nutrunners
+o Demolition Tools
+o Sawing And Cutting Tools
+ Jigsaws
+ Reciprocating Saws
+ Circular Saws
+ Band Saws
+ Shears &amp; Nibblers
+o Material Removal Tools
+ Sanders/Polishers/Buffers
+ Air Scalers
+ Grinders
+o Routing Tools
+o Other Tools
+• Global Power Tools Market Size by Mode Of Operation &amp; CAGR (2025-2032)
 o Market Overview
-o Spring powered
-o Electric powered
-o Gas powered
-• Global Airsoft Guns Market Size by Price Range &amp; CAGR (2025-2032)
+o Electric
+ Corded Tools
+ Cordless Tools
+o Pneumatic
+o Hydraulic
+• Global Power Tools Market Size by Application &amp; CAGR (2025-2032)
 o Market Overview
-o Low (up to 100$)
-o Mid (100$-200$)
-o High (above 300$)
-• Global Airsoft Guns Market Size by Distribution Channel &amp; CAGR (2025-2032)
-o Market Overview
-o Online
- E-commerce websites
- Company websites
-o Offline
- Hypermarket/supermarket
- Departmental stores
- Others
-• Global Airsoft Guns Market Size &amp; CAGR (2025-2032)
-o North America (Product Type, Mechanism, Price Range, Distribution Channel)
+o Industrial/Professional
+ Construction
+ Automotive
+ Aerospace
+ Energy
+ Shipbuilding
+ Other Industries
+o Residential/DIY
+• Global Power Tools Market Size &amp; CAGR (2025-2032)
+o North America (Tool Type, Mode Of Operation, Application)
  US
  Canada
-o Europe (Product Type, Mechanism, Price Range, Distribution Channel)
+o Europe (Tool Type, Mode Of Operation, Application)
  Germany
  Spain
  France
  UK
  Italy
  Rest of Europe
-o Asia Pacific (Product Type, Mechanism, Price Range, Distribution Channel)
+o Asia Pacific (Tool Type, Mode Of Operation, Application)
  China
  India
  Japan
  South Korea
  Rest of Asia-Pacific
-o Latin America (Product Type, Mechanism, Price Range, Distribution Channel)
+o Latin America (Tool Type, Mode Of Operation, Application)
  Brazil
  Rest of Latin America
-o Middle East &amp; Africa (Product Type, Mechanism, Price Range, Distribution Channel)
+o Middle East &amp; Africa (Tool Type, Mode Of Operation, Application)
  GCC Countries
  South Africa
  Rest of Middle East &amp; Africa
@@ -693,102 +706,87 @@
  Company's Segmental Share Analysis
  Revenue Y-O-Y Comparison (2022-2024)
 • Key Company Profiles
-o Tokyo Marui Co. Ltd. (Japan)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o G&amp;G Armament Taiwan Ltd. (Taiwan)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Umarex GmbH &amp; Co. KG (Germany)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o ICS Airsoft Inc. (Taiwan)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Lancer Tactical Inc. (USA)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Colt's Manufacturing Company LLC (USA)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Crosman Corporation (USA)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Valken Inc. (USA)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o A&amp;K Airsoft Limited (China)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o HFC/Ballistic Breakthru Gunnery Corporation (Taiwan)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Systema Professional Training Weapon (PTW) (Japan)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o KWA Performance Industries Inc. (USA)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Classic Army (Hong Kong)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o VFC (Vega Force Company) (Taiwan)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o WE Airsoft (Taiwan)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o King Arms (Hong Kong)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o CYMA (China)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Arcturus (Taiwan)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o ASG (ActionSportGames) (Denmark)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o LCT Airsoft (Taiwan)
+o Robert Bosch GmbH (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Techtronic Industries Co. Ltd. (TTI) (Hong Kong)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Makita Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Hilti Corporation (Liechtenstein)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Atlas Copco AB (Sweden)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Snap-on Incorporated (US)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Emerson Electric Co. (US)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Chervon (China) Trading Co. Ltd. (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o TTI (Techtronic Industries) Power Tools (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Danaher Corporation (US)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Ingersoll Rand plc (Ireland)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o FEIN Power Tools Inc. (Germany)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Panasonic Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o KYOCERA Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Yamabiko Corporation (Japan)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Ken Holding Co., Ltd (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Dynabrade Inc. (US)
  Company Overview
  Business Segment Overview
  Financial Updates
@@ -800,7 +798,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -824,51 +822,48 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>◦ Tokyo Marui Co. Ltd. (Japan)
-◦ G&amp;G Armament Taiwan Ltd. (Taiwan)
-◦ Umarex GmbH &amp; Co. KG (Germany)
-◦ ICS Airsoft Inc. (Taiwan)
-◦ Lancer Tactical Inc. (USA)
-◦ Colt's Manufacturing Company LLC (USA)
-◦ Crosman Corporation (USA)
-◦ Valken Inc. (USA)
-◦ A&amp;K Airsoft Limited (China)
-◦ HFC/Ballistic Breakthru Gunnery Corporation (Taiwan)
-◦ Systema Professional Training Weapon (PTW) (Japan)
-◦ KWA Performance Industries Inc. (USA)
-◦ Classic Army (Hong Kong)
-◦ VFC (Vega Force Company) (Taiwan)
-◦ WE Airsoft (Taiwan)
-◦ King Arms (Hong Kong)
-◦ CYMA (China)
-◦ Arcturus (Taiwan)
-◦ ASG (ActionSportGames) (Denmark)
-◦ LCT Airsoft (Taiwan)</t>
+          <t>◦ Robert Bosch GmbH (Germany)
+◦ Techtronic Industries Co. Ltd. (TTI) (Hong Kong)
+◦ Makita Corporation (Japan)
+◦ Hilti Corporation (Liechtenstein)
+◦ Atlas Copco AB (Sweden)
+◦ Snap-on Incorporated (US)
+◦ Emerson Electric Co. (US)
+◦ Chervon (China) Trading Co. Ltd. (China)
+◦ TTI (Techtronic Industries) Power Tools (China)
+◦ Danaher Corporation (US)
+◦ Ingersoll Rand plc (Ireland)
+◦ FEIN Power Tools Inc. (Germany)
+◦ Panasonic Corporation (Japan)
+◦ KYOCERA Corporation (Japan)
+◦ Yamabiko Corporation (Japan)
+◦ Ken Holding Co., Ltd (China)
+◦ Dynabrade Inc. (US)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>By Product Type (Handguns, Rifles, Shotgun, Muzzle Loading), By Mechanism (Spring Powered, Electric Powered, Gas Powered), By Price Range (Low (up to 100$), Mid (100$-200$), High (above 300$)), By Distribution Channel (Online (E-commerce websites, Company websites), Offline (Hypermarket/supermarket, Departmental stores, Others))</t>
+          <t>By Tool Type (Drilling And Fastening Tools (Drills, Impact Drivers, Impact Wrenches, Screwdrivers And Nutrunners), Demolition Tools, Sawing And Cutting Tools (Jigsaws, Reciprocating Saws, Circular Saws, Band Saws, Shears &amp; Nibblers), Material Removal Tools, Routing Tools, Other Tools), By Mode Of Operation (Electric (Corded Tools, Cordless Tools), Pneumatic, Hydraulic), By Application (Industrial/Professional (Construction, Automotive, Aerospace, Energy, Shipbuilding, Other Industries), Residential/DIY)</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>62.29</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">

--- a/GII.xlsx
+++ b/GII.xlsx
@@ -582,16 +582,16 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>Power Tools Market size was valued at USD 37.5 billion in 2023 and is poised to grow from USD 39.68 billion in 2024 to USD 62.29 billion by 2032, growing at a CAGR of 5.8% during the forecast period (2025-2032).
-The power tools market is currently experiencing significant double-digit growth fueled by various factors in both developed and emerging economies. Notably, the rise in public infrastructure projects in markets like Brazil, Russia, India, China, South Africa, and Gulf Cooperation Council (GCC) countries is a key driver. With rapid population growth, nations like China and India are investing heavily in construction, leading to an increased demand for power tools across building, manufacturing, and maintenance sectors. Additionally, pandemic-induced behavioral shifts have spurred consumer interest in DIY projects, boosting sales of tools for home renovations. Looking ahead, anticipated investments in electric vehicle (EV) infrastructure, including 200 new gigafactories by 2030, will significantly elevate the requirement for power tools in this sector.
-Top-down and bottom-up approaches were used to estimate and validate the size of the Power Tools Market size was valued at USD 37.5 billion in 2023 and is poised to grow from USD 39.68 billion in 2024 to USD 62.29 billion by 2032, growing at a CAGR of 5.8% during the forecast period (2025-2032). market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
-Power Tools Market size was valued at USD 37.5 billion in 2023 and is poised to grow from USD 39.68 billion in 2024 to USD 62.29 billion by 2032, growing at a CAGR of 5.8% during the forecast period (2025-2032). Market Segments Analysis
+The power tools market is experiencing significant growth driven by various factors, with double-digit increases noted in both developed and emerging economies. Key contributors include heightened demand for public infrastructure projects, particularly in rapidly growing nations like China and India, which are investing heavily in construction to support their burgeoning populations. This trend is further bolstered by a surge in DIY home renovation projects during the pandemic, as consumers found themselves with more time at home. Looking ahead, the market is poised for continued expansion, largely fueled by the rising interest in electric vehicles (EVs). With projections for 200 new giga-factories by 2030 dedicated to EV battery manufacturing, the demand for power tools across sectors such as construction and maintenance is set to escalate significantly.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Power Tools market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Power Tools Market Segments Analysis
 Global Power Tools Market is segmented by Tool Type, Mode Of Operation, Application and region. Based on Tool Type, the market is segmented into Drilling And Fastening Tools, Demolition Tools, Sawing And Cutting Tools, Material Removal Tools, Routing Tools and Other Tools. Based on Mode Of Operation, the market is segmented into Electric, Pneumatic and Hydraulic. Based on Application, the market is segmented into Industrial/Professional and Residential/DIY. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
-Driver of the Power Tools Market size was valued at USD 37.5 billion in 2023 and is poised to grow from USD 39.68 billion in 2024 to USD 62.29 billion by 2032, growing at a CAGR of 5.8% during the forecast period (2025-2032). Market
-One of the key market drivers for the global power tools market is the increasing demand for efficient and time-saving construction and manufacturing solutions. As urbanization and infrastructure development accelerate worldwide, there is a growing need for advanced power tools that enhance productivity and precision. The rise of DIY culture, particularly among millennials and homeowners seeking to undertake renovations and home improvements, further fuels this demand. Additionally, technological advancements in battery-powered and cordless tools are driving innovation and attracting both professional and amateur users, thus contributing to the market's robust growth forecasted from 2024 to 2032.
-Restraints in the Power Tools Market size was valued at USD 37.5 billion in 2023 and is poised to grow from USD 39.68 billion in 2024 to USD 62.29 billion by 2032, growing at a CAGR of 5.8% during the forecast period (2025-2032). Market
-The Power Tools Market is currently navigating several restraints that could hinder its growth. One significant challenge is the volatility in raw material prices, largely affecting the production of power tools, including power generators. Developed nations such as the United States, the United Kingdom, Japan, China, and India are projected to drive demand; however, fluctuating costs and economic instability pose risks. Many power tools are manufactured using steel, metals, and aluminum, materials that are often not locally sourced, resulting in price variations impacted by exchange rate fluctuations. These rising raw material costs consequently limit the overall growth potential of the market.
-Market Trends of the Power Tools Market size was valued at USD 37.5 billion in 2023 and is poised to grow from USD 39.68 billion in 2024 to USD 62.29 billion by 2032, growing at a CAGR of 5.8% during the forecast period (2025-2032). Market
-The Power Tools Market is experiencing a significant shift as it evolves towards sustainable and versatile solutions, with a market size valued at USD 37.5 billion in 2023, projected to grow to USD 62.29 billion by 2032, reflecting a robust CAGR of 5.8% from 2025 onwards. Leading companies like Atlas Copco AB and Robert Bosch Tool Corporation are at the forefront, introducing green energy technologies and multi-use cordless tools that cater to consumer preferences for lightweight, portable, and highly accurate devices. This demand for high-quality, efficient products drives innovation, positioning disruptive players to capitalize on the evolving landscape of the power tools industry.</t>
+Driver of the Power Tools Market
+One of the key market drivers for the Global Power Tools Market is the rapid growth of the construction and manufacturing sectors, particularly in emerging economies. As urbanization accelerates and infrastructure development gains momentum, there is a rising demand for efficient and high-performance tools that can enhance productivity and reduce labor costs. Additionally, the DIY (Do-It-Yourself) trend among consumers is further fueling the market, as more homeowners undertake renovation and repair projects themselves. Innovations in cordless technology, battery efficiency, and smart tools are also contributing to the growing popularity and adoption of power tools across various applications.
+Restraints in the Power Tools Market
+The power tools market faces significant restraints due to several challenges impacting the tool industry. Fluctuations in raw material prices, particularly those required for manufacturing power tools, pose a critical threat to market stability. Major economies, such as the United States, United Kingdom, Japan, China, and India, are expected to drive the demand for these tools. However, the interdependence of raw material costs and market growth creates a complex scenario, as many essential materials like steel, metals, and aluminum are not produced domestically in numerous regions. Furthermore, the constant volatility in exchange rates and economic conditions further exacerbates price variations, hindering sustainable market growth and creating barriers for industry participants.
+Market Trends of the Power Tools Market
+The power tools market is witnessing a significant trend towards green energy solutions and multi-use cordless designs. Industry leaders like Atlas Copco AB and Robert Bosch Tool Corporation are at the forefront, offering products that emphasize energy efficiency and versatility. As consumers increasingly prioritize portability and ease of use, the demand for lightweight, cordless tools that can perform multiple tasks with high precision has surged. This shift is driving innovative companies to adopt disruptive strategies, enabling them to fulfill the growing consumer appetite for high-quality, reliable power tools. Consequently, the market is evolving, adapting to sustainability and multifunctionality in its offerings.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">

--- a/GII.xlsx
+++ b/GII.xlsx
@@ -544,23 +544,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Power Tools Market Size, Share, and Growth Analysis, By Tool Type (Drilling And Fastening Tools, Demolition Tools), By Mode Of Operation (Electric, Pneumatic), By Application, By Region - Industry Forecast 2025-2032</t>
+          <t>Light Gauge Steel Framing Market Size, Share, and Growth Analysis, By Type (Skeleton Steel Framing, Wall Bearing Steel Framing), By End Use (Commercial, Residential), By Location, By Region -Industry Forecast 2025-2032 - Industry Forecast 2025-2032</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SQMIG20D2077</t>
+          <t>SQMIG20C2124</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.skyquestt.com/report/power-tools-market</t>
+          <t>https://www.skyquestt.com/report/light-gauge-steel-framing-market</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -581,17 +581,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Power Tools Market size was valued at USD 37.5 billion in 2023 and is poised to grow from USD 39.68 billion in 2024 to USD 62.29 billion by 2032, growing at a CAGR of 5.8% during the forecast period (2025-2032).
-The power tools market is experiencing significant growth driven by various factors, with double-digit increases noted in both developed and emerging economies. Key contributors include heightened demand for public infrastructure projects, particularly in rapidly growing nations like China and India, which are investing heavily in construction to support their burgeoning populations. This trend is further bolstered by a surge in DIY home renovation projects during the pandemic, as consumers found themselves with more time at home. Looking ahead, the market is poised for continued expansion, largely fueled by the rising interest in electric vehicles (EVs). With projections for 200 new giga-factories by 2030 dedicated to EV battery manufacturing, the demand for power tools across sectors such as construction and maintenance is set to escalate significantly.
-Top-down and bottom-up approaches were used to estimate and validate the size of the Power Tools market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
-Power Tools Market Segments Analysis
-Global Power Tools Market is segmented by Tool Type, Mode Of Operation, Application and region. Based on Tool Type, the market is segmented into Drilling And Fastening Tools, Demolition Tools, Sawing And Cutting Tools, Material Removal Tools, Routing Tools and Other Tools. Based on Mode Of Operation, the market is segmented into Electric, Pneumatic and Hydraulic. Based on Application, the market is segmented into Industrial/Professional and Residential/DIY. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
-Driver of the Power Tools Market
-One of the key market drivers for the Global Power Tools Market is the rapid growth of the construction and manufacturing sectors, particularly in emerging economies. As urbanization accelerates and infrastructure development gains momentum, there is a rising demand for efficient and high-performance tools that can enhance productivity and reduce labor costs. Additionally, the DIY (Do-It-Yourself) trend among consumers is further fueling the market, as more homeowners undertake renovation and repair projects themselves. Innovations in cordless technology, battery efficiency, and smart tools are also contributing to the growing popularity and adoption of power tools across various applications.
-Restraints in the Power Tools Market
-The power tools market faces significant restraints due to several challenges impacting the tool industry. Fluctuations in raw material prices, particularly those required for manufacturing power tools, pose a critical threat to market stability. Major economies, such as the United States, United Kingdom, Japan, China, and India, are expected to drive the demand for these tools. However, the interdependence of raw material costs and market growth creates a complex scenario, as many essential materials like steel, metals, and aluminum are not produced domestically in numerous regions. Furthermore, the constant volatility in exchange rates and economic conditions further exacerbates price variations, hindering sustainable market growth and creating barriers for industry participants.
-Market Trends of the Power Tools Market
-The power tools market is witnessing a significant trend towards green energy solutions and multi-use cordless designs. Industry leaders like Atlas Copco AB and Robert Bosch Tool Corporation are at the forefront, offering products that emphasize energy efficiency and versatility. As consumers increasingly prioritize portability and ease of use, the demand for lightweight, cordless tools that can perform multiple tasks with high precision has surged. This shift is driving innovative companies to adopt disruptive strategies, enabling them to fulfill the growing consumer appetite for high-quality, reliable power tools. Consequently, the market is evolving, adapting to sustainability and multifunctionality in its offerings.</t>
+          <t>Global Light Gauge Steel Framing Market size was valued at USD 38.6 billion in 2023 and is poised to grow from USD 41.03 billion in 2024 to USD 66.89 billion by 2032, growing at a CAGR of 6.3% during the forecast period (2025-2032).
+The global light gauge steel framing (LGSF) market is poised for substantial growth driven by the rising demand in both developed and developing countries due to increased construction activities. Housing initiatives supported by governments in nations like India and China are particularly influential, promoting LGSF adoption to support rapid urbanization and infrastructure expansion. Innovative collaborations, such as those involving Tata BlueScope Steel, demonstrate the advantages of using high-strength galvanized steel for building affordable, durable, and earthquake-resistant housing. Additionally, LGSF's ability to reduce project timelines and enhance installation efficiency makes it a preferred choice in high-rise construction. Its strength and flexibility under seismic stress further solidify its popularity in earthquake-prone areas, positioning it as a key player in modern construction technology.
+Top-down and bottom-up approaches were used to estimate and validate the size of the Global Light Gauge Steel Framing market and to estimate the size of various other dependent submarkets. The research methodology used to estimate the market size includes the following details: The key players in the market were identified through secondary research, and their market shares in the respective regions were determined through primary and secondary research. This entire procedure includes the study of the annual and financial reports of the top market players and extensive interviews for key insights from industry leaders such as CEOs, VPs, directors, and marketing executives. All percentage shares split, and breakdowns were determined using secondary sources and verified through Primary sources. All possible parameters that affect the markets covered in this research study have been accounted for, viewed in extensive detail, verified through primary research, and analyzed to get the final quantitative and qualitative data.
+Global Light Gauge Steel Framing Market Segments Analysis
+Global Light Gauge Steel Framing Market is segmented by Type, End Use and region. Based on Type, the market is segmented into Skeleton steel framing, Wall bearing steel framing and Long span steel framing. Based on End Use, the market is segmented into Commercial, Residential and Industrial. Based on region, the market is segmented into North America, Europe, Asia Pacific, Latin America and Middle East &amp; Africa.
+Driver of the Global Light Gauge Steel Framing Market
+The Global Light Gauge Steel Framing market is bolstered by the inherent adaptability of steel frames, which can be molded to fulfill specific structural and architectural needs. This versatility empowers architects and developers to bring innovative and customized designs to life, particularly in projects like modular classroom facilities for educational institutions. Bespoke steel frames can be crafted for off-site construction, enabling unique classroom layouts and architectural elements. Moreover, the stringent quality control measures practiced during the manufacturing of light gauge steel framing enhance its appeal for applications in healthcare facilities, where structural precision and stability are paramount for critical infrastructure projects.
+Restraints in the Global Light Gauge Steel Framing Market
+The Global Light Gauge Steel Framing market faces significant restraints largely due to the inherent conservatism in the building industry regarding the adoption of innovative materials and techniques. Many industry players struggle to transition to light gauge framing, as they are often deeply accustomed to traditional building methods. This reluctance to change can stem from concerns about potential disruptions in established practices, the costs associated with retraining employees, and a lack of confidence in the enduring sustainability and efficiency of light gauge steel framing. Consequently, these factors collectively hinder the expansion and growth of the light gauge steel framing market worldwide.
+Market Trends of the Global Light Gauge Steel Framing Market
+The Global Light Gauge Steel Framing market is witnessing a significant trend towards the integration of Building Information Modeling (BIM) and Artificial Intelligence (AI), transforming construction and design processes. This synergy streamlines project planning and enhances coordination, while AI-driven software improves accuracy, reduces material wastage, and optimizes resource allocation. Companies like FRAMECAD are leading this innovation by providing AI-based structural software that increases construction efficiency and minimizes errors. As a result, light gauge steel framing is becoming a preferred choice in the industry, driving growth and adoption across various sectors, thereby positioning itself as a pivotal player in the evolving construction landscape.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -631,66 +631,41 @@
 o Macro-Economic Indicators
 o Value Chain Analysis
 o Pricing Analysis
-o Regulatory Analysis
-o Technology Analysis
-• Global Power Tools Market Size by Tool Type &amp; CAGR (2025-2032)
+• Global Light Gauge Steel Framing Market Size by Type &amp; CAGR (2025-2032)
 o Market Overview
-o Drilling And Fastening Tools
- Drills
- Impact Drivers
- Impact Wrenches
- Screwdrivers And Nutrunners
-o Demolition Tools
-o Sawing And Cutting Tools
- Jigsaws
- Reciprocating Saws
- Circular Saws
- Band Saws
- Shears &amp; Nibblers
-o Material Removal Tools
- Sanders/Polishers/Buffers
- Air Scalers
- Grinders
-o Routing Tools
-o Other Tools
-• Global Power Tools Market Size by Mode Of Operation &amp; CAGR (2025-2032)
+o Skeleton steel framing
+o Wall bearing steel framing
+o Long span steel framing
+• Global Light Gauge Steel Framing Market Size by End Use &amp; CAGR (2025-2032)
 o Market Overview
-o Electric
- Corded Tools
- Cordless Tools
-o Pneumatic
-o Hydraulic
-• Global Power Tools Market Size by Application &amp; CAGR (2025-2032)
-o Market Overview
-o Industrial/Professional
- Construction
- Automotive
- Aerospace
- Energy
- Shipbuilding
- Other Industries
-o Residential/DIY
-• Global Power Tools Market Size &amp; CAGR (2025-2032)
-o North America (Tool Type, Mode Of Operation, Application)
+o Commercial
+ Hospitals
+ Malls
+ Educational Institutes
+ Others
+o Residential
+o Industrial
+• Global Light Gauge Steel Framing Market Size &amp; CAGR (2025-2032)
+o North America (Type, End Use)
  US
  Canada
-o Europe (Tool Type, Mode Of Operation, Application)
+o Europe (Type, End Use)
  Germany
  Spain
  France
  UK
  Italy
  Rest of Europe
-o Asia Pacific (Tool Type, Mode Of Operation, Application)
+o Asia Pacific (Type, End Use)
  China
  India
  Japan
  South Korea
  Rest of Asia-Pacific
-o Latin America (Tool Type, Mode Of Operation, Application)
+o Latin America (Type, End Use)
  Brazil
  Rest of Latin America
-o Middle East &amp; Africa (Tool Type, Mode Of Operation, Application)
+o Middle East &amp; Africa (Type, End Use)
  GCC Countries
  South Africa
  Rest of Middle East &amp; Africa
@@ -706,87 +681,102 @@
  Company's Segmental Share Analysis
  Revenue Y-O-Y Comparison (2022-2024)
 • Key Company Profiles
-o Robert Bosch GmbH (Germany)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Techtronic Industries Co. Ltd. (TTI) (Hong Kong)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Makita Corporation (Japan)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Hilti Corporation (Liechtenstein)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Atlas Copco AB (Sweden)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Snap-on Incorporated (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Emerson Electric Co. (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Chervon (China) Trading Co. Ltd. (China)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o TTI (Techtronic Industries) Power Tools (China)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Danaher Corporation (US)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Ingersoll Rand plc (Ireland)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o FEIN Power Tools Inc. (Germany)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Panasonic Corporation (Japan)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o KYOCERA Corporation (Japan)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Yamabiko Corporation (Japan)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Ken Holding Co., Ltd (China)
- Company Overview
- Business Segment Overview
- Financial Updates
- Key Developments
-o Dynabrade Inc. (US)
+o ArcelorMittal S.A. (Luxembourg)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o ClarkDietrich Building Systems LLC (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o CEMCO (California Expanded Metal Products Co.) (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Hadley Industries PLC (UK)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Genesis Manazil Steel Framing (UAE)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Jinggong Steel (China)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Precision Walls Inc. (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o FRAMECAD (New Zealand)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Nucor Building Systems (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Allied Steel Buildings (USA)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Scottsdale Construction Systems (New Zealand)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Tata BlueScope Steel (India/Australia)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o EPACK Prefab (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Stratus Steel (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Multi Decor India Pvt. Ltd. (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o INDUE PREFAB PVT LTD (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Steelifi (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o Tata Steel Nest-In (India)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o MEXI® Steel (Romania)
+ Company Overview
+ Business Segment Overview
+ Financial Updates
+ Key Developments
+o MBA Building Supplies (Australia)
  Company Overview
  Business Segment Overview
  Financial Updates
@@ -822,48 +812,51 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>◦ Robert Bosch GmbH (Germany)
-◦ Techtronic Industries Co. Ltd. (TTI) (Hong Kong)
-◦ Makita Corporation (Japan)
-◦ Hilti Corporation (Liechtenstein)
-◦ Atlas Copco AB (Sweden)
-◦ Snap-on Incorporated (US)
-◦ Emerson Electric Co. (US)
-◦ Chervon (China) Trading Co. Ltd. (China)
-◦ TTI (Techtronic Industries) Power Tools (China)
-◦ Danaher Corporation (US)
-◦ Ingersoll Rand plc (Ireland)
-◦ FEIN Power Tools Inc. (Germany)
-◦ Panasonic Corporation (Japan)
-◦ KYOCERA Corporation (Japan)
-◦ Yamabiko Corporation (Japan)
-◦ Ken Holding Co., Ltd (China)
-◦ Dynabrade Inc. (US)</t>
+          <t>◦ ArcelorMittal S.A. (Luxembourg)
+◦ ClarkDietrich Building Systems LLC (USA)
+◦ CEMCO (California Expanded Metal Products Co.) (USA)
+◦ Hadley Industries PLC (UK)
+◦ Genesis Manazil Steel Framing (UAE)
+◦ Jinggong Steel (China)
+◦ Precision Walls Inc. (USA)
+◦ FRAMECAD (New Zealand)
+◦ Nucor Building Systems (USA)
+◦ Allied Steel Buildings (USA)
+◦ Scottsdale Construction Systems (New Zealand)
+◦ Tata BlueScope Steel (India/Australia)
+◦ EPACK Prefab (India)
+◦ Stratus Steel (India)
+◦ Multi Decor India Pvt. Ltd. (India)
+◦ INDUE PREFAB PVT LTD (India)
+◦ Steelifi (India)
+◦ Tata Steel Nest-In (India)
+◦ MEXI® Steel (Romania)
+◦ MBA Building Supplies (Australia)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>By Tool Type (Drilling And Fastening Tools (Drills, Impact Drivers, Impact Wrenches, Screwdrivers And Nutrunners), Demolition Tools, Sawing And Cutting Tools (Jigsaws, Reciprocating Saws, Circular Saws, Band Saws, Shears &amp; Nibblers), Material Removal Tools, Routing Tools, Other Tools), By Mode Of Operation (Electric (Corded Tools, Cordless Tools), Pneumatic, Hydraulic), By Application (Industrial/Professional (Construction, Automotive, Aerospace, Energy, Shipbuilding, Other Industries), Residential/DIY)</t>
+          <t>By Type (Skeleton steel framing, Wall bearing steel framing, Long span steel framing), By End Use (Commercial, Residential, Industrial)</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>62.29</t>
+          <t>66.89</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
